--- a/data/AMP.MI.xlsx
+++ b/data/AMP.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>925542</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>11.5699996948242</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>11.3549995422363</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>11.5200004577637</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>11.4250001907349</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AMP.MI.xlsx
+++ b/data/AMP.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>735779</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>11.4849996566772</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>11.2250003814697</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>11.3950004577637</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>11.4700002670288</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AMP.MI.xlsx
+++ b/data/AMP.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>591325</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>11.6099996566772</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>11.3450002670288</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>11.4449996948242</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>11.5050001144409</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AMP.MI.xlsx
+++ b/data/AMP.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>693011</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>11.6350002288818</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>11.4099998474121</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>11.6000003814697</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>11.5900001525879</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AMP.MI.xlsx
+++ b/data/AMP.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>1025886</v>
+        <v>1476258</v>
       </c>
       <c r="C2715" t="n">
-        <v>11.8599996566772</v>
+        <v>11.7700004577637</v>
       </c>
       <c r="D2715" t="n">
-        <v>11.5450000762939</v>
+        <v>11.5349998474121</v>
       </c>
       <c r="E2715" t="n">
-        <v>11.6350002288818</v>
+        <v>11.7700004577637</v>
       </c>
       <c r="F2715" t="n">
-        <v>11.5500001907349</v>
+        <v>11.6700000762939</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>1253387</v>
+        <v>1025886</v>
       </c>
       <c r="C2716" t="n">
-        <v>11.5349998474121</v>
+        <v>11.8599996566772</v>
       </c>
       <c r="D2716" t="n">
-        <v>11.210000038147</v>
+        <v>11.5450000762939</v>
       </c>
       <c r="E2716" t="n">
-        <v>11.5249996185303</v>
+        <v>11.6350002288818</v>
       </c>
       <c r="F2716" t="n">
-        <v>11.2950000762939</v>
+        <v>11.5500001907349</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>808816</v>
+        <v>1253387</v>
       </c>
       <c r="C2717" t="n">
-        <v>11.4200000762939</v>
+        <v>11.5349998474121</v>
       </c>
       <c r="D2717" t="n">
-        <v>11.2049999237061</v>
+        <v>11.210000038147</v>
       </c>
       <c r="E2717" t="n">
-        <v>11.2250003814697</v>
+        <v>11.5249996185303</v>
       </c>
       <c r="F2717" t="n">
-        <v>11.3450002670288</v>
+        <v>11.2950000762939</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>1370690</v>
+        <v>808816</v>
       </c>
       <c r="C2718" t="n">
-        <v>11.5500001907349</v>
+        <v>11.4200000762939</v>
       </c>
       <c r="D2718" t="n">
-        <v>11.2349996566772</v>
+        <v>11.2049999237061</v>
       </c>
       <c r="E2718" t="n">
-        <v>11.3299999237061</v>
+        <v>11.2250003814697</v>
       </c>
       <c r="F2718" t="n">
-        <v>11.5150003433228</v>
+        <v>11.3450002670288</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>925542</v>
+        <v>1370690</v>
       </c>
       <c r="C2719" t="n">
-        <v>11.5699996948242</v>
+        <v>11.5500001907349</v>
       </c>
       <c r="D2719" t="n">
-        <v>11.3549995422363</v>
+        <v>11.2349996566772</v>
       </c>
       <c r="E2719" t="n">
-        <v>11.5200004577637</v>
+        <v>11.3299999237061</v>
       </c>
       <c r="F2719" t="n">
-        <v>11.4250001907349</v>
+        <v>11.5150003433228</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>735779</v>
+        <v>925542</v>
       </c>
       <c r="C2720" t="n">
-        <v>11.4849996566772</v>
+        <v>11.5699996948242</v>
       </c>
       <c r="D2720" t="n">
-        <v>11.2250003814697</v>
+        <v>11.3549995422363</v>
       </c>
       <c r="E2720" t="n">
-        <v>11.3950004577637</v>
+        <v>11.5200004577637</v>
       </c>
       <c r="F2720" t="n">
-        <v>11.4700002670288</v>
+        <v>11.4250001907349</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>591325</v>
+        <v>735779</v>
       </c>
       <c r="C2721" t="n">
-        <v>11.6099996566772</v>
+        <v>11.4849996566772</v>
       </c>
       <c r="D2721" t="n">
-        <v>11.3450002670288</v>
+        <v>11.2250003814697</v>
       </c>
       <c r="E2721" t="n">
-        <v>11.4449996948242</v>
+        <v>11.3950004577637</v>
       </c>
       <c r="F2721" t="n">
-        <v>11.5050001144409</v>
+        <v>11.4700002670288</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>693011</v>
+        <v>591325</v>
       </c>
       <c r="C2722" t="n">
-        <v>11.6350002288818</v>
+        <v>11.6099996566772</v>
       </c>
       <c r="D2722" t="n">
-        <v>11.4099998474121</v>
+        <v>11.3450002670288</v>
       </c>
       <c r="E2722" t="n">
+        <v>11.4449996948242</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>11.5050001144409</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>1664912</v>
+      </c>
+      <c r="C2723" t="n">
         <v>11.6000003814697</v>
       </c>
-      <c r="F2722" t="n">
-        <v>11.5900001525879</v>
-      </c>
-      <c r="G2722" t="s">
+      <c r="D2723" t="n">
+        <v>11.3199996948242</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>11.5100002288818</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>11.3950004577637</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/AMP.MI.xlsx
+++ b/data/AMP.MI.xlsx
@@ -421,7 +421,7 @@
         <v>7.875</v>
       </c>
       <c r="G2" t="n">
-        <v>7.14058446884155</v>
+        <v>7.14058399200439</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G4" t="n">
-        <v>7.11791563034058</v>
+        <v>7.11791515350342</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G6" t="n">
-        <v>6.96376991271973</v>
+        <v>6.96376895904541</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G10" t="n">
-        <v>6.97283744812012</v>
+        <v>6.9728364944458</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G15" t="n">
-        <v>6.94563436508179</v>
+        <v>6.9456353187561</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>7.88500022888184</v>
       </c>
       <c r="G16" t="n">
-        <v>7.14965105056763</v>
+        <v>7.14965152740479</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G19" t="n">
-        <v>7.11791563034058</v>
+        <v>7.11791515350342</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>7.67500019073486</v>
       </c>
       <c r="G20" t="n">
-        <v>6.95923566818237</v>
+        <v>6.95923614501953</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G21" t="n">
-        <v>6.99097108840942</v>
+        <v>6.99097156524658</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>7.95499992370605</v>
       </c>
       <c r="G22" t="n">
-        <v>7.21312236785889</v>
+        <v>7.21312284469604</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G23" t="n">
-        <v>7.09071350097656</v>
+        <v>7.09071254730225</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>7.66499996185303</v>
       </c>
       <c r="G24" t="n">
-        <v>6.95016765594482</v>
+        <v>6.95016860961914</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>7.57000017166138</v>
       </c>
       <c r="G25" t="n">
-        <v>6.86402750015259</v>
+        <v>6.86402797698975</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G26" t="n">
-        <v>6.66454553604126</v>
+        <v>6.66454362869263</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G27" t="n">
-        <v>6.33811807632446</v>
+        <v>6.3381175994873</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>7.07499980926514</v>
       </c>
       <c r="G29" t="n">
-        <v>6.41519069671631</v>
+        <v>6.41519117355347</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>6.75500011444092</v>
       </c>
       <c r="G31" t="n">
-        <v>6.12503480911255</v>
+        <v>6.12503433227539</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>7.10500001907349</v>
       </c>
       <c r="G33" t="n">
-        <v>6.44239282608032</v>
+        <v>6.44239377975464</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G34" t="n">
-        <v>6.70081472396851</v>
+        <v>6.70081424713135</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G35" t="n">
-        <v>6.70081472396851</v>
+        <v>6.70081424713135</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G37" t="n">
-        <v>6.65547752380371</v>
+        <v>6.65547800064087</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>7.11499977111816</v>
       </c>
       <c r="G39" t="n">
-        <v>6.45146036148071</v>
+        <v>6.45146083831787</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G40" t="n">
-        <v>6.80962371826172</v>
+        <v>6.80962419509888</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G42" t="n">
-        <v>6.7098822593689</v>
+        <v>6.70988130569458</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G44" t="n">
-        <v>6.70081472396851</v>
+        <v>6.70081424713135</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>7.30499982833862</v>
       </c>
       <c r="G45" t="n">
-        <v>6.62374114990234</v>
+        <v>6.6237416267395</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G46" t="n">
-        <v>6.61920785903931</v>
+        <v>6.61920833587646</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>7.10500001907349</v>
       </c>
       <c r="G48" t="n">
-        <v>6.44239282608032</v>
+        <v>6.44239377975464</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G49" t="n">
-        <v>6.48319721221924</v>
+        <v>6.48319673538208</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G50" t="n">
-        <v>6.45599508285522</v>
+        <v>6.45599365234375</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>7.29500007629395</v>
       </c>
       <c r="G51" t="n">
-        <v>6.61467409133911</v>
+        <v>6.61467361450195</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G52" t="n">
-        <v>6.66454553604126</v>
+        <v>6.66454362869263</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>7.28499984741211</v>
       </c>
       <c r="G53" t="n">
-        <v>6.60560703277588</v>
+        <v>6.60560655593872</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>7.36499977111816</v>
       </c>
       <c r="G54" t="n">
-        <v>6.67814636230469</v>
+        <v>6.67814588546753</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>7.52500009536743</v>
       </c>
       <c r="G55" t="n">
-        <v>6.8232250213623</v>
+        <v>6.82322406768799</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>7.60500001907349</v>
       </c>
       <c r="G57" t="n">
-        <v>6.89576387405396</v>
+        <v>6.8957633972168</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>7.63000011444092</v>
       </c>
       <c r="G60" t="n">
-        <v>6.91843271255493</v>
+        <v>6.91843175888062</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>7.77500009536743</v>
       </c>
       <c r="G62" t="n">
-        <v>7.04991006851196</v>
+        <v>7.0499095916748</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G63" t="n">
-        <v>6.90936517715454</v>
+        <v>6.90936470031738</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G64" t="n">
-        <v>6.98190450668335</v>
+        <v>6.98190355300903</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G65" t="n">
-        <v>6.96376991271973</v>
+        <v>6.96376895904541</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>7.63000011444092</v>
       </c>
       <c r="G66" t="n">
-        <v>6.91843271255493</v>
+        <v>6.91843175888062</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G67" t="n">
-        <v>6.96376991271973</v>
+        <v>6.96376895904541</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>7.44500017166138</v>
       </c>
       <c r="G68" t="n">
-        <v>6.75068616867065</v>
+        <v>6.7506856918335</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G69" t="n">
-        <v>6.90936517715454</v>
+        <v>6.90936470031738</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>7.42500019073486</v>
       </c>
       <c r="G70" t="n">
-        <v>6.73255014419556</v>
+        <v>6.73255062103271</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>7.57000017166138</v>
       </c>
       <c r="G71" t="n">
-        <v>6.86402750015259</v>
+        <v>6.86402797698975</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G72" t="n">
-        <v>6.81869029998779</v>
+        <v>6.81869125366211</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G73" t="n">
-        <v>6.96376991271973</v>
+        <v>6.96376895904541</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>7.77500009536743</v>
       </c>
       <c r="G76" t="n">
-        <v>7.04991006851196</v>
+        <v>7.0499095916748</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>7.86499977111816</v>
       </c>
       <c r="G77" t="n">
-        <v>7.13151597976685</v>
+        <v>7.13151693344116</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G78" t="n">
-        <v>7.03630781173706</v>
+        <v>7.03630876541138</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G79" t="n">
-        <v>6.97283744812012</v>
+        <v>6.9728364944458</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>7.67500019073486</v>
       </c>
       <c r="G80" t="n">
-        <v>6.95923566818237</v>
+        <v>6.95923614501953</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>8.03499984741211</v>
       </c>
       <c r="G84" t="n">
-        <v>7.28566265106201</v>
+        <v>7.2856616973877</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>8.13500022888184</v>
       </c>
       <c r="G85" t="n">
-        <v>7.37633562088013</v>
+        <v>7.37633657455444</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>8.10999965667725</v>
       </c>
       <c r="G86" t="n">
-        <v>7.35366725921631</v>
+        <v>7.35366678237915</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G87" t="n">
-        <v>7.5259485244751</v>
+        <v>7.52594900131226</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G88" t="n">
-        <v>7.39900541305542</v>
+        <v>7.39900588989258</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>8.20499992370605</v>
       </c>
       <c r="G89" t="n">
-        <v>7.43980836868286</v>
+        <v>7.43980884552002</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G90" t="n">
-        <v>7.49874639511108</v>
+        <v>7.49874687194824</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>8.30500030517578</v>
       </c>
       <c r="G91" t="n">
-        <v>7.53048324584961</v>
+        <v>7.53048276901245</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G92" t="n">
-        <v>7.5259485244751</v>
+        <v>7.52594900131226</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G94" t="n">
-        <v>7.68009471893311</v>
+        <v>7.68009567260742</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G95" t="n">
-        <v>7.66195964813232</v>
+        <v>7.66195917129517</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>8.52999973297119</v>
       </c>
       <c r="G97" t="n">
-        <v>7.73449850082397</v>
+        <v>7.73449897766113</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>8.6850004196167</v>
       </c>
       <c r="G99" t="n">
-        <v>7.87504434585571</v>
+        <v>7.8750433921814</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G101" t="n">
-        <v>7.88233327865601</v>
+        <v>7.88233280181885</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G102" t="n">
-        <v>7.89144515991211</v>
+        <v>7.89144659042358</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G103" t="n">
-        <v>7.83677101135254</v>
+        <v>7.83677196502686</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G104" t="n">
-        <v>7.95523309707642</v>
+        <v>7.95523357391357</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>8.77499961853027</v>
       </c>
       <c r="G105" t="n">
-        <v>7.99624109268188</v>
+        <v>7.99624061584473</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>8.71500015258789</v>
       </c>
       <c r="G108" t="n">
-        <v>7.94156646728516</v>
+        <v>7.94156551361084</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G109" t="n">
-        <v>7.86410856246948</v>
+        <v>7.8641095161438</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>8.63500022888184</v>
       </c>
       <c r="G110" t="n">
-        <v>7.86866474151611</v>
+        <v>7.86866426467896</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>8.45499992370605</v>
       </c>
       <c r="G113" t="n">
-        <v>7.70463943481445</v>
+        <v>7.70463991165161</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>8.35499954223633</v>
       </c>
       <c r="G114" t="n">
-        <v>7.61351346969604</v>
+        <v>7.61351442337036</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G116" t="n">
-        <v>7.42670726776123</v>
+        <v>7.42670631408691</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>8.17500019073486</v>
       </c>
       <c r="G117" t="n">
-        <v>7.4494891166687</v>
+        <v>7.44949007034302</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>8.07499980926514</v>
       </c>
       <c r="G118" t="n">
-        <v>7.35836362838745</v>
+        <v>7.35836315155029</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>8.53499984741211</v>
       </c>
       <c r="G120" t="n">
-        <v>7.77754020690918</v>
+        <v>7.77753973007202</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G121" t="n">
-        <v>7.73653316497803</v>
+        <v>7.73653364181519</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G122" t="n">
-        <v>7.84588384628296</v>
+        <v>7.84588289260864</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G123" t="n">
-        <v>7.88233327865601</v>
+        <v>7.88233280181885</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G124" t="n">
-        <v>7.4722695350647</v>
+        <v>7.47227001190186</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>8.25</v>
       </c>
       <c r="G126" t="n">
-        <v>7.51783275604248</v>
+        <v>7.51783323287964</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G127" t="n">
-        <v>7.42670726776123</v>
+        <v>7.42670631408691</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G129" t="n">
-        <v>7.71830892562866</v>
+        <v>7.71830940246582</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G130" t="n">
-        <v>7.68185901641846</v>
+        <v>7.6818585395813</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>8.34500026702881</v>
       </c>
       <c r="G131" t="n">
-        <v>7.6044020652771</v>
+        <v>7.60440063476562</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>8.24499988555908</v>
       </c>
       <c r="G132" t="n">
-        <v>7.51327610015869</v>
+        <v>7.51327657699585</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G133" t="n">
-        <v>7.73653316497803</v>
+        <v>7.73653364181519</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G134" t="n">
-        <v>7.67274618148804</v>
+        <v>7.67274522781372</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>8.50500011444092</v>
       </c>
       <c r="G135" t="n">
-        <v>7.75020217895508</v>
+        <v>7.75020265579224</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G136" t="n">
-        <v>7.68185901641846</v>
+        <v>7.6818585395813</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G137" t="n">
-        <v>7.70919466018677</v>
+        <v>7.70919418334961</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>8.60499954223633</v>
       </c>
       <c r="G141" t="n">
-        <v>7.84132671356201</v>
+        <v>7.84132766723633</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G142" t="n">
-        <v>7.96434593200684</v>
+        <v>7.96434640884399</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>8.72500038146973</v>
       </c>
       <c r="G143" t="n">
-        <v>7.95067739486694</v>
+        <v>7.95067644119263</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>8.75500011444092</v>
       </c>
       <c r="G144" t="n">
-        <v>7.97801494598389</v>
+        <v>7.97801542282104</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>8.875</v>
       </c>
       <c r="G146" t="n">
-        <v>8.08736419677734</v>
+        <v>8.08736610412598</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>8.9350004196167</v>
       </c>
       <c r="G147" t="n">
-        <v>8.14204025268555</v>
+        <v>8.14204216003418</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G150" t="n">
-        <v>8.11014652252197</v>
+        <v>8.11014556884766</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G152" t="n">
-        <v>7.93700933456421</v>
+        <v>7.93700838088989</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G154" t="n">
-        <v>8.14659690856934</v>
+        <v>8.14659595489502</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G155" t="n">
-        <v>8.14659690856934</v>
+        <v>8.14659595489502</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>9.19499969482422</v>
       </c>
       <c r="G157" t="n">
-        <v>8.37896728515625</v>
+        <v>8.37896537780762</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>9.22500038146973</v>
       </c>
       <c r="G159" t="n">
-        <v>8.40630435943604</v>
+        <v>8.40630340576172</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>9.35499954223633</v>
       </c>
       <c r="G160" t="n">
-        <v>8.52476787567139</v>
+        <v>8.52476692199707</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>9.24499988555908</v>
       </c>
       <c r="G161" t="n">
-        <v>8.42452907562256</v>
+        <v>8.42452812194824</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G164" t="n">
-        <v>8.68423461914062</v>
+        <v>8.68423557281494</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G165" t="n">
-        <v>8.61133575439453</v>
+        <v>8.61133670806885</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G166" t="n">
-        <v>8.58399772644043</v>
+        <v>8.58399868011475</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>9.34500026702881</v>
       </c>
       <c r="G167" t="n">
-        <v>8.51565551757812</v>
+        <v>8.51565456390381</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>9.24499988555908</v>
       </c>
       <c r="G168" t="n">
-        <v>8.42452907562256</v>
+        <v>8.42452812194824</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>9.22500038146973</v>
       </c>
       <c r="G169" t="n">
-        <v>8.40630435943604</v>
+        <v>8.40630340576172</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G173" t="n">
-        <v>8.58399772644043</v>
+        <v>8.58399868011475</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G175" t="n">
-        <v>8.53843688964844</v>
+        <v>8.5384349822998</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G177" t="n">
-        <v>8.52932357788086</v>
+        <v>8.52932262420654</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>9.25</v>
       </c>
       <c r="G178" t="n">
-        <v>8.42908477783203</v>
+        <v>8.42908668518066</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G179" t="n">
-        <v>8.36529922485352</v>
+        <v>8.3652982711792</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G180" t="n">
-        <v>8.34707164764404</v>
+        <v>8.34707450866699</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>9.19499969482422</v>
       </c>
       <c r="G181" t="n">
-        <v>8.37896728515625</v>
+        <v>8.37896537780762</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>9.14500045776367</v>
       </c>
       <c r="G182" t="n">
-        <v>8.33340454101562</v>
+        <v>8.33340549468994</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>9.0649995803833</v>
       </c>
       <c r="G183" t="n">
-        <v>8.2605037689209</v>
+        <v>8.26050281524658</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G184" t="n">
-        <v>8.34707164764404</v>
+        <v>8.34707450866699</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>9.125</v>
       </c>
       <c r="G185" t="n">
-        <v>8.31517791748047</v>
+        <v>8.3151798248291</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>9.11499977111816</v>
       </c>
       <c r="G186" t="n">
-        <v>8.30606651306152</v>
+        <v>8.30606842041016</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G188" t="n">
-        <v>8.27417373657227</v>
+        <v>8.27417182922363</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>9.125</v>
       </c>
       <c r="G189" t="n">
-        <v>8.31517791748047</v>
+        <v>8.3151798248291</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G190" t="n">
-        <v>8.34707164764404</v>
+        <v>8.34707450866699</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>9.20499992370605</v>
       </c>
       <c r="G191" t="n">
-        <v>8.3880786895752</v>
+        <v>8.38807964324951</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>9.07499980926514</v>
       </c>
       <c r="G192" t="n">
-        <v>8.26961708068848</v>
+        <v>8.26961421966553</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G193" t="n">
-        <v>8.32884693145752</v>
+        <v>8.32884883880615</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>9.22500038146973</v>
       </c>
       <c r="G196" t="n">
-        <v>8.40630435943604</v>
+        <v>8.40630340576172</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>9.11499977111816</v>
       </c>
       <c r="G197" t="n">
-        <v>8.30606651306152</v>
+        <v>8.30606842041016</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>9.04500007629395</v>
       </c>
       <c r="G198" t="n">
-        <v>8.24227809906006</v>
+        <v>8.24227905273438</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>9.07499980926514</v>
       </c>
       <c r="G199" t="n">
-        <v>8.26961708068848</v>
+        <v>8.26961421966553</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>9.10999965667725</v>
       </c>
       <c r="G200" t="n">
-        <v>8.30150890350342</v>
+        <v>8.30150985717773</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G202" t="n">
-        <v>8.33795833587646</v>
+        <v>8.33795928955078</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>9.25</v>
       </c>
       <c r="G203" t="n">
-        <v>8.42908477783203</v>
+        <v>8.42908668518066</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>9.19499969482422</v>
       </c>
       <c r="G204" t="n">
-        <v>8.37896728515625</v>
+        <v>8.37896537780762</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G205" t="n">
-        <v>8.36529922485352</v>
+        <v>8.3652982711792</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G206" t="n">
-        <v>8.36529922485352</v>
+        <v>8.3652982711792</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>9.28499984741211</v>
       </c>
       <c r="G207" t="n">
-        <v>8.46097755432129</v>
+        <v>8.46097850799561</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G208" t="n">
-        <v>8.36529922485352</v>
+        <v>8.3652982711792</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G209" t="n">
-        <v>8.33795833587646</v>
+        <v>8.33795928955078</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G210" t="n">
-        <v>8.33795833587646</v>
+        <v>8.33795928955078</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G211" t="n">
-        <v>8.83914852142334</v>
+        <v>8.83915042877197</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G213" t="n">
-        <v>8.83003711700439</v>
+        <v>8.83003520965576</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G217" t="n">
-        <v>8.70246124267578</v>
+        <v>8.7024621963501</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>9.41499996185303</v>
       </c>
       <c r="G219" t="n">
-        <v>8.57944107055664</v>
+        <v>8.57944202423096</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>9.22500038146973</v>
       </c>
       <c r="G220" t="n">
-        <v>8.40630435943604</v>
+        <v>8.40630340576172</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>9.25</v>
       </c>
       <c r="G221" t="n">
-        <v>8.42908477783203</v>
+        <v>8.42908668518066</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>9.11499977111816</v>
       </c>
       <c r="G222" t="n">
-        <v>8.30606651306152</v>
+        <v>8.30606842041016</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>9</v>
       </c>
       <c r="G224" t="n">
-        <v>8.20127296447754</v>
+        <v>8.20127201080322</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>8.97500038146973</v>
       </c>
       <c r="G225" t="n">
-        <v>8.17849063873291</v>
+        <v>8.17848968505859</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>8.97000026702881</v>
       </c>
       <c r="G226" t="n">
-        <v>8.17393493652344</v>
+        <v>8.17393398284912</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>9</v>
       </c>
       <c r="G227" t="n">
-        <v>8.20127296447754</v>
+        <v>8.20127201080322</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G229" t="n">
-        <v>8.32884693145752</v>
+        <v>8.32884883880615</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>9</v>
       </c>
       <c r="G230" t="n">
-        <v>8.20127296447754</v>
+        <v>8.20127201080322</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>8.91499996185303</v>
       </c>
       <c r="G231" t="n">
-        <v>8.12381458282471</v>
+        <v>8.12381649017334</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>9.0649995803833</v>
       </c>
       <c r="G232" t="n">
-        <v>8.2605037689209</v>
+        <v>8.26050281524658</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G233" t="n">
-        <v>8.34707164764404</v>
+        <v>8.34707450866699</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G236" t="n">
-        <v>8.24683666229248</v>
+        <v>8.24683380126953</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>9.10999965667725</v>
       </c>
       <c r="G237" t="n">
-        <v>8.30150890350342</v>
+        <v>8.30150985717773</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>9.125</v>
       </c>
       <c r="G238" t="n">
-        <v>8.31517791748047</v>
+        <v>8.3151798248291</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G242" t="n">
-        <v>8.29239749908447</v>
+        <v>8.29239845275879</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G243" t="n">
-        <v>7.94612121582031</v>
+        <v>7.94612216949463</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G244" t="n">
-        <v>8.09192085266113</v>
+        <v>8.09192180633545</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G245" t="n">
-        <v>7.70919466018677</v>
+        <v>7.70919418334961</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G246" t="n">
-        <v>7.24445676803589</v>
+        <v>7.24445724487305</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>8.52999973297119</v>
       </c>
       <c r="G247" t="n">
-        <v>7.77298259735107</v>
+        <v>7.77298402786255</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G248" t="n">
-        <v>7.67274618148804</v>
+        <v>7.67274522781372</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>8.5</v>
       </c>
       <c r="G249" t="n">
-        <v>7.74564599990845</v>
+        <v>7.74564695358276</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>8.75500011444092</v>
       </c>
       <c r="G251" t="n">
-        <v>7.97801494598389</v>
+        <v>7.97801542282104</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G252" t="n">
-        <v>7.88233327865601</v>
+        <v>7.88233280181885</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G254" t="n">
-        <v>8.16482067108154</v>
+        <v>8.16482162475586</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>8.98499965667725</v>
       </c>
       <c r="G255" t="n">
-        <v>8.18760395050049</v>
+        <v>8.18760204315186</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>9.02499961853027</v>
       </c>
       <c r="G256" t="n">
-        <v>8.22405338287354</v>
+        <v>8.22405433654785</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G257" t="n">
-        <v>8.24683666229248</v>
+        <v>8.24683380126953</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>9</v>
       </c>
       <c r="G259" t="n">
-        <v>8.20127296447754</v>
+        <v>8.20127201080322</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G260" t="n">
-        <v>8.25594806671143</v>
+        <v>8.25594711303711</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G261" t="n">
-        <v>8.25594806671143</v>
+        <v>8.25594711303711</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>9</v>
       </c>
       <c r="G262" t="n">
-        <v>8.20127296447754</v>
+        <v>8.20127201080322</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G264" t="n">
-        <v>8.11014652252197</v>
+        <v>8.11014556884766</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>8.79500007629395</v>
       </c>
       <c r="G265" t="n">
-        <v>8.01446628570557</v>
+        <v>8.01446533203125</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>8.74499988555908</v>
       </c>
       <c r="G266" t="n">
-        <v>7.96890211105347</v>
+        <v>7.96890258789062</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G267" t="n">
-        <v>8.1557092666626</v>
+        <v>8.15571117401123</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>9.16499996185303</v>
       </c>
       <c r="G269" t="n">
-        <v>8.35162925720215</v>
+        <v>8.35162830352783</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>9.25</v>
       </c>
       <c r="G273" t="n">
-        <v>8.42908477783203</v>
+        <v>8.42908668518066</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G276" t="n">
-        <v>8.51109886169434</v>
+        <v>8.51109790802002</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G278" t="n">
-        <v>8.53843688964844</v>
+        <v>8.5384349822998</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G279" t="n">
-        <v>8.52932357788086</v>
+        <v>8.52932262420654</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G280" t="n">
-        <v>8.83003711700439</v>
+        <v>8.83003520965576</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G281" t="n">
-        <v>8.70246124267578</v>
+        <v>8.7024621963501</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G282" t="n">
-        <v>8.91204833984375</v>
+        <v>8.91204738616943</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G283" t="n">
-        <v>8.72979831695557</v>
+        <v>8.72979927062988</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G285" t="n">
-        <v>9.02139854431152</v>
+        <v>9.02139949798584</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>9.97500038146973</v>
       </c>
       <c r="G286" t="n">
-        <v>9.08974361419678</v>
+        <v>9.08974266052246</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G287" t="n">
-        <v>9.1580867767334</v>
+        <v>9.15808773040771</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>10.1300001144409</v>
       </c>
       <c r="G293" t="n">
-        <v>9.23098850250244</v>
+        <v>9.23098754882812</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G294" t="n">
-        <v>9.1854248046875</v>
+        <v>9.18542385101318</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>9.73499965667725</v>
       </c>
       <c r="G296" t="n">
-        <v>8.87104320526123</v>
+        <v>8.87104225158691</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G297" t="n">
-        <v>8.86648750305176</v>
+        <v>8.86648654937744</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>10.1099996566772</v>
       </c>
       <c r="G299" t="n">
-        <v>9.2127628326416</v>
+        <v>9.21276187896729</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G300" t="n">
-        <v>9.5499267578125</v>
+        <v>9.54992580413818</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G301" t="n">
-        <v>9.69572734832764</v>
+        <v>9.69572639465332</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>10.5900001525879</v>
       </c>
       <c r="G304" t="n">
-        <v>9.65016269683838</v>
+        <v>9.6501636505127</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G305" t="n">
-        <v>9.38590145111084</v>
+        <v>9.38590049743652</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>10.3699998855591</v>
       </c>
       <c r="G306" t="n">
-        <v>9.44968891143799</v>
+        <v>9.44968795776367</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G307" t="n">
-        <v>9.45880126953125</v>
+        <v>9.45880031585693</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>10.710000038147</v>
       </c>
       <c r="G310" t="n">
-        <v>9.75951290130615</v>
+        <v>9.75951385498047</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>10.6899995803833</v>
       </c>
       <c r="G311" t="n">
-        <v>9.74128913879395</v>
+        <v>9.74129009246826</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G312" t="n">
-        <v>9.91442775726318</v>
+        <v>9.91442584991455</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G313" t="n">
-        <v>9.96910095214844</v>
+        <v>9.96910285949707</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G315" t="n">
-        <v>10.1513519287109</v>
+        <v>10.1513528823853</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>11.0699996948242</v>
       </c>
       <c r="G317" t="n">
-        <v>10.0875654220581</v>
+        <v>10.0875644683838</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G318" t="n">
-        <v>10.0602283477783</v>
+        <v>10.0602293014526</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>11.2299995422363</v>
       </c>
       <c r="G320" t="n">
-        <v>10.2333650588989</v>
+        <v>10.2333660125732</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G321" t="n">
-        <v>10.2242517471313</v>
+        <v>10.2242527008057</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G323" t="n">
-        <v>10.5249671936035</v>
+        <v>10.5249681472778</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G326" t="n">
-        <v>10.3700523376465</v>
+        <v>10.3700542449951</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>11.3699998855591</v>
       </c>
       <c r="G327" t="n">
-        <v>10.3609409332275</v>
+        <v>10.3609399795532</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>11.3699998855591</v>
       </c>
       <c r="G328" t="n">
-        <v>10.3609409332275</v>
+        <v>10.3609399795532</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G329" t="n">
-        <v>10.3427152633667</v>
+        <v>10.342716217041</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G330" t="n">
-        <v>10.4247283935547</v>
+        <v>10.4247274398804</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G331" t="n">
-        <v>10.3700523376465</v>
+        <v>10.3700542449951</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G332" t="n">
-        <v>10.6069784164429</v>
+        <v>10.6069793701172</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G334" t="n">
-        <v>10.6434297561646</v>
+        <v>10.6434288024902</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>11.75</v>
       </c>
       <c r="G335" t="n">
-        <v>10.7072162628174</v>
+        <v>10.7072172164917</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G339" t="n">
-        <v>10.953254699707</v>
+        <v>10.9532556533813</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>11.710000038147</v>
       </c>
       <c r="G340" t="n">
-        <v>10.6707668304443</v>
+        <v>10.67076587677</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G342" t="n">
-        <v>10.8712425231934</v>
+        <v>10.8712434768677</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>11.75</v>
       </c>
       <c r="G345" t="n">
-        <v>10.7072162628174</v>
+        <v>10.7072172164917</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G348" t="n">
-        <v>10.953254699707</v>
+        <v>10.9532556533813</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G349" t="n">
-        <v>10.9805927276611</v>
+        <v>10.9805917739868</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G350" t="n">
-        <v>10.9805927276611</v>
+        <v>10.9805917739868</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>12.210000038147</v>
       </c>
       <c r="G351" t="n">
-        <v>11.126392364502</v>
+        <v>11.1263914108276</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G354" t="n">
-        <v>11.1537294387817</v>
+        <v>11.1537303924561</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>12.6899995803833</v>
       </c>
       <c r="G358" t="n">
-        <v>11.6303052902222</v>
+        <v>11.6303081512451</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>12.6899995803833</v>
       </c>
       <c r="G359" t="n">
-        <v>11.6303052902222</v>
+        <v>11.6303081512451</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G361" t="n">
-        <v>11.6119785308838</v>
+        <v>11.6119775772095</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G362" t="n">
-        <v>11.6211433410645</v>
+        <v>11.6211423873901</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>12.710000038147</v>
       </c>
       <c r="G363" t="n">
-        <v>11.6486368179321</v>
+        <v>11.6486358642578</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G365" t="n">
-        <v>11.7769460678101</v>
+        <v>11.7769470214844</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>12.7700004577637</v>
       </c>
       <c r="G366" t="n">
-        <v>11.7036256790161</v>
+        <v>11.7036266326904</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>12.9700002670288</v>
       </c>
       <c r="G367" t="n">
-        <v>11.886923789978</v>
+        <v>11.8869256973267</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G368" t="n">
-        <v>11.859429359436</v>
+        <v>11.8594303131104</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G371" t="n">
-        <v>11.8227691650391</v>
+        <v>11.8227701187134</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G375" t="n">
-        <v>11.4195137023926</v>
+        <v>11.4195127487183</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G377" t="n">
-        <v>11.4470071792603</v>
+        <v>11.4470090866089</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G378" t="n">
-        <v>11.3186979293823</v>
+        <v>11.3186988830566</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>12.289999961853</v>
       </c>
       <c r="G379" t="n">
-        <v>11.2637100219727</v>
+        <v>11.263710975647</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G380" t="n">
-        <v>11.2178840637207</v>
+        <v>11.217885017395</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G381" t="n">
-        <v>11.1628952026367</v>
+        <v>11.162896156311</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G382" t="n">
-        <v>11.0712451934814</v>
+        <v>11.0712461471558</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>11.5600004196167</v>
       </c>
       <c r="G384" t="n">
-        <v>10.594669342041</v>
+        <v>10.5946683883667</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G385" t="n">
-        <v>10.4113702774048</v>
+        <v>10.4113683700562</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G386" t="n">
-        <v>10.2830591201782</v>
+        <v>10.2830610275269</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G388" t="n">
-        <v>10.4571933746338</v>
+        <v>10.4571943283081</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G389" t="n">
-        <v>10.6221647262573</v>
+        <v>10.622163772583</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G390" t="n">
-        <v>10.612998008728</v>
+        <v>10.6129989624023</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>11.6300001144409</v>
       </c>
       <c r="G391" t="n">
-        <v>10.6588249206543</v>
+        <v>10.6588230133057</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>11.8299999237061</v>
       </c>
       <c r="G392" t="n">
-        <v>10.8421211242676</v>
+        <v>10.8421220779419</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G394" t="n">
-        <v>11.0529165267944</v>
+        <v>11.0529155731201</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G399" t="n">
-        <v>11.1079063415527</v>
+        <v>11.1079053878784</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G405" t="n">
-        <v>11.1262340545654</v>
+        <v>11.1262359619141</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G406" t="n">
-        <v>11.0345859527588</v>
+        <v>11.0345869064331</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G410" t="n">
-        <v>10.8146286010742</v>
+        <v>10.8146276473999</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G411" t="n">
-        <v>10.8146286010742</v>
+        <v>10.8146276473999</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G413" t="n">
-        <v>10.6313276290894</v>
+        <v>10.6313285827637</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>11.3299999237061</v>
       </c>
       <c r="G414" t="n">
-        <v>10.3838739395142</v>
+        <v>10.3838748931885</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G416" t="n">
-        <v>10.5030193328857</v>
+        <v>10.5030183792114</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G420" t="n">
-        <v>10.8329572677612</v>
+        <v>10.8329563140869</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>12.0299997329712</v>
       </c>
       <c r="G422" t="n">
-        <v>11.0254192352295</v>
+        <v>11.0254211425781</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G423" t="n">
-        <v>10.9429368972778</v>
+        <v>10.9429359436035</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>11.8699998855591</v>
       </c>
       <c r="G426" t="n">
-        <v>10.8787822723389</v>
+        <v>10.8787803649902</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G427" t="n">
-        <v>11.1354007720947</v>
+        <v>11.1353998184204</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G429" t="n">
-        <v>11.1628952026367</v>
+        <v>11.162896156311</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G430" t="n">
-        <v>11.4470071792603</v>
+        <v>11.4470090866089</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>12.6899995803833</v>
       </c>
       <c r="G432" t="n">
-        <v>11.6303052902222</v>
+        <v>11.6303081512451</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>12.789999961853</v>
       </c>
       <c r="G438" t="n">
-        <v>11.7219562530518</v>
+        <v>11.7219572067261</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G439" t="n">
-        <v>11.7586164474487</v>
+        <v>11.7586154937744</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>12.5699996948242</v>
       </c>
       <c r="G441" t="n">
-        <v>11.5203275680542</v>
+        <v>11.5203266143799</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G443" t="n">
-        <v>11.7586164474487</v>
+        <v>11.7586154937744</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G445" t="n">
-        <v>11.8960905075073</v>
+        <v>11.896089553833</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>12.9099998474121</v>
       </c>
       <c r="G446" t="n">
-        <v>11.8319358825684</v>
+        <v>11.8319339752197</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G447" t="n">
-        <v>11.8960905075073</v>
+        <v>11.896089553833</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G448" t="n">
-        <v>11.786111831665</v>
+        <v>11.7861099243164</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G449" t="n">
-        <v>12.1527080535889</v>
+        <v>12.1527070999146</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>13.4300003051758</v>
       </c>
       <c r="G451" t="n">
-        <v>12.3085126876831</v>
+        <v>12.3085117340088</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G452" t="n">
-        <v>12.4459857940674</v>
+        <v>12.4459867477417</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>13.6099996566772</v>
       </c>
       <c r="G453" t="n">
-        <v>12.4734811782837</v>
+        <v>12.4734802246094</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>13.6300001144409</v>
       </c>
       <c r="G454" t="n">
-        <v>12.4918117523193</v>
+        <v>12.491810798645</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>13.6300001144409</v>
       </c>
       <c r="G455" t="n">
-        <v>12.4918117523193</v>
+        <v>12.491810798645</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G456" t="n">
-        <v>12.4643154144287</v>
+        <v>12.4643182754517</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G457" t="n">
-        <v>11.8227691650391</v>
+        <v>11.8227701187134</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G458" t="n">
-        <v>11.8685960769653</v>
+        <v>11.868595123291</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G460" t="n">
-        <v>11.786111831665</v>
+        <v>11.7861099243164</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G461" t="n">
-        <v>11.7769460678101</v>
+        <v>11.7769470214844</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G462" t="n">
-        <v>11.4745035171509</v>
+        <v>11.4745025634766</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G463" t="n">
-        <v>11.4195137023926</v>
+        <v>11.4195127487183</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G465" t="n">
-        <v>11.5386571884155</v>
+        <v>11.5386581420898</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G466" t="n">
-        <v>11.4195137023926</v>
+        <v>11.4195127487183</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G467" t="n">
-        <v>11.7127914428711</v>
+        <v>11.7127904891968</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G468" t="n">
-        <v>11.8502674102783</v>
+        <v>11.850266456604</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G469" t="n">
-        <v>11.8960905075073</v>
+        <v>11.896089553833</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G470" t="n">
-        <v>11.9510793685913</v>
+        <v>11.9510803222656</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G471" t="n">
-        <v>11.7586164474487</v>
+        <v>11.7586154937744</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G472" t="n">
-        <v>11.5844821929932</v>
+        <v>11.5844831466675</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G473" t="n">
-        <v>11.6119785308838</v>
+        <v>11.6119775772095</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G474" t="n">
-        <v>11.6119785308838</v>
+        <v>11.6119775772095</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G477" t="n">
-        <v>11.4470071792603</v>
+        <v>11.4470090866089</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G478" t="n">
-        <v>11.1445636749268</v>
+        <v>11.1445655822754</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G480" t="n">
-        <v>11.2545442581177</v>
+        <v>11.254545211792</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G482" t="n">
-        <v>11.3645238876343</v>
+        <v>11.36452293396</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>12.5100002288818</v>
       </c>
       <c r="G484" t="n">
-        <v>11.4653387069702</v>
+        <v>11.4653367996216</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G485" t="n">
-        <v>11.7677793502808</v>
+        <v>11.7677822113037</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G488" t="n">
-        <v>11.877760887146</v>
+        <v>11.8777599334717</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G489" t="n">
-        <v>11.8227691650391</v>
+        <v>11.8227701187134</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G490" t="n">
-        <v>11.8227691650391</v>
+        <v>11.8227701187134</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G491" t="n">
-        <v>11.8136053085327</v>
+        <v>11.813606262207</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>12.9099998474121</v>
       </c>
       <c r="G493" t="n">
-        <v>11.8319358825684</v>
+        <v>11.8319339752197</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G494" t="n">
-        <v>11.859429359436</v>
+        <v>11.8594303131104</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>12.9099998474121</v>
       </c>
       <c r="G495" t="n">
-        <v>11.8319358825684</v>
+        <v>11.8319339752197</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G497" t="n">
-        <v>11.7769460678101</v>
+        <v>11.7769470214844</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G498" t="n">
-        <v>12.0060701370239</v>
+        <v>12.0060691833496</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G500" t="n">
-        <v>11.8502674102783</v>
+        <v>11.850266456604</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G501" t="n">
-        <v>11.8410997390747</v>
+        <v>11.8411016464233</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>12.5100002288818</v>
       </c>
       <c r="G502" t="n">
-        <v>11.4653387069702</v>
+        <v>11.4653367996216</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G504" t="n">
-        <v>11.7127914428711</v>
+        <v>11.7127904891968</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G509" t="n">
-        <v>12.1527080535889</v>
+        <v>12.1527070999146</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G510" t="n">
-        <v>12.0060701370239</v>
+        <v>12.0060691833496</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G511" t="n">
-        <v>11.7677793502808</v>
+        <v>11.7677822113037</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G512" t="n">
-        <v>11.8410997390747</v>
+        <v>11.8411016464233</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>12.9700002670288</v>
       </c>
       <c r="G513" t="n">
-        <v>11.886923789978</v>
+        <v>11.8869256973267</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G514" t="n">
-        <v>12.2076969146729</v>
+        <v>12.2076978683472</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>13.3299999237061</v>
       </c>
       <c r="G515" t="n">
-        <v>12.2168607711792</v>
+        <v>12.2168626785278</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G516" t="n">
-        <v>12.1710367202759</v>
+        <v>12.1710376739502</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G517" t="n">
-        <v>12.2993478775024</v>
+        <v>12.2993459701538</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G518" t="n">
-        <v>12.4643154144287</v>
+        <v>12.4643182754517</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G519" t="n">
-        <v>12.7850904464722</v>
+        <v>12.7850894927979</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G521" t="n">
-        <v>12.7850904464722</v>
+        <v>12.7850894927979</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G523" t="n">
-        <v>12.6109561920166</v>
+        <v>12.6109552383423</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G524" t="n">
-        <v>12.7850904464722</v>
+        <v>12.7850894927979</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G528" t="n">
-        <v>13.1791830062866</v>
+        <v>13.179181098938</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G529" t="n">
-        <v>13.1975107192993</v>
+        <v>13.1975116729736</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>14.3100004196167</v>
       </c>
       <c r="G533" t="n">
-        <v>13.1150274276733</v>
+        <v>13.1150283813477</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>14.1300001144409</v>
       </c>
       <c r="G534" t="n">
-        <v>12.9500570297241</v>
+        <v>12.9500579833984</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G536" t="n">
-        <v>12.2810163497925</v>
+        <v>12.2810182571411</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G537" t="n">
-        <v>12.0793886184692</v>
+        <v>12.0793895721436</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G538" t="n">
-        <v>12.2810163497925</v>
+        <v>12.2810182571411</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G539" t="n">
-        <v>11.8502674102783</v>
+        <v>11.850266456604</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G540" t="n">
-        <v>11.786111831665</v>
+        <v>11.7861099243164</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G541" t="n">
-        <v>12.0518922805786</v>
+        <v>12.0518941879272</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G542" t="n">
-        <v>12.1343793869019</v>
+        <v>12.1343784332275</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>13.6800003051758</v>
       </c>
       <c r="G545" t="n">
-        <v>12.537636756897</v>
+        <v>12.5376358032227</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G546" t="n">
-        <v>12.5101404190063</v>
+        <v>12.5101413726807</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G547" t="n">
-        <v>12.2626895904541</v>
+        <v>12.2626867294312</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G548" t="n">
-        <v>12.2993478775024</v>
+        <v>12.2993459701538</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G549" t="n">
-        <v>12.1343793869019</v>
+        <v>12.1343784332275</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>12.9700002670288</v>
       </c>
       <c r="G550" t="n">
-        <v>11.886923789978</v>
+        <v>11.8869256973267</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>12.9700002670288</v>
       </c>
       <c r="G552" t="n">
-        <v>11.886923789978</v>
+        <v>11.8869256973267</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G553" t="n">
-        <v>11.960244178772</v>
+        <v>11.9602451324463</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G555" t="n">
-        <v>12.0793886184692</v>
+        <v>12.0793895721436</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G556" t="n">
-        <v>11.960244178772</v>
+        <v>11.9602451324463</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G558" t="n">
-        <v>12.6934385299683</v>
+        <v>12.6934413909912</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>13.9099998474121</v>
       </c>
       <c r="G559" t="n">
-        <v>12.7484292984009</v>
+        <v>12.7484273910522</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>14.0900001525879</v>
       </c>
       <c r="G560" t="n">
-        <v>12.9133977890015</v>
+        <v>12.9133987426758</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>14.1599998474121</v>
       </c>
       <c r="G562" t="n">
-        <v>12.9775514602661</v>
+        <v>12.9775533676147</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G563" t="n">
-        <v>12.9683876037598</v>
+        <v>12.9683885574341</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G564" t="n">
-        <v>12.9683876037598</v>
+        <v>12.9683885574341</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G565" t="n">
-        <v>12.8125839233398</v>
+        <v>12.8125829696655</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>14.0900001525879</v>
       </c>
       <c r="G566" t="n">
-        <v>12.9133977890015</v>
+        <v>12.9133987426758</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>14.1700000762939</v>
       </c>
       <c r="G567" t="n">
-        <v>12.9867181777954</v>
+        <v>12.9867172241211</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>14.0699996948242</v>
       </c>
       <c r="G568" t="n">
-        <v>12.8950691223145</v>
+        <v>12.8950672149658</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>13.6899995803833</v>
       </c>
       <c r="G570" t="n">
-        <v>12.5468015670776</v>
+        <v>12.5468006134033</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G572" t="n">
-        <v>12.9408941268921</v>
+        <v>12.9408922195435</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>14.4099998474121</v>
       </c>
       <c r="G573" t="n">
-        <v>13.2066745758057</v>
+        <v>13.2066764831543</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>14.4899997711182</v>
       </c>
       <c r="G575" t="n">
-        <v>13.2799959182739</v>
+        <v>13.2799949645996</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G579" t="n">
-        <v>13.7657384872437</v>
+        <v>13.7657375335693</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G581" t="n">
-        <v>13.9215421676636</v>
+        <v>13.9215412139893</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>15.4700002670288</v>
       </c>
       <c r="G582" t="n">
-        <v>14.1781597137451</v>
+        <v>14.1781606674194</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G584" t="n">
-        <v>14.2973031997681</v>
+        <v>14.2973041534424</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G585" t="n">
-        <v>14.517261505127</v>
+        <v>14.5172624588013</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G586" t="n">
-        <v>14.462272644043</v>
+        <v>14.4622716903687</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G587" t="n">
-        <v>14.7097263336182</v>
+        <v>14.7097253799438</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>15.9300003051758</v>
       </c>
       <c r="G589" t="n">
-        <v>14.5997476577759</v>
+        <v>14.5997467041016</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G592" t="n">
-        <v>14.4989328384399</v>
+        <v>14.4989318847656</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>15.5</v>
       </c>
       <c r="G594" t="n">
-        <v>14.2056541442871</v>
+        <v>14.2056550979614</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>15.9300003051758</v>
       </c>
       <c r="G595" t="n">
-        <v>14.5997476577759</v>
+        <v>14.5997467041016</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>16.1900005340576</v>
       </c>
       <c r="G598" t="n">
-        <v>14.8380365371704</v>
+        <v>14.8380346298218</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G602" t="n">
-        <v>15.140477180481</v>
+        <v>15.1404781341553</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>16.6299991607666</v>
       </c>
       <c r="G603" t="n">
-        <v>15.2412900924683</v>
+        <v>15.2412919998169</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G604" t="n">
-        <v>15.012167930603</v>
+        <v>15.0121688842773</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G605" t="n">
-        <v>14.6180763244629</v>
+        <v>14.6180772781372</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G607" t="n">
-        <v>14.462272644043</v>
+        <v>14.4622716903687</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>15.4700002670288</v>
       </c>
       <c r="G609" t="n">
-        <v>14.2776870727539</v>
+        <v>14.2776880264282</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>15.1300001144409</v>
       </c>
       <c r="G610" t="n">
-        <v>13.9638929367065</v>
+        <v>13.9638919830322</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G612" t="n">
-        <v>14.3422918319702</v>
+        <v>14.3422908782959</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G615" t="n">
-        <v>14.0192670822144</v>
+        <v>14.01926612854</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>15.4300003051758</v>
       </c>
       <c r="G617" t="n">
-        <v>14.2407712936401</v>
+        <v>14.2407693862915</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G619" t="n">
-        <v>15.0806331634521</v>
+        <v>15.0806322097778</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G621" t="n">
-        <v>16.0220222473145</v>
+        <v>16.0220184326172</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G622" t="n">
-        <v>15.7266836166382</v>
+        <v>15.7266845703125</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G623" t="n">
-        <v>15.7359104156494</v>
+        <v>15.7359113693237</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>17.0900001525879</v>
       </c>
       <c r="G624" t="n">
-        <v>15.7728300094604</v>
+        <v>15.7728290557861</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G626" t="n">
-        <v>15.7820587158203</v>
+        <v>15.7820606231689</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G627" t="n">
-        <v>15.8928108215332</v>
+        <v>15.8928079605103</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G628" t="n">
-        <v>15.6805372238159</v>
+        <v>15.6805362701416</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G629" t="n">
-        <v>15.6436185836792</v>
+        <v>15.6436214447021</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G631" t="n">
-        <v>16.2804393768311</v>
+        <v>16.2804412841797</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G632" t="n">
-        <v>16.2250652313232</v>
+        <v>16.2250633239746</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G635" t="n">
-        <v>15.8282041549683</v>
+        <v>15.8282051086426</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G637" t="n">
-        <v>16.3911895751953</v>
+        <v>16.3911914825439</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>17.8099994659424</v>
       </c>
       <c r="G638" t="n">
-        <v>16.4373378753662</v>
+        <v>16.4373397827148</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G639" t="n">
-        <v>16.5942363739014</v>
+        <v>16.5942344665527</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G640" t="n">
-        <v>16.4742546081543</v>
+        <v>16.4742527008057</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G641" t="n">
-        <v>16.326587677002</v>
+        <v>16.3265857696533</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G642" t="n">
-        <v>16.326587677002</v>
+        <v>16.3265857696533</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G645" t="n">
-        <v>15.6805372238159</v>
+        <v>15.6805362701416</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>17.1100006103516</v>
       </c>
       <c r="G648" t="n">
-        <v>15.7912874221802</v>
+        <v>15.7912902832031</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G649" t="n">
-        <v>15.9666433334351</v>
+        <v>15.9666442871094</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G650" t="n">
-        <v>16.1143112182617</v>
+        <v>16.1143093109131</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G651" t="n">
-        <v>15.9297294616699</v>
+        <v>15.9297256469727</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G654" t="n">
-        <v>16.6496124267578</v>
+        <v>16.6496105194092</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>18.5</v>
       </c>
       <c r="G655" t="n">
-        <v>17.0741558074951</v>
+        <v>17.0741577148438</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>18.9300003051758</v>
       </c>
       <c r="G656" t="n">
-        <v>17.4710159301758</v>
+        <v>17.4710178375244</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G657" t="n">
-        <v>16.9818630218506</v>
+        <v>16.9818668365479</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>19.1599998474121</v>
       </c>
       <c r="G659" t="n">
-        <v>17.6832866668701</v>
+        <v>17.6832885742188</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>19.7399997711182</v>
       </c>
       <c r="G660" t="n">
-        <v>18.2185859680176</v>
+        <v>18.2185878753662</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>19.4200000762939</v>
       </c>
       <c r="G662" t="n">
-        <v>17.9232501983643</v>
+        <v>17.9232521057129</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>19.25</v>
       </c>
       <c r="G663" t="n">
-        <v>17.7663516998291</v>
+        <v>17.7663536071777</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G665" t="n">
-        <v>17.3879528045654</v>
+        <v>17.3879508972168</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G666" t="n">
-        <v>17.1664505004883</v>
+        <v>17.1664524078369</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>19.3799991607666</v>
       </c>
       <c r="G670" t="n">
-        <v>17.8863334655762</v>
+        <v>17.8863296508789</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G672" t="n">
-        <v>17.7202053070068</v>
+        <v>17.7202091217041</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G673" t="n">
-        <v>17.5540790557861</v>
+        <v>17.5540809631348</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G674" t="n">
-        <v>17.6279163360596</v>
+        <v>17.6279144287109</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G676" t="n">
-        <v>17.5817680358887</v>
+        <v>17.5817642211914</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>18.9200000762939</v>
       </c>
       <c r="G678" t="n">
-        <v>17.461784362793</v>
+        <v>17.4617900848389</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G679" t="n">
-        <v>17.5540790557861</v>
+        <v>17.5540809631348</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>18.9899997711182</v>
       </c>
       <c r="G680" t="n">
-        <v>17.526388168335</v>
+        <v>17.5263919830322</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>18.5400009155273</v>
       </c>
       <c r="G681" t="n">
-        <v>17.1110725402832</v>
+        <v>17.1110744476318</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G683" t="n">
-        <v>17.9047908782959</v>
+        <v>17.9047927856445</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>18.8099994659424</v>
       </c>
       <c r="G684" t="n">
-        <v>17.3602657318115</v>
+        <v>17.3602638244629</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>19.7700004577637</v>
       </c>
       <c r="G688" t="n">
-        <v>18.2462768554688</v>
+        <v>18.2462749481201</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G689" t="n">
-        <v>18.8277187347412</v>
+        <v>18.8277168273926</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>20.4400005340576</v>
       </c>
       <c r="G691" t="n">
-        <v>18.8646354675293</v>
+        <v>18.8646373748779</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G692" t="n">
-        <v>18.6800518035889</v>
+        <v>18.6800498962402</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G693" t="n">
-        <v>18.5508403778076</v>
+        <v>18.5508422851562</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>19.4200000762939</v>
       </c>
       <c r="G695" t="n">
-        <v>17.9232501983643</v>
+        <v>17.9232521057129</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>19.4599990844727</v>
       </c>
       <c r="G696" t="n">
-        <v>17.960168838501</v>
+        <v>17.9601650238037</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>19.5400009155273</v>
       </c>
       <c r="G697" t="n">
-        <v>18.0340003967285</v>
+        <v>18.0340023040771</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G698" t="n">
-        <v>18.2739601135254</v>
+        <v>18.273962020874</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>19.7099990844727</v>
       </c>
       <c r="G700" t="n">
-        <v>18.1908988952637</v>
+        <v>18.1909008026123</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>19.1399993896484</v>
       </c>
       <c r="G701" t="n">
-        <v>17.6648330688477</v>
+        <v>17.6648292541504</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>19.0300006866455</v>
       </c>
       <c r="G703" t="n">
-        <v>17.5633106231689</v>
+        <v>17.5633087158203</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>18.9899997711182</v>
       </c>
       <c r="G704" t="n">
-        <v>17.526388168335</v>
+        <v>17.5263919830322</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G706" t="n">
-        <v>16.3911895751953</v>
+        <v>16.3911914825439</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G708" t="n">
-        <v>15.6436185836792</v>
+        <v>15.6436214447021</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>16.5300006866455</v>
       </c>
       <c r="G711" t="n">
-        <v>15.2559909820557</v>
+        <v>15.2559900283813</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>16.3099994659424</v>
       </c>
       <c r="G714" t="n">
-        <v>15.0529460906982</v>
+        <v>15.0529451370239</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>16.6700000762939</v>
       </c>
       <c r="G716" t="n">
-        <v>15.3852014541626</v>
+        <v>15.3852005004883</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>16.5900001525879</v>
       </c>
       <c r="G717" t="n">
-        <v>15.3113651275635</v>
+        <v>15.3113660812378</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>15.7700004577637</v>
       </c>
       <c r="G718" t="n">
-        <v>14.5545654296875</v>
+        <v>14.5545663833618</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G720" t="n">
-        <v>14.6007127761841</v>
+        <v>14.6007108688354</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G721" t="n">
-        <v>14.5822534561157</v>
+        <v>14.58225440979</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G723" t="n">
-        <v>14.6191701889038</v>
+        <v>14.6191692352295</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G724" t="n">
-        <v>14.4530420303345</v>
+        <v>14.4530429840088</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G725" t="n">
-        <v>14.268458366394</v>
+        <v>14.2684574127197</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>15.5100002288818</v>
       </c>
       <c r="G726" t="n">
-        <v>14.3146057128906</v>
+        <v>14.3146047592163</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G727" t="n">
-        <v>14.2869167327881</v>
+        <v>14.2869157791138</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>15.75</v>
       </c>
       <c r="G729" t="n">
-        <v>14.5361080169678</v>
+        <v>14.5361070632935</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G730" t="n">
-        <v>14.6560878753662</v>
+        <v>14.6560888290405</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G732" t="n">
-        <v>14.3976669311523</v>
+        <v>14.3976678848267</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>15.75</v>
       </c>
       <c r="G733" t="n">
-        <v>14.5361080169678</v>
+        <v>14.5361070632935</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G736" t="n">
-        <v>13.3639879226685</v>
+        <v>13.3639888763428</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G737" t="n">
-        <v>12.782543182373</v>
+        <v>12.782546043396</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G738" t="n">
-        <v>12.7363977432251</v>
+        <v>12.7363986968994</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G739" t="n">
-        <v>13.0317354202271</v>
+        <v>13.0317344665527</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>14.1300001144409</v>
       </c>
       <c r="G741" t="n">
-        <v>13.0409641265869</v>
+        <v>13.0409650802612</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G742" t="n">
-        <v>13.290153503418</v>
+        <v>13.2901544570923</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>14.2299995422363</v>
       </c>
       <c r="G743" t="n">
-        <v>13.1332559585571</v>
+        <v>13.1332569122314</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G746" t="n">
-        <v>13.6408672332764</v>
+        <v>13.6408662796021</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>15.289999961853</v>
       </c>
       <c r="G747" t="n">
-        <v>14.1115589141846</v>
+        <v>14.1115598678589</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>15</v>
       </c>
       <c r="G748" t="n">
-        <v>13.8439102172852</v>
+        <v>13.8439121246338</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>14.9399995803833</v>
       </c>
       <c r="G749" t="n">
-        <v>13.7885360717773</v>
+        <v>13.7885341644287</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>15.0900001525879</v>
       </c>
       <c r="G750" t="n">
-        <v>13.9269752502441</v>
+        <v>13.9269742965698</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G755" t="n">
-        <v>13.2347793579102</v>
+        <v>13.2347784042358</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>14.5100002288818</v>
       </c>
       <c r="G756" t="n">
-        <v>13.3916759490967</v>
+        <v>13.3916778564453</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G757" t="n">
-        <v>13.5301160812378</v>
+        <v>13.5301151275635</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>14.710000038147</v>
       </c>
       <c r="G758" t="n">
-        <v>13.5762624740601</v>
+        <v>13.5762615203857</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>15.210000038147</v>
       </c>
       <c r="G759" t="n">
-        <v>14.0377244949341</v>
+        <v>14.0377254486084</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>14.5299997329712</v>
       </c>
       <c r="G760" t="n">
-        <v>13.4101343154907</v>
+        <v>13.410135269165</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G762" t="n">
-        <v>12.782543182373</v>
+        <v>12.782546043396</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>13.9099998474121</v>
       </c>
       <c r="G764" t="n">
-        <v>12.8379201889038</v>
+        <v>12.8379182815552</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>14.5</v>
       </c>
       <c r="G765" t="n">
-        <v>13.3824481964111</v>
+        <v>13.3824472427368</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G766" t="n">
-        <v>13.290153503418</v>
+        <v>13.2901544570923</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>16.0900001525879</v>
       </c>
       <c r="G769" t="n">
-        <v>14.8499021530151</v>
+        <v>14.8499011993408</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G770" t="n">
-        <v>14.4899606704712</v>
+        <v>14.4899597167969</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>15.7700004577637</v>
       </c>
       <c r="G771" t="n">
-        <v>14.5545654296875</v>
+        <v>14.5545663833618</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>15.9099998474121</v>
       </c>
       <c r="G772" t="n">
-        <v>14.6837739944458</v>
+        <v>14.6837749481201</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>15.9099998474121</v>
       </c>
       <c r="G774" t="n">
-        <v>14.6837739944458</v>
+        <v>14.6837749481201</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G775" t="n">
-        <v>14.7483797073364</v>
+        <v>14.7483806610107</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G777" t="n">
-        <v>14.9514255523682</v>
+        <v>14.9514265060425</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>16.1299991607666</v>
       </c>
       <c r="G778" t="n">
-        <v>14.8868188858032</v>
+        <v>14.8868198394775</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>15.75</v>
       </c>
       <c r="G782" t="n">
-        <v>14.5361080169678</v>
+        <v>14.5361070632935</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>15.75</v>
       </c>
       <c r="G783" t="n">
-        <v>14.5361080169678</v>
+        <v>14.5361070632935</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G784" t="n">
-        <v>14.5268774032593</v>
+        <v>14.5268754959106</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G785" t="n">
-        <v>14.4345846176147</v>
+        <v>14.4345855712891</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G787" t="n">
-        <v>14.545334815979</v>
+        <v>14.5453367233276</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>16.4699993133545</v>
       </c>
       <c r="G788" t="n">
-        <v>15.2006130218506</v>
+        <v>15.2006149291992</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>15.8900003433228</v>
       </c>
       <c r="G790" t="n">
-        <v>14.6653175354004</v>
+        <v>14.6653156280518</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G791" t="n">
-        <v>14.8129844665527</v>
+        <v>14.8129835128784</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>16.3099994659424</v>
       </c>
       <c r="G793" t="n">
-        <v>15.0529460906982</v>
+        <v>15.0529451370239</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G794" t="n">
-        <v>15.0252590179443</v>
+        <v>15.025260925293</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G795" t="n">
-        <v>14.9883403778076</v>
+        <v>14.9883394241333</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G796" t="n">
-        <v>15.0806331634521</v>
+        <v>15.0806322097778</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G797" t="n">
-        <v>14.9514255523682</v>
+        <v>14.9514265060425</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>15.5900001525879</v>
       </c>
       <c r="G798" t="n">
-        <v>14.3884382247925</v>
+        <v>14.3884372711182</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G799" t="n">
-        <v>14.5084180831909</v>
+        <v>14.5084199905396</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G800" t="n">
-        <v>14.8222150802612</v>
+        <v>14.8222141265869</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>16.0300006866455</v>
       </c>
       <c r="G801" t="n">
-        <v>14.794527053833</v>
+        <v>14.7945289611816</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>16.2900009155273</v>
       </c>
       <c r="G803" t="n">
-        <v>15.0344886779785</v>
+        <v>15.0344877243042</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>16.2099990844727</v>
       </c>
       <c r="G804" t="n">
-        <v>14.9606513977051</v>
+        <v>14.9606523513794</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G808" t="n">
-        <v>15.5420980453491</v>
+        <v>15.5420999526978</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G809" t="n">
-        <v>14.9883403778076</v>
+        <v>14.9883394241333</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>16.2099990844727</v>
       </c>
       <c r="G811" t="n">
-        <v>14.9606513977051</v>
+        <v>14.9606523513794</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G812" t="n">
-        <v>15.0252590179443</v>
+        <v>15.025260925293</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G814" t="n">
-        <v>15.3667421340942</v>
+        <v>15.3667402267456</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G815" t="n">
-        <v>15.9666433334351</v>
+        <v>15.9666442871094</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G816" t="n">
-        <v>16.2435207366943</v>
+        <v>16.2435245513916</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G817" t="n">
-        <v>16.2435207366943</v>
+        <v>16.2435245513916</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G818" t="n">
-        <v>16.2435207366943</v>
+        <v>16.2435245513916</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>17.7700004577637</v>
       </c>
       <c r="G819" t="n">
-        <v>16.4004230499268</v>
+        <v>16.4004192352295</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G820" t="n">
-        <v>16.2804393768311</v>
+        <v>16.2804412841797</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G821" t="n">
-        <v>16.2435207366943</v>
+        <v>16.2435245513916</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G822" t="n">
-        <v>16.0589370727539</v>
+        <v>16.0589389801025</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>17.1200008392334</v>
       </c>
       <c r="G825" t="n">
-        <v>15.8005208969116</v>
+        <v>15.8005170822144</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G827" t="n">
-        <v>16.2804393768311</v>
+        <v>16.2804412841797</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>17.8099994659424</v>
       </c>
       <c r="G828" t="n">
-        <v>16.4373378753662</v>
+        <v>16.4373397827148</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G831" t="n">
-        <v>15.9851016998291</v>
+        <v>15.9851036071777</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G832" t="n">
-        <v>16.0589370727539</v>
+        <v>16.0589389801025</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G834" t="n">
-        <v>16.2896690368652</v>
+        <v>16.2896709442139</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G836" t="n">
-        <v>16.2250652313232</v>
+        <v>16.2250633239746</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>17.7700004577637</v>
       </c>
       <c r="G837" t="n">
-        <v>16.4004230499268</v>
+        <v>16.4004192352295</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>17.7900009155273</v>
       </c>
       <c r="G838" t="n">
-        <v>16.4188804626465</v>
+        <v>16.4188785552979</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G839" t="n">
-        <v>15.8189735412598</v>
+        <v>15.8189754486084</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>16.7700004577637</v>
       </c>
       <c r="G840" t="n">
-        <v>15.4774951934814</v>
+        <v>15.4774932861328</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>16.7600002288818</v>
       </c>
       <c r="G841" t="n">
-        <v>15.46826171875</v>
+        <v>15.4682626724243</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G843" t="n">
-        <v>15.4313468933105</v>
+        <v>15.4313449859619</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>17.1200008392334</v>
       </c>
       <c r="G844" t="n">
-        <v>15.8005208969116</v>
+        <v>15.8005170822144</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>17.25</v>
       </c>
       <c r="G845" t="n">
-        <v>15.9204969406128</v>
+        <v>15.9204978942871</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>17.1299991607666</v>
       </c>
       <c r="G846" t="n">
-        <v>15.8097457885742</v>
+        <v>15.8097448348999</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>16.7700004577637</v>
       </c>
       <c r="G847" t="n">
-        <v>15.4774951934814</v>
+        <v>15.4774932861328</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G848" t="n">
-        <v>15.7359104156494</v>
+        <v>15.7359113693237</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>16.7900009155273</v>
       </c>
       <c r="G849" t="n">
-        <v>15.4959516525269</v>
+        <v>15.4959526062012</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G850" t="n">
-        <v>17.037239074707</v>
+        <v>17.0372409820557</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>18.6299991607666</v>
       </c>
       <c r="G851" t="n">
-        <v>17.1941356658936</v>
+        <v>17.1941337585449</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>18.2600002288818</v>
       </c>
       <c r="G853" t="n">
-        <v>16.8526554107666</v>
+        <v>16.852653503418</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>18.9899997711182</v>
       </c>
       <c r="G855" t="n">
-        <v>17.526388168335</v>
+        <v>17.5263919830322</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>19.3799991607666</v>
       </c>
       <c r="G858" t="n">
-        <v>17.8863334655762</v>
+        <v>17.8863296508789</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G859" t="n">
-        <v>18.0815582275391</v>
+        <v>18.0815601348877</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>20.5200004577637</v>
       </c>
       <c r="G861" t="n">
-        <v>19.0762767791748</v>
+        <v>19.0762786865234</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>19.8199996948242</v>
       </c>
       <c r="G863" t="n">
-        <v>18.4255256652832</v>
+        <v>18.4255275726318</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>19.8400001525879</v>
       </c>
       <c r="G864" t="n">
-        <v>18.4441204071045</v>
+        <v>18.4441184997559</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>19.8799991607666</v>
       </c>
       <c r="G865" t="n">
-        <v>18.4813041687012</v>
+        <v>18.4813022613525</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>20.1399993896484</v>
       </c>
       <c r="G870" t="n">
-        <v>18.7230129241943</v>
+        <v>18.7230110168457</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G871" t="n">
-        <v>18.871753692627</v>
+        <v>18.8717555999756</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>20.0200004577637</v>
       </c>
       <c r="G874" t="n">
-        <v>18.6114540100098</v>
+        <v>18.6114559173584</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>20.8400001525879</v>
       </c>
       <c r="G877" t="n">
-        <v>19.3737621307373</v>
+        <v>19.3737640380859</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>21.2199993133545</v>
       </c>
       <c r="G879" t="n">
-        <v>19.7270259857178</v>
+        <v>19.7270240783691</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>21.5599994659424</v>
       </c>
       <c r="G880" t="n">
-        <v>20.0431022644043</v>
+        <v>20.0431041717529</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G884" t="n">
-        <v>19.4295406341553</v>
+        <v>19.4295387268066</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>20.7800006866455</v>
       </c>
       <c r="G885" t="n">
-        <v>19.3179836273193</v>
+        <v>19.317985534668</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G889" t="n">
-        <v>19.1506500244141</v>
+        <v>19.1506481170654</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G890" t="n">
-        <v>19.1506500244141</v>
+        <v>19.1506481170654</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>21.0400009155273</v>
       </c>
       <c r="G891" t="n">
-        <v>19.5596923828125</v>
+        <v>19.5596942901611</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>20.8799991607666</v>
       </c>
       <c r="G892" t="n">
-        <v>19.410945892334</v>
+        <v>19.4109477996826</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>20.5799999237061</v>
       </c>
       <c r="G893" t="n">
-        <v>19.1320552825928</v>
+        <v>19.1320533752441</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>21.2600002288818</v>
       </c>
       <c r="G899" t="n">
-        <v>19.7642116546631</v>
+        <v>19.7642135620117</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>21.2399997711182</v>
       </c>
       <c r="G900" t="n">
-        <v>19.7456207275391</v>
+        <v>19.7456188201904</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>21.6599998474121</v>
       </c>
       <c r="G904" t="n">
-        <v>20.1360683441162</v>
+        <v>20.1360702514648</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>21.0799999237061</v>
       </c>
       <c r="G908" t="n">
-        <v>19.5968780517578</v>
+        <v>19.5968761444092</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>21.0799999237061</v>
       </c>
       <c r="G909" t="n">
-        <v>19.5968780517578</v>
+        <v>19.5968761444092</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>22.2800006866455</v>
       </c>
       <c r="G911" t="n">
-        <v>20.7124481201172</v>
+        <v>20.7124500274658</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>20.9599990844727</v>
       </c>
       <c r="G915" t="n">
-        <v>19.4853210449219</v>
+        <v>19.4853191375732</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>21.5400009155273</v>
       </c>
       <c r="G916" t="n">
-        <v>20.0245132446289</v>
+        <v>20.0245151519775</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G918" t="n">
-        <v>20.5451145172119</v>
+        <v>20.5451126098633</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>22.2600002288818</v>
       </c>
       <c r="G920" t="n">
-        <v>20.6938533782959</v>
+        <v>20.6938571929932</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>23.5400009155273</v>
       </c>
       <c r="G924" t="n">
-        <v>21.8838005065918</v>
+        <v>21.8837985992432</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>23.6200008392334</v>
       </c>
       <c r="G925" t="n">
-        <v>21.9581718444824</v>
+        <v>21.9581699371338</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>23.5799999237061</v>
       </c>
       <c r="G926" t="n">
-        <v>21.9209842681885</v>
+        <v>21.9209861755371</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G928" t="n">
-        <v>21.6606826782227</v>
+        <v>21.6606864929199</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>23.5799999237061</v>
       </c>
       <c r="G929" t="n">
-        <v>21.9209842681885</v>
+        <v>21.9209861755371</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>23</v>
       </c>
       <c r="G930" t="n">
-        <v>21.3817920684814</v>
+        <v>21.3817901611328</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>23.6599998474121</v>
       </c>
       <c r="G933" t="n">
-        <v>21.9953536987305</v>
+        <v>21.9953556060791</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>23.8199996948242</v>
       </c>
       <c r="G934" t="n">
-        <v>22.1440963745117</v>
+        <v>22.1440982818604</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>23.8799991607666</v>
       </c>
       <c r="G935" t="n">
-        <v>22.199878692627</v>
+        <v>22.1998748779297</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G936" t="n">
-        <v>21.4747562408447</v>
+        <v>21.4747543334961</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>23.2800006866455</v>
       </c>
       <c r="G937" t="n">
-        <v>21.6420917510986</v>
+        <v>21.6420936584473</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>21.4200000762939</v>
       </c>
       <c r="G940" t="n">
-        <v>19.9129543304443</v>
+        <v>19.912956237793</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>22.1200008392334</v>
       </c>
       <c r="G941" t="n">
-        <v>20.5637054443359</v>
+        <v>20.5637092590332</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>21.7600002288818</v>
       </c>
       <c r="G942" t="n">
-        <v>20.2290344238281</v>
+        <v>20.2290325164795</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>21.8600006103516</v>
       </c>
       <c r="G943" t="n">
-        <v>20.3220024108887</v>
+        <v>20.32200050354</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>22.0799999237061</v>
       </c>
       <c r="G944" t="n">
-        <v>20.5265216827393</v>
+        <v>20.5265197753906</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>22.5200004577637</v>
       </c>
       <c r="G946" t="n">
-        <v>20.9355640411377</v>
+        <v>20.9355621337891</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>22.2199993133545</v>
       </c>
       <c r="G947" t="n">
-        <v>20.6566715240479</v>
+        <v>20.6566696166992</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>23</v>
       </c>
       <c r="G949" t="n">
-        <v>21.3817920684814</v>
+        <v>21.3817901611328</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>22.5200004577637</v>
       </c>
       <c r="G950" t="n">
-        <v>20.9355640411377</v>
+        <v>20.9355621337891</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>22.6200008392334</v>
       </c>
       <c r="G951" t="n">
-        <v>21.0285301208496</v>
+        <v>21.028528213501</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>21.5799999237061</v>
       </c>
       <c r="G956" t="n">
-        <v>20.0616989135742</v>
+        <v>20.0617008209229</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>22.2600002288818</v>
       </c>
       <c r="G958" t="n">
-        <v>20.6938533782959</v>
+        <v>20.6938571929932</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>21.8400001525879</v>
       </c>
       <c r="G959" t="n">
-        <v>20.3034076690674</v>
+        <v>20.3034057617188</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>21.8600006103516</v>
       </c>
       <c r="G960" t="n">
-        <v>20.3220024108887</v>
+        <v>20.32200050354</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>21.3400001525879</v>
       </c>
       <c r="G962" t="n">
-        <v>19.8385848999023</v>
+        <v>19.8385829925537</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>22.1200008392334</v>
       </c>
       <c r="G964" t="n">
-        <v>20.5637054443359</v>
+        <v>20.5637092590332</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>21.9200000762939</v>
       </c>
       <c r="G965" t="n">
-        <v>20.3777751922607</v>
+        <v>20.3777770996094</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>22.2199993133545</v>
       </c>
       <c r="G967" t="n">
-        <v>20.6566715240479</v>
+        <v>20.6566696166992</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>21.2800006866455</v>
       </c>
       <c r="G968" t="n">
-        <v>19.7828063964844</v>
+        <v>19.7828044891357</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>21.2399997711182</v>
       </c>
       <c r="G969" t="n">
-        <v>19.7456207275391</v>
+        <v>19.7456188201904</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G972" t="n">
-        <v>19.8013973236084</v>
+        <v>19.801399230957</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>21.8400001525879</v>
       </c>
       <c r="G974" t="n">
-        <v>20.3034076690674</v>
+        <v>20.3034057617188</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>23</v>
       </c>
       <c r="G975" t="n">
-        <v>21.3817920684814</v>
+        <v>21.3817901611328</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>22.5200004577637</v>
       </c>
       <c r="G976" t="n">
-        <v>20.9355640411377</v>
+        <v>20.9355621337891</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G977" t="n">
-        <v>21.4747562408447</v>
+        <v>21.4747543334961</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>23.8199996948242</v>
       </c>
       <c r="G982" t="n">
-        <v>22.1440963745117</v>
+        <v>22.1440982818604</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>24.8400001525879</v>
       </c>
       <c r="G986" t="n">
-        <v>23.0923347473145</v>
+        <v>23.0923366546631</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>25.0400009155273</v>
       </c>
       <c r="G987" t="n">
-        <v>23.2782649993896</v>
+        <v>23.278263092041</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>25.0400009155273</v>
       </c>
       <c r="G988" t="n">
-        <v>23.2782649993896</v>
+        <v>23.278263092041</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>24.6800003051758</v>
       </c>
       <c r="G989" t="n">
-        <v>22.9435901641846</v>
+        <v>22.9435920715332</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>24.9200000762939</v>
       </c>
       <c r="G991" t="n">
-        <v>23.1667079925537</v>
+        <v>23.1667098999023</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>25</v>
       </c>
       <c r="G992" t="n">
-        <v>23.2410774230957</v>
+        <v>23.2410755157471</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>26.0400009155273</v>
       </c>
       <c r="G995" t="n">
-        <v>24.2079067230225</v>
+        <v>24.2079086303711</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>26.2800006866455</v>
       </c>
       <c r="G996" t="n">
-        <v>24.431022644043</v>
+        <v>24.4310207366943</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>26.5599994659424</v>
       </c>
       <c r="G997" t="n">
-        <v>24.6913185119629</v>
+        <v>24.6913204193115</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>25.4799995422363</v>
       </c>
       <c r="G998" t="n">
-        <v>23.6873073577881</v>
+        <v>23.6873035430908</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>26.4799995422363</v>
       </c>
       <c r="G1000" t="n">
-        <v>24.6169509887695</v>
+        <v>24.6169490814209</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1002" t="n">
-        <v>24.3566493988037</v>
+        <v>24.3566513061523</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G1008" t="n">
-        <v>23.798864364624</v>
+        <v>23.7988662719727</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G1009" t="n">
-        <v>23.8918285369873</v>
+        <v>23.8918304443359</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G1010" t="n">
-        <v>23.8918285369873</v>
+        <v>23.8918304443359</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>25.8199996948242</v>
       </c>
       <c r="G1012" t="n">
-        <v>24.0033855438232</v>
+        <v>24.0033836364746</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>25.8199996948242</v>
       </c>
       <c r="G1016" t="n">
-        <v>24.0033855438232</v>
+        <v>24.0033836364746</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>25.8600006103516</v>
       </c>
       <c r="G1020" t="n">
-        <v>24.0405731201172</v>
+        <v>24.0405712127686</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>26.2800006866455</v>
       </c>
       <c r="G1022" t="n">
-        <v>24.431022644043</v>
+        <v>24.4310207366943</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>26.5400009155273</v>
       </c>
       <c r="G1025" t="n">
-        <v>24.6727294921875</v>
+        <v>24.6727313995361</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>26.0200004577637</v>
       </c>
       <c r="G1026" t="n">
-        <v>24.1893138885498</v>
+        <v>24.1893119812012</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1029" t="n">
-        <v>24.5425777435303</v>
+        <v>24.5425796508789</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>26.9799995422363</v>
       </c>
       <c r="G1030" t="n">
-        <v>25.0817699432373</v>
+        <v>25.0817680358887</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>26.7600002288818</v>
       </c>
       <c r="G1032" t="n">
-        <v>24.8772525787354</v>
+        <v>24.8772487640381</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>26.3400001525879</v>
       </c>
       <c r="G1033" t="n">
-        <v>24.4868030548096</v>
+        <v>24.4868011474609</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>27.0400009155273</v>
       </c>
       <c r="G1035" t="n">
-        <v>25.1375503540039</v>
+        <v>25.1375522613525</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>25.9400005340576</v>
       </c>
       <c r="G1036" t="n">
-        <v>24.1149406433105</v>
+        <v>24.1149425506592</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>25.6800003051758</v>
       </c>
       <c r="G1037" t="n">
-        <v>23.873233795166</v>
+        <v>23.8732357025146</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>26.0799999237061</v>
       </c>
       <c r="G1038" t="n">
-        <v>24.2450904846191</v>
+        <v>24.2450923919678</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>26.5400009155273</v>
       </c>
       <c r="G1039" t="n">
-        <v>24.6727294921875</v>
+        <v>24.6727313995361</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>27.4599990844727</v>
       </c>
       <c r="G1041" t="n">
-        <v>25.5279998779297</v>
+        <v>25.5279979705811</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>27.5200004577637</v>
       </c>
       <c r="G1042" t="n">
-        <v>25.5837802886963</v>
+        <v>25.583776473999</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>27.6399993896484</v>
       </c>
       <c r="G1043" t="n">
-        <v>25.6953353881836</v>
+        <v>25.695333480835</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>28.4200000762939</v>
       </c>
       <c r="G1044" t="n">
-        <v>26.4204578399658</v>
+        <v>26.4204540252686</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>28.8199996948242</v>
       </c>
       <c r="G1046" t="n">
-        <v>26.7923126220703</v>
+        <v>26.7923145294189</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>29</v>
       </c>
       <c r="G1047" t="n">
-        <v>26.9596519470215</v>
+        <v>26.9596500396729</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>29.6200008392334</v>
       </c>
       <c r="G1051" t="n">
-        <v>27.5360317230225</v>
+        <v>27.5360298156738</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1053" t="n">
-        <v>25.2862930297852</v>
+        <v>25.2862949371338</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1054" t="n">
-        <v>24.3566493988037</v>
+        <v>24.3566513061523</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>26.4200000762939</v>
       </c>
       <c r="G1055" t="n">
-        <v>24.5611705780029</v>
+        <v>24.5611724853516</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>25.7600002288818</v>
       </c>
       <c r="G1057" t="n">
-        <v>23.9476070404053</v>
+        <v>23.9476051330566</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>24.7199993133545</v>
       </c>
       <c r="G1058" t="n">
-        <v>22.9807777404785</v>
+        <v>22.9807758331299</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>25.6200008392334</v>
       </c>
       <c r="G1059" t="n">
-        <v>23.8174571990967</v>
+        <v>23.817455291748</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>23.8199996948242</v>
       </c>
       <c r="G1062" t="n">
-        <v>22.1440963745117</v>
+        <v>22.1440982818604</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>22.2199993133545</v>
       </c>
       <c r="G1063" t="n">
-        <v>20.6566715240479</v>
+        <v>20.6566696166992</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G1066" t="n">
-        <v>15.1717758178711</v>
+        <v>15.1717748641968</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G1069" t="n">
-        <v>15.6923751831055</v>
+        <v>15.6923742294312</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G1071" t="n">
-        <v>17.0589504241943</v>
+        <v>17.058952331543</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G1072" t="n">
-        <v>17.2727699279785</v>
+        <v>17.2727680206299</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>18.9899997711182</v>
       </c>
       <c r="G1073" t="n">
-        <v>17.6539192199707</v>
+        <v>17.6539211273193</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>19.0799999237061</v>
       </c>
       <c r="G1077" t="n">
-        <v>17.7375907897949</v>
+        <v>17.7375888824463</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>18.9699993133545</v>
       </c>
       <c r="G1078" t="n">
-        <v>17.6353282928467</v>
+        <v>17.635326385498</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>18.7199993133545</v>
       </c>
       <c r="G1079" t="n">
-        <v>17.4029216766357</v>
+        <v>17.4029178619385</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1080" t="n">
-        <v>16.919506072998</v>
+        <v>16.9195079803467</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G1083" t="n">
-        <v>17.1798038482666</v>
+        <v>17.1798057556152</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>19.6700000762939</v>
       </c>
       <c r="G1084" t="n">
-        <v>18.2860794067383</v>
+        <v>18.2860774993896</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1085" t="n">
-        <v>17.9421119689941</v>
+        <v>17.9421100616455</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>19.3150005340576</v>
       </c>
       <c r="G1086" t="n">
-        <v>17.9560585021973</v>
+        <v>17.9560565948486</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>19.6499996185303</v>
       </c>
       <c r="G1087" t="n">
-        <v>18.2674865722656</v>
+        <v>18.267484664917</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G1088" t="n">
-        <v>17.0589504241943</v>
+        <v>17.058952331543</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G1091" t="n">
-        <v>20.3127002716064</v>
+        <v>20.3127040863037</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>21.0400009155273</v>
       </c>
       <c r="G1092" t="n">
-        <v>19.5596923828125</v>
+        <v>19.5596942901611</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G1096" t="n">
-        <v>19.4760265350342</v>
+        <v>19.4760246276855</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>21.6499996185303</v>
       </c>
       <c r="G1101" t="n">
-        <v>20.1267757415771</v>
+        <v>20.1267719268799</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>22.3899993896484</v>
       </c>
       <c r="G1103" t="n">
-        <v>20.8147068023682</v>
+        <v>20.8147106170654</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>23.3899993896484</v>
       </c>
       <c r="G1106" t="n">
-        <v>21.7443504333496</v>
+        <v>21.7443523406982</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>22.8199996948242</v>
       </c>
       <c r="G1107" t="n">
-        <v>21.2144527435303</v>
+        <v>21.2144565582275</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>22.0100002288818</v>
       </c>
       <c r="G1108" t="n">
-        <v>20.4614429473877</v>
+        <v>20.4614448547363</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>22.4400005340576</v>
       </c>
       <c r="G1109" t="n">
-        <v>20.8611888885498</v>
+        <v>20.8611907958984</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>22.8899993896484</v>
       </c>
       <c r="G1110" t="n">
-        <v>21.2795295715332</v>
+        <v>21.2795314788818</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>21.9400005340576</v>
       </c>
       <c r="G1111" t="n">
-        <v>20.3963718414307</v>
+        <v>20.396369934082</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>23.0300006866455</v>
       </c>
       <c r="G1112" t="n">
-        <v>21.4096832275391</v>
+        <v>21.4096813201904</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>23</v>
       </c>
       <c r="G1114" t="n">
-        <v>21.3817920684814</v>
+        <v>21.3817901611328</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>24.2299995422363</v>
       </c>
       <c r="G1116" t="n">
-        <v>22.5252532958984</v>
+        <v>22.5252513885498</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>23.3299999237061</v>
       </c>
       <c r="G1117" t="n">
-        <v>21.6885738372803</v>
+        <v>21.6885757446289</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>24.6299991607666</v>
       </c>
       <c r="G1120" t="n">
-        <v>22.8971080780029</v>
+        <v>22.8971099853516</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>24.9400005340576</v>
       </c>
       <c r="G1122" t="n">
-        <v>23.1852989196777</v>
+        <v>23.1853008270264</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>24.4599990844727</v>
       </c>
       <c r="G1123" t="n">
-        <v>22.739070892334</v>
+        <v>22.7390689849854</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>23.7600002288818</v>
       </c>
       <c r="G1124" t="n">
-        <v>22.0883197784424</v>
+        <v>22.0883178710938</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>23.3299999237061</v>
       </c>
       <c r="G1125" t="n">
-        <v>21.6885738372803</v>
+        <v>21.6885757446289</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1126" t="n">
-        <v>22.0325412750244</v>
+        <v>22.032543182373</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>22.9200000762939</v>
       </c>
       <c r="G1128" t="n">
-        <v>21.3074188232422</v>
+        <v>21.3074207305908</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>23.1100006103516</v>
       </c>
       <c r="G1129" t="n">
-        <v>21.4840526580811</v>
+        <v>21.4840507507324</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>23.7700004577637</v>
       </c>
       <c r="G1130" t="n">
-        <v>22.0976181030273</v>
+        <v>22.0976161956787</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>24.0200004577637</v>
       </c>
       <c r="G1131" t="n">
-        <v>22.3300304412842</v>
+        <v>22.3300285339355</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>23.75</v>
       </c>
       <c r="G1133" t="n">
-        <v>22.0790252685547</v>
+        <v>22.0790233612061</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>24.2399997711182</v>
       </c>
       <c r="G1135" t="n">
-        <v>22.5345497131348</v>
+        <v>22.5345478057861</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>24.5699996948242</v>
       </c>
       <c r="G1136" t="n">
-        <v>22.841329574585</v>
+        <v>22.8413314819336</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>23.4799995422363</v>
       </c>
       <c r="G1137" t="n">
-        <v>21.8280200958252</v>
+        <v>21.8280181884766</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>23.5400009155273</v>
       </c>
       <c r="G1138" t="n">
-        <v>21.8838005065918</v>
+        <v>21.8837985992432</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>23.6200008392334</v>
       </c>
       <c r="G1139" t="n">
-        <v>21.9581718444824</v>
+        <v>21.9581699371338</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>23.5200004577637</v>
       </c>
       <c r="G1140" t="n">
-        <v>21.8652057647705</v>
+        <v>21.8652076721191</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>23.7099990844727</v>
       </c>
       <c r="G1141" t="n">
-        <v>22.0418376922607</v>
+        <v>22.0418395996094</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>23.8099994659424</v>
       </c>
       <c r="G1142" t="n">
-        <v>22.1348037719727</v>
+        <v>22.134801864624</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>24.3700008392334</v>
       </c>
       <c r="G1143" t="n">
-        <v>22.6554050445557</v>
+        <v>22.6554069519043</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>24.3400001525879</v>
       </c>
       <c r="G1144" t="n">
-        <v>22.627513885498</v>
+        <v>22.6275119781494</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>24.6499996185303</v>
       </c>
       <c r="G1145" t="n">
-        <v>22.9157047271729</v>
+        <v>22.9157028198242</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>24.9599990844727</v>
       </c>
       <c r="G1147" t="n">
-        <v>23.203893661499</v>
+        <v>23.2038917541504</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>24.8299999237061</v>
       </c>
       <c r="G1148" t="n">
-        <v>23.0830383300781</v>
+        <v>23.0830364227295</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1153" t="n">
-        <v>24.0777568817139</v>
+        <v>24.0777549743652</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>25.8199996948242</v>
       </c>
       <c r="G1154" t="n">
-        <v>24.0033855438232</v>
+        <v>24.0033836364746</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>26.25</v>
       </c>
       <c r="G1156" t="n">
-        <v>24.403133392334</v>
+        <v>24.4031314849854</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>27.8099994659424</v>
       </c>
       <c r="G1162" t="n">
-        <v>25.8533763885498</v>
+        <v>25.8533744812012</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G1164" t="n">
-        <v>26.9131698608398</v>
+        <v>26.9131679534912</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1166" t="n">
-        <v>26.7737197875977</v>
+        <v>26.7737236022949</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G1169" t="n">
-        <v>26.8202037811279</v>
+        <v>26.8202018737793</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>28.6700000762939</v>
       </c>
       <c r="G1172" t="n">
-        <v>26.6528663635254</v>
+        <v>26.652868270874</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>28.5100002288818</v>
       </c>
       <c r="G1173" t="n">
-        <v>26.5041255950928</v>
+        <v>26.5041275024414</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>27.9699993133545</v>
       </c>
       <c r="G1178" t="n">
-        <v>26.0021152496338</v>
+        <v>26.0021171569824</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>27.75</v>
       </c>
       <c r="G1179" t="n">
-        <v>25.7975959777832</v>
+        <v>25.7975978851318</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1180" t="n">
-        <v>25.7511119842529</v>
+        <v>25.7511157989502</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1182" t="n">
-        <v>25.7511119842529</v>
+        <v>25.7511157989502</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>27.5</v>
       </c>
       <c r="G1184" t="n">
-        <v>25.565185546875</v>
+        <v>25.5651836395264</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>27.9300003051758</v>
       </c>
       <c r="G1188" t="n">
-        <v>25.9649333953857</v>
+        <v>25.9649314880371</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>28.0200004577637</v>
       </c>
       <c r="G1189" t="n">
-        <v>26.0485992431641</v>
+        <v>26.0486011505127</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1190" t="n">
-        <v>26.7737197875977</v>
+        <v>26.7737236022949</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>28.6800003051758</v>
       </c>
       <c r="G1192" t="n">
-        <v>26.6621646881104</v>
+        <v>26.662166595459</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>29.5100002288818</v>
       </c>
       <c r="G1194" t="n">
-        <v>27.4337673187256</v>
+        <v>27.433765411377</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>29.6900005340576</v>
       </c>
       <c r="G1195" t="n">
-        <v>27.6011047363281</v>
+        <v>27.6011066436768</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>30.3600006103516</v>
       </c>
       <c r="G1197" t="n">
-        <v>28.2239665985107</v>
+        <v>28.2239646911621</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>30.1499996185303</v>
       </c>
       <c r="G1198" t="n">
-        <v>28.0287399291992</v>
+        <v>28.0287418365479</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>30.0499992370605</v>
       </c>
       <c r="G1199" t="n">
-        <v>27.9357757568359</v>
+        <v>27.9357738494873</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>28.8799991607666</v>
       </c>
       <c r="G1200" t="n">
-        <v>26.8480911254883</v>
+        <v>26.8480930328369</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>28.7700004577637</v>
       </c>
       <c r="G1203" t="n">
-        <v>26.7458305358887</v>
+        <v>26.7458324432373</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>28.9899997711182</v>
       </c>
       <c r="G1204" t="n">
-        <v>26.9503536224365</v>
+        <v>26.9503555297852</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>30.7700004577637</v>
       </c>
       <c r="G1205" t="n">
-        <v>28.6051158905029</v>
+        <v>28.6051197052002</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>30.5499992370605</v>
       </c>
       <c r="G1207" t="n">
-        <v>28.4005966186523</v>
+        <v>28.400598526001</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>30.8700008392334</v>
       </c>
       <c r="G1208" t="n">
-        <v>28.6980819702148</v>
+        <v>28.6980838775635</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>31.4400005340576</v>
       </c>
       <c r="G1210" t="n">
-        <v>29.2279777526855</v>
+        <v>29.2279796600342</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>30.5400009155273</v>
       </c>
       <c r="G1211" t="n">
-        <v>28.391300201416</v>
+        <v>28.3913040161133</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>31.2099990844727</v>
       </c>
       <c r="G1213" t="n">
-        <v>29.0141639709473</v>
+        <v>29.01416015625</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>31.9099998474121</v>
       </c>
       <c r="G1214" t="n">
-        <v>29.6649112701416</v>
+        <v>29.6649074554443</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>32.4500007629395</v>
       </c>
       <c r="G1215" t="n">
-        <v>30.166919708252</v>
+        <v>30.1669178009033</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>31.9799995422363</v>
       </c>
       <c r="G1218" t="n">
-        <v>29.7299861907959</v>
+        <v>29.7299880981445</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>32.3800010681152</v>
       </c>
       <c r="G1219" t="n">
-        <v>30.1018466949463</v>
+        <v>30.1018447875977</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>32.189998626709</v>
       </c>
       <c r="G1220" t="n">
-        <v>29.9252109527588</v>
+        <v>29.9252090454102</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>32.3899993896484</v>
       </c>
       <c r="G1221" t="n">
-        <v>30.1111431121826</v>
+        <v>30.1111392974854</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>32.1699981689453</v>
       </c>
       <c r="G1222" t="n">
-        <v>29.9066181182861</v>
+        <v>29.9066162109375</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>32.1300010681152</v>
       </c>
       <c r="G1223" t="n">
-        <v>29.8694343566895</v>
+        <v>29.8694362640381</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>32.2700004577637</v>
       </c>
       <c r="G1224" t="n">
-        <v>29.999584197998</v>
+        <v>29.9995861053467</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>31.9200000762939</v>
       </c>
       <c r="G1225" t="n">
-        <v>29.6742095947266</v>
+        <v>29.6742076873779</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>32</v>
       </c>
       <c r="G1226" t="n">
-        <v>29.7485790252686</v>
+        <v>29.7485809326172</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>30.0799999237061</v>
       </c>
       <c r="G1227" t="n">
-        <v>27.9636669158936</v>
+        <v>27.9636650085449</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>30.5900001525879</v>
       </c>
       <c r="G1228" t="n">
-        <v>28.4377841949463</v>
+        <v>28.4377822875977</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>31.2099990844727</v>
       </c>
       <c r="G1229" t="n">
-        <v>29.0141639709473</v>
+        <v>29.01416015625</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>32.3600006103516</v>
       </c>
       <c r="G1230" t="n">
-        <v>30.0832538604736</v>
+        <v>30.083251953125</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>34.4500007629395</v>
       </c>
       <c r="G1232" t="n">
-        <v>32.0262069702148</v>
+        <v>32.0262031555176</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>34.8800010681152</v>
       </c>
       <c r="G1234" t="n">
-        <v>32.425952911377</v>
+        <v>32.4259567260742</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>34.9000015258789</v>
       </c>
       <c r="G1236" t="n">
-        <v>32.4445457458496</v>
+        <v>32.4445419311523</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>35.1399993896484</v>
       </c>
       <c r="G1237" t="n">
-        <v>32.6676559448242</v>
+        <v>32.6676635742188</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>35.0099983215332</v>
       </c>
       <c r="G1239" t="n">
-        <v>32.5467987060547</v>
+        <v>32.546802520752</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>35.5299987792969</v>
       </c>
       <c r="G1242" t="n">
-        <v>33.0302200317383</v>
+        <v>33.0302238464355</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1245" t="n">
-        <v>31.9797267913818</v>
+        <v>31.9797229766846</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>33</v>
       </c>
       <c r="G1246" t="n">
-        <v>30.6782207489014</v>
+        <v>30.67822265625</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1247" t="n">
-        <v>30.7711868286133</v>
+        <v>30.7711849212646</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>33.4799995422363</v>
       </c>
       <c r="G1248" t="n">
-        <v>31.124454498291</v>
+        <v>31.1244525909424</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>34.2799987792969</v>
       </c>
       <c r="G1249" t="n">
-        <v>31.8681621551514</v>
+        <v>31.8681659698486</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>33.5699996948242</v>
       </c>
       <c r="G1250" t="n">
-        <v>31.2081203460693</v>
+        <v>31.208122253418</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>32.3800010681152</v>
       </c>
       <c r="G1251" t="n">
-        <v>30.1018466949463</v>
+        <v>30.1018447875977</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>32.7299995422363</v>
       </c>
       <c r="G1252" t="n">
-        <v>30.4272212982178</v>
+        <v>30.4272174835205</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>32.3800010681152</v>
       </c>
       <c r="G1253" t="n">
-        <v>30.1018466949463</v>
+        <v>30.1018447875977</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>32.3400001525879</v>
       </c>
       <c r="G1254" t="n">
-        <v>30.0646591186523</v>
+        <v>30.0646572113037</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>32.3300018310547</v>
       </c>
       <c r="G1257" t="n">
-        <v>30.0553646087646</v>
+        <v>30.0553607940674</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>33.1100006103516</v>
       </c>
       <c r="G1259" t="n">
-        <v>30.7804851531982</v>
+        <v>30.7804832458496</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>33.6100006103516</v>
       </c>
       <c r="G1260" t="n">
-        <v>31.245304107666</v>
+        <v>31.2453060150146</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>32.8400001525879</v>
       </c>
       <c r="G1261" t="n">
-        <v>30.5294818878174</v>
+        <v>30.5294799804688</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>33.6699981689453</v>
       </c>
       <c r="G1262" t="n">
-        <v>31.301082611084</v>
+        <v>31.3010807037354</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>33.4500007629395</v>
       </c>
       <c r="G1263" t="n">
-        <v>31.0965614318848</v>
+        <v>31.0965633392334</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>33.9500007629395</v>
       </c>
       <c r="G1264" t="n">
-        <v>31.5613842010498</v>
+        <v>31.5613861083984</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>33.7299995422363</v>
       </c>
       <c r="G1266" t="n">
-        <v>31.3568630218506</v>
+        <v>31.3568649291992</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1269" t="n">
-        <v>31.4219341278076</v>
+        <v>31.421932220459</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>34.0400009155273</v>
       </c>
       <c r="G1270" t="n">
-        <v>31.6450519561768</v>
+        <v>31.6450538635254</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>33.939998626709</v>
       </c>
       <c r="G1271" t="n">
-        <v>31.5520877838135</v>
+        <v>31.5520858764648</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>33.560001373291</v>
       </c>
       <c r="G1272" t="n">
-        <v>31.1988220214844</v>
+        <v>31.1988201141357</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>33.0200004577637</v>
       </c>
       <c r="G1273" t="n">
-        <v>30.6968173980713</v>
+        <v>30.6968116760254</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>32.6800003051758</v>
       </c>
       <c r="G1274" t="n">
-        <v>30.3807353973389</v>
+        <v>30.3807373046875</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>33.8400001525879</v>
       </c>
       <c r="G1275" t="n">
-        <v>31.4591178894043</v>
+        <v>31.4591236114502</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>33.6800003051758</v>
       </c>
       <c r="G1276" t="n">
-        <v>31.3103809356689</v>
+        <v>31.3103790283203</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>33.6199989318848</v>
       </c>
       <c r="G1277" t="n">
-        <v>31.2546005249023</v>
+        <v>31.2546043395996</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>33.9099998474121</v>
       </c>
       <c r="G1278" t="n">
-        <v>31.5241966247559</v>
+        <v>31.5241947174072</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>34.189998626709</v>
       </c>
       <c r="G1281" t="n">
-        <v>31.7844924926758</v>
+        <v>31.7845001220703</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>34.1199989318848</v>
       </c>
       <c r="G1283" t="n">
-        <v>31.7194213867188</v>
+        <v>31.7194194793701</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>33.8800010681152</v>
       </c>
       <c r="G1284" t="n">
-        <v>31.4963092803955</v>
+        <v>31.4963073730469</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>33.5499992370605</v>
       </c>
       <c r="G1287" t="n">
-        <v>31.1895236968994</v>
+        <v>31.189525604248</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G1288" t="n">
-        <v>31.7008266448975</v>
+        <v>31.7008304595947</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>32.7299995422363</v>
       </c>
       <c r="G1290" t="n">
-        <v>30.4272212982178</v>
+        <v>30.4272174835205</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>33.4300003051758</v>
       </c>
       <c r="G1291" t="n">
-        <v>31.0779705047607</v>
+        <v>31.0779685974121</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G1293" t="n">
-        <v>32.1656494140625</v>
+        <v>32.1656532287598</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>36.5900001525879</v>
       </c>
       <c r="G1297" t="n">
-        <v>34.0156402587891</v>
+        <v>34.0156440734863</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>36.6500015258789</v>
       </c>
       <c r="G1299" t="n">
-        <v>34.0714225769043</v>
+        <v>34.071418762207</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>37.4900016784668</v>
       </c>
       <c r="G1300" t="n">
-        <v>34.8523216247559</v>
+        <v>34.8523178100586</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>34.939998626709</v>
       </c>
       <c r="G1305" t="n">
-        <v>32.4817276000977</v>
+        <v>32.4817237854004</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>33.2799987792969</v>
       </c>
       <c r="G1307" t="n">
-        <v>30.9385223388672</v>
+        <v>30.9385242462158</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>33.310001373291</v>
       </c>
       <c r="G1308" t="n">
-        <v>30.9664154052734</v>
+        <v>30.9664115905762</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>33.2799987792969</v>
       </c>
       <c r="G1309" t="n">
-        <v>30.9385223388672</v>
+        <v>30.9385242462158</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>33</v>
       </c>
       <c r="G1310" t="n">
-        <v>30.6782207489014</v>
+        <v>30.67822265625</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>33.9900016784668</v>
       </c>
       <c r="G1311" t="n">
-        <v>31.5985717773438</v>
+        <v>31.5985698699951</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>31.3899993896484</v>
       </c>
       <c r="G1313" t="n">
-        <v>29.1814937591553</v>
+        <v>29.1814975738525</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>30.8799991607666</v>
       </c>
       <c r="G1314" t="n">
-        <v>28.7073802947998</v>
+        <v>28.7073783874512</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>30.3700008392334</v>
       </c>
       <c r="G1316" t="n">
-        <v>28.2332630157471</v>
+        <v>28.2332611083984</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>31.8199996948242</v>
       </c>
       <c r="G1317" t="n">
-        <v>29.581241607666</v>
+        <v>29.5812454223633</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>32.0900001525879</v>
       </c>
       <c r="G1318" t="n">
-        <v>29.8322467803955</v>
+        <v>29.8322486877441</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>32.1800003051758</v>
       </c>
       <c r="G1321" t="n">
-        <v>29.9159164428711</v>
+        <v>29.9159145355225</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>32.5900001525879</v>
       </c>
       <c r="G1322" t="n">
-        <v>30.2970714569092</v>
+        <v>30.2970676422119</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>31.4400005340576</v>
       </c>
       <c r="G1324" t="n">
-        <v>29.2279777526855</v>
+        <v>29.2279796600342</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>30.9300003051758</v>
       </c>
       <c r="G1325" t="n">
-        <v>28.7538623809814</v>
+        <v>28.7538642883301</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>33.1599998474121</v>
       </c>
       <c r="G1327" t="n">
-        <v>30.8269710540771</v>
+        <v>30.8269691467285</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>32</v>
       </c>
       <c r="G1329" t="n">
-        <v>29.7485790252686</v>
+        <v>29.7485809326172</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>32.2200012207031</v>
       </c>
       <c r="G1330" t="n">
-        <v>29.9531021118164</v>
+        <v>29.9531002044678</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>31.9799995422363</v>
       </c>
       <c r="G1332" t="n">
-        <v>29.7299861907959</v>
+        <v>29.7299880981445</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>32.4199981689453</v>
       </c>
       <c r="G1336" t="n">
-        <v>30.1390266418457</v>
+        <v>30.1390285491943</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>32.6800003051758</v>
       </c>
       <c r="G1337" t="n">
-        <v>30.3807353973389</v>
+        <v>30.3807373046875</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>33.0699996948242</v>
       </c>
       <c r="G1338" t="n">
-        <v>30.7432956695557</v>
+        <v>30.7432975769043</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>35.0800018310547</v>
       </c>
       <c r="G1340" t="n">
-        <v>32.6118812561035</v>
+        <v>32.6118850708008</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>35.2200012207031</v>
       </c>
       <c r="G1344" t="n">
-        <v>32.7420349121094</v>
+        <v>32.7420310974121</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>35.5299987792969</v>
       </c>
       <c r="G1345" t="n">
-        <v>33.0302200317383</v>
+        <v>33.0302238464355</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>35.7900009155273</v>
       </c>
       <c r="G1347" t="n">
-        <v>33.2719306945801</v>
+        <v>33.2719268798828</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>36.6399993896484</v>
       </c>
       <c r="G1349" t="n">
-        <v>34.0621185302734</v>
+        <v>34.062126159668</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>36.4700012207031</v>
       </c>
       <c r="G1350" t="n">
-        <v>33.9040908813477</v>
+        <v>33.9040832519531</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>35.9199981689453</v>
       </c>
       <c r="G1351" t="n">
-        <v>33.3927841186523</v>
+        <v>33.3927803039551</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>35.1300010681152</v>
       </c>
       <c r="G1353" t="n">
-        <v>32.6583671569824</v>
+        <v>32.6583633422852</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>35.7000007629395</v>
       </c>
       <c r="G1356" t="n">
-        <v>33.1882591247559</v>
+        <v>33.1882629394531</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>33.3899993896484</v>
       </c>
       <c r="G1362" t="n">
-        <v>31.0407810211182</v>
+        <v>31.0407791137695</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1364" t="n">
-        <v>31.2360076904297</v>
+        <v>31.2360057830811</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>34.5</v>
       </c>
       <c r="G1365" t="n">
-        <v>32.0726852416992</v>
+        <v>32.072681427002</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>36.439998626709</v>
       </c>
       <c r="G1368" t="n">
-        <v>33.8761901855469</v>
+        <v>33.8761940002441</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>37.4300003051758</v>
       </c>
       <c r="G1371" t="n">
-        <v>35.0078926086426</v>
+        <v>35.0078964233398</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>38.2700004577637</v>
       </c>
       <c r="G1372" t="n">
-        <v>35.7935409545898</v>
+        <v>35.7935371398926</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>38.9500007629395</v>
       </c>
       <c r="G1374" t="n">
-        <v>36.4295387268066</v>
+        <v>36.4295349121094</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>38.6399993896484</v>
       </c>
       <c r="G1375" t="n">
-        <v>36.139591217041</v>
+        <v>36.1395950317383</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>38.5299987792969</v>
       </c>
       <c r="G1376" t="n">
-        <v>36.0367126464844</v>
+        <v>36.0367164611816</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>38.6399993896484</v>
       </c>
       <c r="G1377" t="n">
-        <v>36.139591217041</v>
+        <v>36.1395950317383</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G1379" t="n">
-        <v>37.2245330810547</v>
+        <v>37.224536895752</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>39.4300003051758</v>
       </c>
       <c r="G1381" t="n">
-        <v>36.8784713745117</v>
+        <v>36.8784790039062</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>39.5699996948242</v>
       </c>
       <c r="G1383" t="n">
-        <v>37.0094146728516</v>
+        <v>37.0094108581543</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>40.8499984741211</v>
       </c>
       <c r="G1384" t="n">
-        <v>38.2065849304199</v>
+        <v>38.2065811157227</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>40.9500007629395</v>
       </c>
       <c r="G1387" t="n">
-        <v>38.3001136779785</v>
+        <v>38.300121307373</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>40.3800010681152</v>
       </c>
       <c r="G1389" t="n">
-        <v>37.7670021057129</v>
+        <v>37.7669982910156</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>40.1800003051758</v>
       </c>
       <c r="G1391" t="n">
-        <v>37.5799446105957</v>
+        <v>37.5799407958984</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>41.2700004577637</v>
       </c>
       <c r="G1393" t="n">
-        <v>38.5994110107422</v>
+        <v>38.5994071960449</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>41.3699989318848</v>
       </c>
       <c r="G1394" t="n">
-        <v>38.6929397583008</v>
+        <v>38.6929321289062</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>41.6399993896484</v>
       </c>
       <c r="G1396" t="n">
-        <v>38.9454650878906</v>
+        <v>38.9454612731934</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>41.5999984741211</v>
       </c>
       <c r="G1398" t="n">
-        <v>38.9080505371094</v>
+        <v>38.9080543518066</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>41.2200012207031</v>
       </c>
       <c r="G1399" t="n">
-        <v>38.5526428222656</v>
+        <v>38.5526466369629</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>41.6300010681152</v>
       </c>
       <c r="G1401" t="n">
-        <v>38.9361114501953</v>
+        <v>38.9361152648926</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>40.6699981689453</v>
       </c>
       <c r="G1402" t="n">
-        <v>38.0382308959961</v>
+        <v>38.0382270812988</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>38.0699996948242</v>
       </c>
       <c r="G1403" t="n">
-        <v>35.6064796447754</v>
+        <v>35.6064758300781</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>39.0999984741211</v>
       </c>
       <c r="G1404" t="n">
-        <v>36.5698280334473</v>
+        <v>36.5698318481445</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>39.0900001525879</v>
       </c>
       <c r="G1405" t="n">
-        <v>36.560474395752</v>
+        <v>36.5604782104492</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>40.3800010681152</v>
       </c>
       <c r="G1407" t="n">
-        <v>37.7670021057129</v>
+        <v>37.7669982910156</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>40.8499984741211</v>
       </c>
       <c r="G1411" t="n">
-        <v>38.2065849304199</v>
+        <v>38.2065811157227</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>41.3699989318848</v>
       </c>
       <c r="G1413" t="n">
-        <v>38.6929397583008</v>
+        <v>38.6929321289062</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>40.3499984741211</v>
       </c>
       <c r="G1417" t="n">
-        <v>37.738941192627</v>
+        <v>37.7389373779297</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>42.2999992370605</v>
       </c>
       <c r="G1419" t="n">
-        <v>39.5627555847168</v>
+        <v>39.5627593994141</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>42.3899993896484</v>
       </c>
       <c r="G1420" t="n">
-        <v>39.6469306945801</v>
+        <v>39.6469345092773</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>42.3699989318848</v>
       </c>
       <c r="G1422" t="n">
-        <v>39.6282234191895</v>
+        <v>39.6282196044922</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>42.0999984741211</v>
       </c>
       <c r="G1426" t="n">
-        <v>39.3757019042969</v>
+        <v>39.3756980895996</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>42.8199996948242</v>
       </c>
       <c r="G1428" t="n">
-        <v>40.0491065979004</v>
+        <v>40.0491027832031</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>43.0299987792969</v>
       </c>
       <c r="G1429" t="n">
-        <v>40.2455139160156</v>
+        <v>40.2455177307129</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>42.9099998474121</v>
       </c>
       <c r="G1430" t="n">
-        <v>40.1332817077637</v>
+        <v>40.1332778930664</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>43.2599983215332</v>
       </c>
       <c r="G1432" t="n">
-        <v>40.4606285095215</v>
+        <v>40.4606323242188</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>43.7999992370605</v>
       </c>
       <c r="G1433" t="n">
-        <v>40.965690612793</v>
+        <v>40.9656867980957</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>43.9700012207031</v>
       </c>
       <c r="G1435" t="n">
-        <v>41.1246910095215</v>
+        <v>41.1246871948242</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>43.75</v>
       </c>
       <c r="G1436" t="n">
-        <v>40.9189300537109</v>
+        <v>40.9189262390137</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>43.6800003051758</v>
       </c>
       <c r="G1438" t="n">
-        <v>40.853458404541</v>
+        <v>40.8534545898438</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>44.4099998474121</v>
       </c>
       <c r="G1441" t="n">
-        <v>41.5362205505371</v>
+        <v>41.5362167358398</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>44.7400016784668</v>
       </c>
       <c r="G1442" t="n">
-        <v>41.8448638916016</v>
+        <v>41.8448600769043</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>44.6500015258789</v>
       </c>
       <c r="G1444" t="n">
-        <v>41.760684967041</v>
+        <v>41.7606887817383</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>43.689998626709</v>
       </c>
       <c r="G1446" t="n">
-        <v>40.8628082275391</v>
+        <v>40.8628044128418</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>43.2299995422363</v>
       </c>
       <c r="G1447" t="n">
-        <v>40.4325752258301</v>
+        <v>40.4325714111328</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>41.6500015258789</v>
       </c>
       <c r="G1451" t="n">
-        <v>38.9548225402832</v>
+        <v>38.9548187255859</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>42.2999992370605</v>
       </c>
       <c r="G1452" t="n">
-        <v>39.5627555847168</v>
+        <v>39.5627593994141</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>42.5</v>
       </c>
       <c r="G1453" t="n">
-        <v>39.749813079834</v>
+        <v>39.7498168945312</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>42.7400016784668</v>
       </c>
       <c r="G1454" t="n">
-        <v>39.9742813110352</v>
+        <v>39.9742851257324</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>44.8300018310547</v>
       </c>
       <c r="G1455" t="n">
-        <v>41.9290390014648</v>
+        <v>41.9290428161621</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>44.9300003051758</v>
       </c>
       <c r="G1456" t="n">
-        <v>42.0225715637207</v>
+        <v>42.0225677490234</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>44.9799995422363</v>
       </c>
       <c r="G1458" t="n">
-        <v>42.0693283081055</v>
+        <v>42.0693321228027</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>41.4099998474121</v>
       </c>
       <c r="G1460" t="n">
-        <v>38.7303466796875</v>
+        <v>38.7303504943848</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>40.5999984741211</v>
       </c>
       <c r="G1469" t="n">
-        <v>37.9727592468262</v>
+        <v>37.9727668762207</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>41.2700004577637</v>
       </c>
       <c r="G1471" t="n">
-        <v>38.5994110107422</v>
+        <v>38.5994071960449</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>41.6500015258789</v>
       </c>
       <c r="G1472" t="n">
-        <v>38.9548225402832</v>
+        <v>38.9548187255859</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>42.9300003051758</v>
       </c>
       <c r="G1476" t="n">
-        <v>40.1519889831543</v>
+        <v>40.1519927978516</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>43.3199996948242</v>
       </c>
       <c r="G1477" t="n">
-        <v>40.5167503356934</v>
+        <v>40.5167541503906</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>43.689998626709</v>
       </c>
       <c r="G1478" t="n">
-        <v>40.8628082275391</v>
+        <v>40.8628044128418</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>44.5400009155273</v>
       </c>
       <c r="G1479" t="n">
-        <v>41.6578102111816</v>
+        <v>41.6578063964844</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>43.2700004577637</v>
       </c>
       <c r="G1480" t="n">
-        <v>40.4699897766113</v>
+        <v>40.4699859619141</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>42.8499984741211</v>
       </c>
       <c r="G1481" t="n">
-        <v>40.0771675109863</v>
+        <v>40.0771636962891</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>45.7599983215332</v>
       </c>
       <c r="G1488" t="n">
-        <v>42.7988624572754</v>
+        <v>42.7988586425781</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>45.6500015258789</v>
       </c>
       <c r="G1489" t="n">
-        <v>42.6959800720215</v>
+        <v>42.6959762573242</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>46.5400009155273</v>
       </c>
       <c r="G1490" t="n">
-        <v>43.5283889770508</v>
+        <v>43.5283851623535</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>45.7999992370605</v>
       </c>
       <c r="G1493" t="n">
-        <v>42.8362693786621</v>
+        <v>42.8362731933594</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>46.0099983215332</v>
       </c>
       <c r="G1494" t="n">
-        <v>43.0326805114746</v>
+        <v>43.0326766967773</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>43.9799995422363</v>
       </c>
       <c r="G1496" t="n">
-        <v>41.1340408325195</v>
+        <v>41.1340370178223</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>44.6100006103516</v>
       </c>
       <c r="G1497" t="n">
-        <v>41.7232780456543</v>
+        <v>41.723274230957</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>44.5499992370605</v>
       </c>
       <c r="G1498" t="n">
-        <v>41.6671600341797</v>
+        <v>41.6671562194824</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39343,7 +39343,7 @@
         <v>43.7999992370605</v>
       </c>
       <c r="G1499" t="n">
-        <v>40.965690612793</v>
+        <v>40.9656867980957</v>
       </c>
       <c r="H1499" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>42.7400016784668</v>
       </c>
       <c r="G1501" t="n">
-        <v>39.9742813110352</v>
+        <v>39.9742851257324</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>42.2000007629395</v>
       </c>
       <c r="G1503" t="n">
-        <v>39.4692268371582</v>
+        <v>39.4692306518555</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>43.1199989318848</v>
       </c>
       <c r="G1505" t="n">
-        <v>40.3296890258789</v>
+        <v>40.3296928405762</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39629,7 +39629,7 @@
         <v>42.9500007629395</v>
       </c>
       <c r="G1510" t="n">
-        <v>40.1706924438477</v>
+        <v>40.1706962585449</v>
       </c>
       <c r="H1510" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>41.6399993896484</v>
       </c>
       <c r="G1512" t="n">
-        <v>38.9454650878906</v>
+        <v>38.9454612731934</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>41.7799987792969</v>
       </c>
       <c r="G1513" t="n">
-        <v>39.0764083862305</v>
+        <v>39.0764045715332</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>41.9599990844727</v>
       </c>
       <c r="G1514" t="n">
-        <v>39.2447547912598</v>
+        <v>39.244758605957</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>42.7700004577637</v>
       </c>
       <c r="G1515" t="n">
-        <v>40.0023345947266</v>
+        <v>40.0023384094238</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>43.7000007629395</v>
       </c>
       <c r="G1516" t="n">
-        <v>40.8721618652344</v>
+        <v>40.8721656799316</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>44.0800018310547</v>
       </c>
       <c r="G1518" t="n">
-        <v>41.2275733947754</v>
+        <v>41.2275772094727</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>44.0999984741211</v>
       </c>
       <c r="G1519" t="n">
-        <v>41.2462768554688</v>
+        <v>41.246280670166</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>44.2999992370605</v>
       </c>
       <c r="G1520" t="n">
-        <v>41.4333305358887</v>
+        <v>41.4333343505859</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>45.310001373291</v>
       </c>
       <c r="G1521" t="n">
-        <v>42.3779830932617</v>
+        <v>42.3779754638672</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>45.439998626709</v>
       </c>
       <c r="G1522" t="n">
-        <v>42.4995651245117</v>
+        <v>42.4995613098145</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>46.9099998474121</v>
       </c>
       <c r="G1524" t="n">
-        <v>43.874439239502</v>
+        <v>43.8744430541992</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>46.6399993896484</v>
       </c>
       <c r="G1527" t="n">
-        <v>43.6219139099121</v>
+        <v>43.6219100952148</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>45.6800003051758</v>
       </c>
       <c r="G1528" t="n">
-        <v>42.7240371704102</v>
+        <v>42.7240295410156</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>45.8499984741211</v>
       </c>
       <c r="G1529" t="n">
-        <v>42.8830375671387</v>
+        <v>42.8830299377441</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40149,7 +40149,7 @@
         <v>44.3300018310547</v>
       </c>
       <c r="G1530" t="n">
-        <v>41.4613914489746</v>
+        <v>41.4613952636719</v>
       </c>
       <c r="H1530" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>43.5800018310547</v>
       </c>
       <c r="G1531" t="n">
-        <v>40.7599296569824</v>
+        <v>40.7599258422852</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>41.6599998474121</v>
       </c>
       <c r="G1532" t="n">
-        <v>38.964168548584</v>
+        <v>38.9641723632812</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>41.6500015258789</v>
       </c>
       <c r="G1534" t="n">
-        <v>38.9548225402832</v>
+        <v>38.9548187255859</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>40.8699989318848</v>
       </c>
       <c r="G1535" t="n">
-        <v>38.2252883911133</v>
+        <v>38.2252922058105</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>40.5200004577637</v>
       </c>
       <c r="G1536" t="n">
-        <v>37.8979377746582</v>
+        <v>37.8979415893555</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>40.8699989318848</v>
       </c>
       <c r="G1537" t="n">
-        <v>38.2252883911133</v>
+        <v>38.2252922058105</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>40.3800010681152</v>
       </c>
       <c r="G1540" t="n">
-        <v>37.7670021057129</v>
+        <v>37.7669982910156</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>37.2400016784668</v>
       </c>
       <c r="G1542" t="n">
-        <v>34.830192565918</v>
+        <v>34.8301887512207</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>35.9300003051758</v>
       </c>
       <c r="G1543" t="n">
-        <v>33.6049613952637</v>
+        <v>33.6049575805664</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>36.4300003051758</v>
       </c>
       <c r="G1544" t="n">
-        <v>34.0726051330566</v>
+        <v>34.0726089477539</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>36.4700012207031</v>
       </c>
       <c r="G1545" t="n">
-        <v>34.1100196838379</v>
+        <v>34.1100158691406</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>37.5299987792969</v>
       </c>
       <c r="G1547" t="n">
-        <v>35.1014213562012</v>
+        <v>35.1014251708984</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G1548" t="n">
-        <v>35.7280731201172</v>
+        <v>35.7280693054199</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>39.4099998474121</v>
       </c>
       <c r="G1549" t="n">
-        <v>36.8597717285156</v>
+        <v>36.8597640991211</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>37.0099983215332</v>
       </c>
       <c r="G1550" t="n">
-        <v>34.6150741577148</v>
+        <v>34.6150703430176</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>36.310001373291</v>
       </c>
       <c r="G1551" t="n">
-        <v>33.9603729248047</v>
+        <v>33.9603691101074</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40773,7 +40773,7 @@
         <v>36.5499992370605</v>
       </c>
       <c r="G1554" t="n">
-        <v>34.1848411560059</v>
+        <v>34.1848373413086</v>
       </c>
       <c r="H1554" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>36.189998626709</v>
       </c>
       <c r="G1555" t="n">
-        <v>33.8481330871582</v>
+        <v>33.8481369018555</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>35.6699981689453</v>
       </c>
       <c r="G1559" t="n">
-        <v>33.3617820739746</v>
+        <v>33.3617858886719</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>35.5400009155273</v>
       </c>
       <c r="G1561" t="n">
-        <v>33.2402038574219</v>
+        <v>33.2401962280273</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>35.2099990844727</v>
       </c>
       <c r="G1563" t="n">
-        <v>32.9315528869629</v>
+        <v>32.9315490722656</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>35.9799995422363</v>
       </c>
       <c r="G1564" t="n">
-        <v>33.6517219543457</v>
+        <v>33.651725769043</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G1566" t="n">
-        <v>34.9798316955566</v>
+        <v>34.9798355102539</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>36.2000007629395</v>
       </c>
       <c r="G1571" t="n">
-        <v>33.857494354248</v>
+        <v>33.8574867248535</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G1574" t="n">
-        <v>34.6992492675781</v>
+        <v>34.6992454528809</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>35.0800018310547</v>
       </c>
       <c r="G1575" t="n">
-        <v>32.8099632263184</v>
+        <v>32.8099670410156</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41371,7 +41371,7 @@
         <v>36.5699996948242</v>
       </c>
       <c r="G1577" t="n">
-        <v>34.2035446166992</v>
+        <v>34.2035484313965</v>
       </c>
       <c r="H1577" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>36.3499984741211</v>
       </c>
       <c r="G1578" t="n">
-        <v>33.9977836608887</v>
+        <v>33.9977798461914</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>37.75</v>
       </c>
       <c r="G1579" t="n">
-        <v>35.307186126709</v>
+        <v>35.3071899414062</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>37.2200012207031</v>
       </c>
       <c r="G1586" t="n">
-        <v>34.8114814758301</v>
+        <v>34.8114852905273</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>40.5400009155273</v>
       </c>
       <c r="G1590" t="n">
-        <v>37.9166488647461</v>
+        <v>37.9166412353516</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41891,7 +41891,7 @@
         <v>40.3499984741211</v>
       </c>
       <c r="G1597" t="n">
-        <v>37.738941192627</v>
+        <v>37.7389373779297</v>
       </c>
       <c r="H1597" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>40.5999984741211</v>
       </c>
       <c r="G1600" t="n">
-        <v>37.9727592468262</v>
+        <v>37.9727668762207</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>40.2000007629395</v>
       </c>
       <c r="G1602" t="n">
-        <v>37.5986480712891</v>
+        <v>37.5986518859863</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42047,7 +42047,7 @@
         <v>39.5299987792969</v>
       </c>
       <c r="G1603" t="n">
-        <v>36.9720001220703</v>
+        <v>36.9720039367676</v>
       </c>
       <c r="H1603" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>38.1399993896484</v>
       </c>
       <c r="G1605" t="n">
-        <v>35.6719512939453</v>
+        <v>35.671947479248</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42125,7 +42125,7 @@
         <v>37.8199996948242</v>
       </c>
       <c r="G1606" t="n">
-        <v>35.3726615905762</v>
+        <v>35.3726577758789</v>
       </c>
       <c r="H1606" t="s">
         <v>8</v>
@@ -42151,7 +42151,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G1607" t="n">
-        <v>34.5121917724609</v>
+        <v>34.5121879577637</v>
       </c>
       <c r="H1607" t="s">
         <v>8</v>
@@ -42177,7 +42177,7 @@
         <v>37.7299995422363</v>
       </c>
       <c r="G1608" t="n">
-        <v>35.2884826660156</v>
+        <v>35.2884864807129</v>
       </c>
       <c r="H1608" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>38.2200012207031</v>
       </c>
       <c r="G1609" t="n">
-        <v>35.7467765808105</v>
+        <v>35.7467727661133</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>37.6100006103516</v>
       </c>
       <c r="G1610" t="n">
-        <v>35.1762504577637</v>
+        <v>35.1762466430664</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42255,7 +42255,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G1611" t="n">
-        <v>34.6992492675781</v>
+        <v>34.6992454528809</v>
       </c>
       <c r="H1611" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>36.7599983215332</v>
       </c>
       <c r="G1613" t="n">
-        <v>34.3812446594238</v>
+        <v>34.3812522888184</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>35.4599990844727</v>
       </c>
       <c r="G1614" t="n">
-        <v>33.1653709411621</v>
+        <v>33.1653747558594</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42385,7 +42385,7 @@
         <v>34.3300018310547</v>
       </c>
       <c r="G1616" t="n">
-        <v>32.1084938049316</v>
+        <v>32.1085014343262</v>
       </c>
       <c r="H1616" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>32.3199996948242</v>
       </c>
       <c r="G1618" t="n">
-        <v>30.2285633087158</v>
+        <v>30.2285652160645</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>34.25</v>
       </c>
       <c r="G1619" t="n">
-        <v>32.0336685180664</v>
+        <v>32.0336723327637</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42489,7 +42489,7 @@
         <v>34.2599983215332</v>
       </c>
       <c r="G1620" t="n">
-        <v>32.0430221557617</v>
+        <v>32.043025970459</v>
       </c>
       <c r="H1620" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>32.5499992370605</v>
       </c>
       <c r="G1622" t="n">
-        <v>30.4436817169189</v>
+        <v>30.4436798095703</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42567,7 +42567,7 @@
         <v>31.5799999237061</v>
       </c>
       <c r="G1623" t="n">
-        <v>29.536449432373</v>
+        <v>29.5364513397217</v>
       </c>
       <c r="H1623" t="s">
         <v>8</v>
@@ -71300,6 +71300,32 @@
         <v>11.5699996948242</v>
       </c>
       <c r="H2728" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2729">
+      <c r="A2729" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2729" t="n">
+        <v>1074733</v>
+      </c>
+      <c r="C2729" t="n">
+        <v>11.7299995422363</v>
+      </c>
+      <c r="D2729" t="n">
+        <v>11.3699998855591</v>
+      </c>
+      <c r="E2729" t="n">
+        <v>11.5600004196167</v>
+      </c>
+      <c r="F2729" t="n">
+        <v>11.4250001907349</v>
+      </c>
+      <c r="G2729" t="n">
+        <v>11.4250001907349</v>
+      </c>
+      <c r="H2729" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/AMP.MI.xlsx
+++ b/data/AMP.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>11.7049999237061</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>12.085000038147</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>1255394</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>12.3050003051758</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>12.039999961853</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>12.1499996185303</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/AMP.MI.xlsx
+++ b/data/AMP.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>12.1499996185303</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>12.1949996948242</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>1016506</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>12.2799997329712</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>12.0200004577637</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>12.1949996948242</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/AMP.MI.xlsx
+++ b/data/AMP.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>12.1949996948242</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>12.1099996566772</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>655925</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>12.0749998092651</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>11.8850002288818</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>12.0200004577637</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/AMP.MI.xlsx
+++ b/data/AMP.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>12.0200004577637</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>12.039999961853</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>3464004</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>12.9200000762939</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>12.1850004196167</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>12.2399997711182</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/AMP.MI.xlsx
+++ b/data/AMP.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>1074846</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>12.960000038147</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>12.6300001144409</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>12.835000038147</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>12.6499996185303</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AMP.MI.xlsx
+++ b/data/AMP.MI.xlsx
@@ -427,7 +427,7 @@
         <v>7.875</v>
       </c>
       <c r="G2" t="n">
-        <v>7.14058494567871</v>
+        <v>7.14058399200439</v>
       </c>
       <c r="H2" t="n">
         <v>581549</v>
@@ -456,7 +456,7 @@
         <v>7.93499994277954</v>
       </c>
       <c r="G3" t="n">
-        <v>7.19498777389526</v>
+        <v>7.19498872756958</v>
       </c>
       <c r="H3" t="n">
         <v>1026450</v>
@@ -485,7 +485,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G4" t="n">
-        <v>7.11791515350342</v>
+        <v>7.11791563034058</v>
       </c>
       <c r="H4" t="n">
         <v>412059</v>
@@ -543,7 +543,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G6" t="n">
-        <v>6.96377038955688</v>
+        <v>6.96376943588257</v>
       </c>
       <c r="H6" t="n">
         <v>564414</v>
@@ -572,7 +572,7 @@
         <v>7.47499990463257</v>
       </c>
       <c r="G7" t="n">
-        <v>6.77788782119751</v>
+        <v>6.77788734436035</v>
       </c>
       <c r="H7" t="n">
         <v>790319</v>
@@ -601,7 +601,7 @@
         <v>7.75</v>
       </c>
       <c r="G8" t="n">
-        <v>7.02724170684814</v>
+        <v>7.02724075317383</v>
       </c>
       <c r="H8" t="n">
         <v>410093</v>
@@ -688,7 +688,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G11" t="n">
-        <v>6.84589385986328</v>
+        <v>6.84589338302612</v>
       </c>
       <c r="H11" t="n">
         <v>741151</v>
@@ -717,7 +717,7 @@
         <v>7.6100001335144</v>
       </c>
       <c r="G12" t="n">
-        <v>6.90029716491699</v>
+        <v>6.90029764175415</v>
       </c>
       <c r="H12" t="n">
         <v>895306</v>
@@ -746,7 +746,7 @@
         <v>7.72499990463257</v>
       </c>
       <c r="G13" t="n">
-        <v>7.00457334518433</v>
+        <v>7.00457286834717</v>
       </c>
       <c r="H13" t="n">
         <v>647831</v>
@@ -775,7 +775,7 @@
         <v>7.5</v>
       </c>
       <c r="G14" t="n">
-        <v>6.80055618286133</v>
+        <v>6.80055665969849</v>
       </c>
       <c r="H14" t="n">
         <v>661465</v>
@@ -804,7 +804,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G15" t="n">
-        <v>6.94563484191895</v>
+        <v>6.94563388824463</v>
       </c>
       <c r="H15" t="n">
         <v>921804</v>
@@ -862,7 +862,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G17" t="n">
-        <v>7.04537582397461</v>
+        <v>7.04537534713745</v>
       </c>
       <c r="H17" t="n">
         <v>474730</v>
@@ -920,7 +920,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G19" t="n">
-        <v>7.11791515350342</v>
+        <v>7.11791563034058</v>
       </c>
       <c r="H19" t="n">
         <v>324890</v>
@@ -978,7 +978,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G21" t="n">
-        <v>6.99097204208374</v>
+        <v>6.99097108840942</v>
       </c>
       <c r="H21" t="n">
         <v>492355</v>
@@ -1094,7 +1094,7 @@
         <v>7.57000017166138</v>
       </c>
       <c r="G25" t="n">
-        <v>6.86402750015259</v>
+        <v>6.86402797698975</v>
       </c>
       <c r="H25" t="n">
         <v>408165</v>
@@ -1123,7 +1123,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G26" t="n">
-        <v>6.66454601287842</v>
+        <v>6.66454410552979</v>
       </c>
       <c r="H26" t="n">
         <v>302407</v>
@@ -1181,7 +1181,7 @@
         <v>6.92999982833862</v>
       </c>
       <c r="G28" t="n">
-        <v>6.28371334075928</v>
+        <v>6.28371429443359</v>
       </c>
       <c r="H28" t="n">
         <v>843907</v>
@@ -1210,7 +1210,7 @@
         <v>7.07499980926514</v>
       </c>
       <c r="G29" t="n">
-        <v>6.41519117355347</v>
+        <v>6.41519165039062</v>
       </c>
       <c r="H29" t="n">
         <v>619256</v>
@@ -1239,7 +1239,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G30" t="n">
-        <v>6.16583728790283</v>
+        <v>6.16583776473999</v>
       </c>
       <c r="H30" t="n">
         <v>688119</v>
@@ -1268,7 +1268,7 @@
         <v>6.75500011444092</v>
       </c>
       <c r="G31" t="n">
-        <v>6.12503433227539</v>
+        <v>6.12503385543823</v>
       </c>
       <c r="H31" t="n">
         <v>487657</v>
@@ -1297,7 +1297,7 @@
         <v>6.89499998092651</v>
       </c>
       <c r="G32" t="n">
-        <v>6.25197792053223</v>
+        <v>6.25197696685791</v>
       </c>
       <c r="H32" t="n">
         <v>620923</v>
@@ -1326,7 +1326,7 @@
         <v>7.10500001907349</v>
       </c>
       <c r="G33" t="n">
-        <v>6.4423942565918</v>
+        <v>6.44239330291748</v>
       </c>
       <c r="H33" t="n">
         <v>498343</v>
@@ -1413,7 +1413,7 @@
         <v>7.20499992370605</v>
       </c>
       <c r="G36" t="n">
-        <v>6.53306722640991</v>
+        <v>6.53306770324707</v>
       </c>
       <c r="H36" t="n">
         <v>449688</v>
@@ -1471,7 +1471,7 @@
         <v>7.19500017166138</v>
       </c>
       <c r="G38" t="n">
-        <v>6.52400064468384</v>
+        <v>6.52400016784668</v>
       </c>
       <c r="H38" t="n">
         <v>259216</v>
@@ -1529,7 +1529,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G40" t="n">
-        <v>6.80962324142456</v>
+        <v>6.80962371826172</v>
       </c>
       <c r="H40" t="n">
         <v>712401</v>
@@ -1558,7 +1558,7 @@
         <v>7.5</v>
       </c>
       <c r="G41" t="n">
-        <v>6.80055618286133</v>
+        <v>6.80055665969849</v>
       </c>
       <c r="H41" t="n">
         <v>634905</v>
@@ -1587,7 +1587,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G42" t="n">
-        <v>6.70988130569458</v>
+        <v>6.7098822593689</v>
       </c>
       <c r="H42" t="n">
         <v>408673</v>
@@ -1616,7 +1616,7 @@
         <v>7.5</v>
       </c>
       <c r="G43" t="n">
-        <v>6.80055618286133</v>
+        <v>6.80055665969849</v>
       </c>
       <c r="H43" t="n">
         <v>247981</v>
@@ -1674,7 +1674,7 @@
         <v>7.30499982833862</v>
       </c>
       <c r="G45" t="n">
-        <v>6.62374210357666</v>
+        <v>6.62374114990234</v>
       </c>
       <c r="H45" t="n">
         <v>383515</v>
@@ -1703,7 +1703,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G46" t="n">
-        <v>6.61920833587646</v>
+        <v>6.61920785903931</v>
       </c>
       <c r="H46" t="n">
         <v>254992</v>
@@ -1761,7 +1761,7 @@
         <v>7.10500001907349</v>
       </c>
       <c r="G48" t="n">
-        <v>6.4423942565918</v>
+        <v>6.44239330291748</v>
       </c>
       <c r="H48" t="n">
         <v>288953</v>
@@ -1790,7 +1790,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G49" t="n">
-        <v>6.48319721221924</v>
+        <v>6.48319625854492</v>
       </c>
       <c r="H49" t="n">
         <v>332635</v>
@@ -1819,7 +1819,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G50" t="n">
-        <v>6.45599460601807</v>
+        <v>6.45599412918091</v>
       </c>
       <c r="H50" t="n">
         <v>387072</v>
@@ -1848,7 +1848,7 @@
         <v>7.29500007629395</v>
       </c>
       <c r="G51" t="n">
-        <v>6.61467409133911</v>
+        <v>6.61467504501343</v>
       </c>
       <c r="H51" t="n">
         <v>353216</v>
@@ -1877,7 +1877,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G52" t="n">
-        <v>6.66454601287842</v>
+        <v>6.66454410552979</v>
       </c>
       <c r="H52" t="n">
         <v>402066</v>
@@ -1906,7 +1906,7 @@
         <v>7.28499984741211</v>
       </c>
       <c r="G53" t="n">
-        <v>6.60560607910156</v>
+        <v>6.60560703277588</v>
       </c>
       <c r="H53" t="n">
         <v>448263</v>
@@ -1935,7 +1935,7 @@
         <v>7.36499977111816</v>
       </c>
       <c r="G54" t="n">
-        <v>6.67814636230469</v>
+        <v>6.67814588546753</v>
       </c>
       <c r="H54" t="n">
         <v>408735</v>
@@ -2080,7 +2080,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G59" t="n">
-        <v>7.01817417144775</v>
+        <v>7.01817321777344</v>
       </c>
       <c r="H59" t="n">
         <v>367903</v>
@@ -2109,7 +2109,7 @@
         <v>7.63000011444092</v>
       </c>
       <c r="G60" t="n">
-        <v>6.91843223571777</v>
+        <v>6.91843175888062</v>
       </c>
       <c r="H60" t="n">
         <v>166161</v>
@@ -2138,7 +2138,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G61" t="n">
-        <v>6.85496044158936</v>
+        <v>6.85495948791504</v>
       </c>
       <c r="H61" t="n">
         <v>601185</v>
@@ -2167,7 +2167,7 @@
         <v>7.77500009536743</v>
       </c>
       <c r="G62" t="n">
-        <v>7.04991006851196</v>
+        <v>7.04991054534912</v>
       </c>
       <c r="H62" t="n">
         <v>253910</v>
@@ -2196,7 +2196,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G63" t="n">
-        <v>6.90936470031738</v>
+        <v>6.90936517715454</v>
       </c>
       <c r="H63" t="n">
         <v>337648</v>
@@ -2254,7 +2254,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G65" t="n">
-        <v>6.96377038955688</v>
+        <v>6.96376943588257</v>
       </c>
       <c r="H65" t="n">
         <v>466696</v>
@@ -2283,7 +2283,7 @@
         <v>7.63000011444092</v>
       </c>
       <c r="G66" t="n">
-        <v>6.91843223571777</v>
+        <v>6.91843175888062</v>
       </c>
       <c r="H66" t="n">
         <v>279615</v>
@@ -2312,7 +2312,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G67" t="n">
-        <v>6.96377038955688</v>
+        <v>6.96376943588257</v>
       </c>
       <c r="H67" t="n">
         <v>286573</v>
@@ -2370,7 +2370,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G69" t="n">
-        <v>6.90936470031738</v>
+        <v>6.90936517715454</v>
       </c>
       <c r="H69" t="n">
         <v>250709</v>
@@ -2399,7 +2399,7 @@
         <v>7.42500019073486</v>
       </c>
       <c r="G70" t="n">
-        <v>6.73255062103271</v>
+        <v>6.73255109786987</v>
       </c>
       <c r="H70" t="n">
         <v>210960</v>
@@ -2428,7 +2428,7 @@
         <v>7.57000017166138</v>
       </c>
       <c r="G71" t="n">
-        <v>6.86402750015259</v>
+        <v>6.86402797698975</v>
       </c>
       <c r="H71" t="n">
         <v>310537</v>
@@ -2457,7 +2457,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G72" t="n">
-        <v>6.81869077682495</v>
+        <v>6.81869173049927</v>
       </c>
       <c r="H72" t="n">
         <v>460281</v>
@@ -2486,7 +2486,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G73" t="n">
-        <v>6.96377038955688</v>
+        <v>6.96376943588257</v>
       </c>
       <c r="H73" t="n">
         <v>187563</v>
@@ -2515,7 +2515,7 @@
         <v>7.6100001335144</v>
       </c>
       <c r="G74" t="n">
-        <v>6.90029716491699</v>
+        <v>6.90029764175415</v>
       </c>
       <c r="H74" t="n">
         <v>231734</v>
@@ -2544,7 +2544,7 @@
         <v>7.80499982833862</v>
       </c>
       <c r="G75" t="n">
-        <v>7.07711172103882</v>
+        <v>7.07711267471313</v>
       </c>
       <c r="H75" t="n">
         <v>380604</v>
@@ -2573,7 +2573,7 @@
         <v>7.77500009536743</v>
       </c>
       <c r="G76" t="n">
-        <v>7.04991006851196</v>
+        <v>7.04991054534912</v>
       </c>
       <c r="H76" t="n">
         <v>308594</v>
@@ -2602,7 +2602,7 @@
         <v>7.86499977111816</v>
       </c>
       <c r="G77" t="n">
-        <v>7.13151550292969</v>
+        <v>7.131516456604</v>
       </c>
       <c r="H77" t="n">
         <v>459218</v>
@@ -2631,7 +2631,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G78" t="n">
-        <v>7.03630781173706</v>
+        <v>7.03630876541138</v>
       </c>
       <c r="H78" t="n">
         <v>257235</v>
@@ -2718,7 +2718,7 @@
         <v>7.75</v>
       </c>
       <c r="G81" t="n">
-        <v>7.02724170684814</v>
+        <v>7.02724075317383</v>
       </c>
       <c r="H81" t="n">
         <v>241339</v>
@@ -2747,7 +2747,7 @@
         <v>8.05500030517578</v>
       </c>
       <c r="G82" t="n">
-        <v>7.30379772186279</v>
+        <v>7.30379724502563</v>
       </c>
       <c r="H82" t="n">
         <v>1582564</v>
@@ -2776,7 +2776,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G83" t="n">
-        <v>7.21765613555908</v>
+        <v>7.2176570892334</v>
       </c>
       <c r="H83" t="n">
         <v>1025479</v>
@@ -2805,7 +2805,7 @@
         <v>8.03499984741211</v>
       </c>
       <c r="G84" t="n">
-        <v>7.28566217422485</v>
+        <v>7.28566265106201</v>
       </c>
       <c r="H84" t="n">
         <v>533935</v>
@@ -2834,7 +2834,7 @@
         <v>8.13500022888184</v>
       </c>
       <c r="G85" t="n">
-        <v>7.37633657455444</v>
+        <v>7.37633562088013</v>
       </c>
       <c r="H85" t="n">
         <v>616876</v>
@@ -2863,7 +2863,7 @@
         <v>8.10999965667725</v>
       </c>
       <c r="G86" t="n">
-        <v>7.35366821289062</v>
+        <v>7.35366773605347</v>
       </c>
       <c r="H86" t="n">
         <v>1128963</v>
@@ -2892,7 +2892,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G87" t="n">
-        <v>7.52594757080078</v>
+        <v>7.52594995498657</v>
       </c>
       <c r="H87" t="n">
         <v>1276411</v>
@@ -2921,7 +2921,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G88" t="n">
-        <v>7.39900493621826</v>
+        <v>7.39900541305542</v>
       </c>
       <c r="H88" t="n">
         <v>551788</v>
@@ -2979,7 +2979,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G90" t="n">
-        <v>7.49874639511108</v>
+        <v>7.49874782562256</v>
       </c>
       <c r="H90" t="n">
         <v>474707</v>
@@ -3037,7 +3037,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G92" t="n">
-        <v>7.52594757080078</v>
+        <v>7.52594995498657</v>
       </c>
       <c r="H92" t="n">
         <v>552611</v>
@@ -3066,7 +3066,7 @@
         <v>8.46500015258789</v>
       </c>
       <c r="G93" t="n">
-        <v>7.67556190490723</v>
+        <v>7.67556095123291</v>
       </c>
       <c r="H93" t="n">
         <v>847984</v>
@@ -3124,7 +3124,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G95" t="n">
-        <v>7.66195917129517</v>
+        <v>7.66196012496948</v>
       </c>
       <c r="H95" t="n">
         <v>273222</v>
@@ -3153,7 +3153,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G96" t="n">
-        <v>7.58035230636597</v>
+        <v>7.58035278320312</v>
       </c>
       <c r="H96" t="n">
         <v>525629</v>
@@ -3182,7 +3182,7 @@
         <v>8.52999973297119</v>
       </c>
       <c r="G97" t="n">
-        <v>7.73449945449829</v>
+        <v>7.73449802398682</v>
       </c>
       <c r="H97" t="n">
         <v>620017</v>
@@ -3211,7 +3211,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G98" t="n">
-        <v>7.67102670669556</v>
+        <v>7.67102766036987</v>
       </c>
       <c r="H98" t="n">
         <v>391453</v>
@@ -3240,7 +3240,7 @@
         <v>8.6850004196167</v>
       </c>
       <c r="G99" t="n">
-        <v>7.87504434585571</v>
+        <v>7.87504386901855</v>
       </c>
       <c r="H99" t="n">
         <v>385168</v>
@@ -3298,7 +3298,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G101" t="n">
-        <v>7.88233375549316</v>
+        <v>7.88233470916748</v>
       </c>
       <c r="H101" t="n">
         <v>266998</v>
@@ -3327,7 +3327,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G102" t="n">
-        <v>7.89144659042358</v>
+        <v>7.8914475440979</v>
       </c>
       <c r="H102" t="n">
         <v>378020</v>
@@ -3356,7 +3356,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G103" t="n">
-        <v>7.83677196502686</v>
+        <v>7.83677053451538</v>
       </c>
       <c r="H103" t="n">
         <v>253080</v>
@@ -3414,7 +3414,7 @@
         <v>8.77499961853027</v>
       </c>
       <c r="G105" t="n">
-        <v>7.99624061584473</v>
+        <v>7.99623966217041</v>
       </c>
       <c r="H105" t="n">
         <v>219356</v>
@@ -3443,7 +3443,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G106" t="n">
-        <v>8.01902198791504</v>
+        <v>8.01902294158936</v>
       </c>
       <c r="H106" t="n">
         <v>414930</v>
@@ -3472,7 +3472,7 @@
         <v>8.78499984741211</v>
       </c>
       <c r="G107" t="n">
-        <v>8.00535297393799</v>
+        <v>8.00535202026367</v>
       </c>
       <c r="H107" t="n">
         <v>433091</v>
@@ -3501,7 +3501,7 @@
         <v>8.71500015258789</v>
       </c>
       <c r="G108" t="n">
-        <v>7.94156455993652</v>
+        <v>7.94156646728516</v>
       </c>
       <c r="H108" t="n">
         <v>610032</v>
@@ -3559,7 +3559,7 @@
         <v>8.63500022888184</v>
       </c>
       <c r="G110" t="n">
-        <v>7.86866426467896</v>
+        <v>7.86866521835327</v>
       </c>
       <c r="H110" t="n">
         <v>723142</v>
@@ -3617,7 +3617,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G112" t="n">
-        <v>7.80032300949097</v>
+        <v>7.80032110214233</v>
       </c>
       <c r="H112" t="n">
         <v>412613</v>
@@ -3646,7 +3646,7 @@
         <v>8.45499992370605</v>
       </c>
       <c r="G113" t="n">
-        <v>7.70463943481445</v>
+        <v>7.70463991165161</v>
       </c>
       <c r="H113" t="n">
         <v>744954</v>
@@ -3675,7 +3675,7 @@
         <v>8.35499954223633</v>
       </c>
       <c r="G114" t="n">
-        <v>7.6135139465332</v>
+        <v>7.61351442337036</v>
       </c>
       <c r="H114" t="n">
         <v>415231</v>
@@ -3762,7 +3762,7 @@
         <v>8.17500019073486</v>
       </c>
       <c r="G117" t="n">
-        <v>7.44948959350586</v>
+        <v>7.4494891166687</v>
       </c>
       <c r="H117" t="n">
         <v>509659</v>
@@ -3791,7 +3791,7 @@
         <v>8.07499980926514</v>
       </c>
       <c r="G118" t="n">
-        <v>7.35836362838745</v>
+        <v>7.35836315155029</v>
       </c>
       <c r="H118" t="n">
         <v>920550</v>
@@ -3820,7 +3820,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G119" t="n">
-        <v>7.43582010269165</v>
+        <v>7.43582057952881</v>
       </c>
       <c r="H119" t="n">
         <v>712210</v>
@@ -3849,7 +3849,7 @@
         <v>8.53499984741211</v>
       </c>
       <c r="G120" t="n">
-        <v>7.77754020690918</v>
+        <v>7.77753973007202</v>
       </c>
       <c r="H120" t="n">
         <v>885852</v>
@@ -3878,7 +3878,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G121" t="n">
-        <v>7.73653268814087</v>
+        <v>7.73653221130371</v>
       </c>
       <c r="H121" t="n">
         <v>368453</v>
@@ -3907,7 +3907,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G122" t="n">
-        <v>7.84588432312012</v>
+        <v>7.84588289260864</v>
       </c>
       <c r="H122" t="n">
         <v>536002</v>
@@ -3936,7 +3936,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G123" t="n">
-        <v>7.88233375549316</v>
+        <v>7.88233470916748</v>
       </c>
       <c r="H123" t="n">
         <v>538910</v>
@@ -3965,7 +3965,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G124" t="n">
-        <v>7.4722695350647</v>
+        <v>7.47227001190186</v>
       </c>
       <c r="H124" t="n">
         <v>632439</v>
@@ -3994,7 +3994,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G125" t="n">
-        <v>7.50871992111206</v>
+        <v>7.50872039794922</v>
       </c>
       <c r="H125" t="n">
         <v>1268409</v>
@@ -4023,7 +4023,7 @@
         <v>8.25</v>
       </c>
       <c r="G126" t="n">
-        <v>7.51783275604248</v>
+        <v>7.51783227920532</v>
       </c>
       <c r="H126" t="n">
         <v>811392</v>
@@ -4081,7 +4081,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G128" t="n">
-        <v>7.66363334655762</v>
+        <v>7.6636323928833</v>
       </c>
       <c r="H128" t="n">
         <v>1043426</v>
@@ -4139,7 +4139,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G130" t="n">
-        <v>7.68185758590698</v>
+        <v>7.68185806274414</v>
       </c>
       <c r="H130" t="n">
         <v>174237</v>
@@ -4168,7 +4168,7 @@
         <v>8.34500026702881</v>
       </c>
       <c r="G131" t="n">
-        <v>7.60440158843994</v>
+        <v>7.6044020652771</v>
       </c>
       <c r="H131" t="n">
         <v>317775</v>
@@ -4197,7 +4197,7 @@
         <v>8.24499988555908</v>
       </c>
       <c r="G132" t="n">
-        <v>7.51327610015869</v>
+        <v>7.51327657699585</v>
       </c>
       <c r="H132" t="n">
         <v>292915</v>
@@ -4226,7 +4226,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G133" t="n">
-        <v>7.73653268814087</v>
+        <v>7.73653221130371</v>
       </c>
       <c r="H133" t="n">
         <v>394547</v>
@@ -4255,7 +4255,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G134" t="n">
-        <v>7.67274522781372</v>
+        <v>7.67274570465088</v>
       </c>
       <c r="H134" t="n">
         <v>243583</v>
@@ -4284,7 +4284,7 @@
         <v>8.50500011444092</v>
       </c>
       <c r="G135" t="n">
-        <v>7.75020313262939</v>
+        <v>7.75020408630371</v>
       </c>
       <c r="H135" t="n">
         <v>163424</v>
@@ -4313,7 +4313,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G136" t="n">
-        <v>7.68185758590698</v>
+        <v>7.68185806274414</v>
       </c>
       <c r="H136" t="n">
         <v>270347</v>
@@ -4342,7 +4342,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G137" t="n">
-        <v>7.70919561386108</v>
+        <v>7.7091965675354</v>
       </c>
       <c r="H137" t="n">
         <v>136097</v>
@@ -4371,7 +4371,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G138" t="n">
-        <v>7.70008277893066</v>
+        <v>7.70008325576782</v>
       </c>
       <c r="H138" t="n">
         <v>172356</v>
@@ -4400,7 +4400,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G139" t="n">
-        <v>7.66363334655762</v>
+        <v>7.6636323928833</v>
       </c>
       <c r="H139" t="n">
         <v>207308</v>
@@ -4429,7 +4429,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G140" t="n">
-        <v>7.66363334655762</v>
+        <v>7.6636323928833</v>
       </c>
       <c r="H140" t="n">
         <v>132469</v>
@@ -4487,7 +4487,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G142" t="n">
-        <v>7.96434545516968</v>
+        <v>7.96434640884399</v>
       </c>
       <c r="H142" t="n">
         <v>548934</v>
@@ -4574,7 +4574,7 @@
         <v>8.75</v>
       </c>
       <c r="G145" t="n">
-        <v>7.97345876693726</v>
+        <v>7.97346019744873</v>
       </c>
       <c r="H145" t="n">
         <v>185565</v>
@@ -4632,7 +4632,7 @@
         <v>8.9350004196167</v>
       </c>
       <c r="G147" t="n">
-        <v>8.14204216003418</v>
+        <v>8.14204120635986</v>
       </c>
       <c r="H147" t="n">
         <v>404689</v>
@@ -4661,7 +4661,7 @@
         <v>8.75</v>
       </c>
       <c r="G148" t="n">
-        <v>7.97345876693726</v>
+        <v>7.97346019744873</v>
       </c>
       <c r="H148" t="n">
         <v>364351</v>
@@ -4690,7 +4690,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G149" t="n">
-        <v>8.12837314605713</v>
+        <v>8.12837219238281</v>
       </c>
       <c r="H149" t="n">
         <v>253809</v>
@@ -4719,7 +4719,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G150" t="n">
-        <v>8.11014747619629</v>
+        <v>8.11014556884766</v>
       </c>
       <c r="H150" t="n">
         <v>205684</v>
@@ -4748,7 +4748,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G151" t="n">
-        <v>8.07369613647461</v>
+        <v>8.07369709014893</v>
       </c>
       <c r="H151" t="n">
         <v>235945</v>
@@ -4777,7 +4777,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G152" t="n">
-        <v>7.93700838088989</v>
+        <v>7.93700933456421</v>
       </c>
       <c r="H152" t="n">
         <v>251104</v>
@@ -4806,7 +4806,7 @@
         <v>8.85499954223633</v>
       </c>
       <c r="G153" t="n">
-        <v>8.06914043426514</v>
+        <v>8.06914138793945</v>
       </c>
       <c r="H153" t="n">
         <v>254436</v>
@@ -4835,7 +4835,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G154" t="n">
-        <v>8.14659786224365</v>
+        <v>8.14659595489502</v>
       </c>
       <c r="H154" t="n">
         <v>267284</v>
@@ -4864,7 +4864,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G155" t="n">
-        <v>8.14659786224365</v>
+        <v>8.14659595489502</v>
       </c>
       <c r="H155" t="n">
         <v>283271</v>
@@ -4893,7 +4893,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G156" t="n">
-        <v>8.28328418731689</v>
+        <v>8.28328514099121</v>
       </c>
       <c r="H156" t="n">
         <v>472957</v>
@@ -4951,7 +4951,7 @@
         <v>9.09500026702881</v>
       </c>
       <c r="G158" t="n">
-        <v>8.28783893585205</v>
+        <v>8.28784084320068</v>
       </c>
       <c r="H158" t="n">
         <v>201685</v>
@@ -4980,7 +4980,7 @@
         <v>9.22500038146973</v>
       </c>
       <c r="G159" t="n">
-        <v>8.40630435943604</v>
+        <v>8.40630531311035</v>
       </c>
       <c r="H159" t="n">
         <v>495044</v>
@@ -5038,7 +5038,7 @@
         <v>9.24499988555908</v>
       </c>
       <c r="G161" t="n">
-        <v>8.42452907562256</v>
+        <v>8.42452812194824</v>
       </c>
       <c r="H161" t="n">
         <v>439158</v>
@@ -5096,7 +5096,7 @@
         <v>9.40999984741211</v>
       </c>
       <c r="G163" t="n">
-        <v>8.57488632202148</v>
+        <v>8.57488441467285</v>
       </c>
       <c r="H163" t="n">
         <v>551295</v>
@@ -5125,7 +5125,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G164" t="n">
-        <v>8.68423557281494</v>
+        <v>8.68423461914062</v>
       </c>
       <c r="H164" t="n">
         <v>587842</v>
@@ -5183,7 +5183,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G166" t="n">
-        <v>8.58399868011475</v>
+        <v>8.58400058746338</v>
       </c>
       <c r="H166" t="n">
         <v>296276</v>
@@ -5212,7 +5212,7 @@
         <v>9.34500026702881</v>
       </c>
       <c r="G167" t="n">
-        <v>8.51565456390381</v>
+        <v>8.51565361022949</v>
       </c>
       <c r="H167" t="n">
         <v>418932</v>
@@ -5241,7 +5241,7 @@
         <v>9.24499988555908</v>
       </c>
       <c r="G168" t="n">
-        <v>8.42452907562256</v>
+        <v>8.42452812194824</v>
       </c>
       <c r="H168" t="n">
         <v>343828</v>
@@ -5270,7 +5270,7 @@
         <v>9.22500038146973</v>
       </c>
       <c r="G169" t="n">
-        <v>8.40630435943604</v>
+        <v>8.40630531311035</v>
       </c>
       <c r="H169" t="n">
         <v>254488</v>
@@ -5299,7 +5299,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G170" t="n">
-        <v>8.52021026611328</v>
+        <v>8.52020931243896</v>
       </c>
       <c r="H170" t="n">
         <v>374103</v>
@@ -5357,7 +5357,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G172" t="n">
-        <v>8.50198554992676</v>
+        <v>8.50198364257812</v>
       </c>
       <c r="H172" t="n">
         <v>563561</v>
@@ -5386,7 +5386,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G173" t="n">
-        <v>8.58399868011475</v>
+        <v>8.58400058746338</v>
       </c>
       <c r="H173" t="n">
         <v>317516</v>
@@ -5473,7 +5473,7 @@
         <v>9.40999984741211</v>
       </c>
       <c r="G176" t="n">
-        <v>8.57488632202148</v>
+        <v>8.57488441467285</v>
       </c>
       <c r="H176" t="n">
         <v>195679</v>
@@ -5502,7 +5502,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G177" t="n">
-        <v>8.52932262420654</v>
+        <v>8.52932167053223</v>
       </c>
       <c r="H177" t="n">
         <v>171294</v>
@@ -5560,7 +5560,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G179" t="n">
-        <v>8.36529731750488</v>
+        <v>8.3652982711792</v>
       </c>
       <c r="H179" t="n">
         <v>221326</v>
@@ -5647,7 +5647,7 @@
         <v>9.14500045776367</v>
       </c>
       <c r="G182" t="n">
-        <v>8.33340549468994</v>
+        <v>8.33340454101562</v>
       </c>
       <c r="H182" t="n">
         <v>271932</v>
@@ -5676,7 +5676,7 @@
         <v>9.0649995803833</v>
       </c>
       <c r="G183" t="n">
-        <v>8.26050472259521</v>
+        <v>8.2605037689209</v>
       </c>
       <c r="H183" t="n">
         <v>402522</v>
@@ -5734,7 +5734,7 @@
         <v>9.125</v>
       </c>
       <c r="G185" t="n">
-        <v>8.31517791748047</v>
+        <v>8.31517696380615</v>
       </c>
       <c r="H185" t="n">
         <v>155421</v>
@@ -5763,7 +5763,7 @@
         <v>9.11499977111816</v>
       </c>
       <c r="G186" t="n">
-        <v>8.30606746673584</v>
+        <v>8.30606651306152</v>
       </c>
       <c r="H186" t="n">
         <v>154188</v>
@@ -5821,7 +5821,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G188" t="n">
-        <v>8.27417278289795</v>
+        <v>8.27417182922363</v>
       </c>
       <c r="H188" t="n">
         <v>118030</v>
@@ -5850,7 +5850,7 @@
         <v>9.125</v>
       </c>
       <c r="G189" t="n">
-        <v>8.31517791748047</v>
+        <v>8.31517696380615</v>
       </c>
       <c r="H189" t="n">
         <v>250190</v>
@@ -5908,7 +5908,7 @@
         <v>9.20499992370605</v>
       </c>
       <c r="G191" t="n">
-        <v>8.38807964324951</v>
+        <v>8.3880786895752</v>
       </c>
       <c r="H191" t="n">
         <v>207047</v>
@@ -5937,7 +5937,7 @@
         <v>9.07499980926514</v>
       </c>
       <c r="G192" t="n">
-        <v>8.26961517333984</v>
+        <v>8.26961612701416</v>
       </c>
       <c r="H192" t="n">
         <v>310716</v>
@@ -5995,7 +5995,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G194" t="n">
-        <v>8.50198554992676</v>
+        <v>8.50198364257812</v>
       </c>
       <c r="H194" t="n">
         <v>489594</v>
@@ -6053,7 +6053,7 @@
         <v>9.22500038146973</v>
       </c>
       <c r="G196" t="n">
-        <v>8.40630435943604</v>
+        <v>8.40630531311035</v>
       </c>
       <c r="H196" t="n">
         <v>234943</v>
@@ -6082,7 +6082,7 @@
         <v>9.11499977111816</v>
       </c>
       <c r="G197" t="n">
-        <v>8.30606746673584</v>
+        <v>8.30606651306152</v>
       </c>
       <c r="H197" t="n">
         <v>196094</v>
@@ -6111,7 +6111,7 @@
         <v>9.04500007629395</v>
       </c>
       <c r="G198" t="n">
-        <v>8.24227905273438</v>
+        <v>8.24227809906006</v>
       </c>
       <c r="H198" t="n">
         <v>266136</v>
@@ -6140,7 +6140,7 @@
         <v>9.07499980926514</v>
       </c>
       <c r="G199" t="n">
-        <v>8.26961517333984</v>
+        <v>8.26961612701416</v>
       </c>
       <c r="H199" t="n">
         <v>497449</v>
@@ -6169,7 +6169,7 @@
         <v>9.10999965667725</v>
       </c>
       <c r="G200" t="n">
-        <v>8.3015079498291</v>
+        <v>8.30150985717773</v>
       </c>
       <c r="H200" t="n">
         <v>514708</v>
@@ -6227,7 +6227,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G202" t="n">
-        <v>8.33795833587646</v>
+        <v>8.33795928955078</v>
       </c>
       <c r="H202" t="n">
         <v>464648</v>
@@ -6314,7 +6314,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G205" t="n">
-        <v>8.36529731750488</v>
+        <v>8.3652982711792</v>
       </c>
       <c r="H205" t="n">
         <v>181776</v>
@@ -6343,7 +6343,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G206" t="n">
-        <v>8.36529731750488</v>
+        <v>8.3652982711792</v>
       </c>
       <c r="H206" t="n">
         <v>229481</v>
@@ -6401,7 +6401,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G208" t="n">
-        <v>8.36529731750488</v>
+        <v>8.3652982711792</v>
       </c>
       <c r="H208" t="n">
         <v>182217</v>
@@ -6430,7 +6430,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G209" t="n">
-        <v>8.33795833587646</v>
+        <v>8.33795928955078</v>
       </c>
       <c r="H209" t="n">
         <v>230003</v>
@@ -6459,7 +6459,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G210" t="n">
-        <v>8.33795833587646</v>
+        <v>8.33795928955078</v>
       </c>
       <c r="H210" t="n">
         <v>232109</v>
@@ -6517,7 +6517,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G212" t="n">
-        <v>9.00317573547363</v>
+        <v>9.00317478179932</v>
       </c>
       <c r="H212" t="n">
         <v>992925</v>
@@ -6546,7 +6546,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G213" t="n">
-        <v>8.83003616333008</v>
+        <v>8.83003520965576</v>
       </c>
       <c r="H213" t="n">
         <v>1009620</v>
@@ -6633,7 +6633,7 @@
         <v>9.40999984741211</v>
       </c>
       <c r="G216" t="n">
-        <v>8.57488632202148</v>
+        <v>8.57488441467285</v>
       </c>
       <c r="H216" t="n">
         <v>413946</v>
@@ -6691,7 +6691,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G218" t="n">
-        <v>8.50198554992676</v>
+        <v>8.50198364257812</v>
       </c>
       <c r="H218" t="n">
         <v>394254</v>
@@ -6749,7 +6749,7 @@
         <v>9.22500038146973</v>
       </c>
       <c r="G220" t="n">
-        <v>8.40630435943604</v>
+        <v>8.40630531311035</v>
       </c>
       <c r="H220" t="n">
         <v>480737</v>
@@ -6807,7 +6807,7 @@
         <v>9.11499977111816</v>
       </c>
       <c r="G222" t="n">
-        <v>8.30606746673584</v>
+        <v>8.30606651306152</v>
       </c>
       <c r="H222" t="n">
         <v>506275</v>
@@ -6836,7 +6836,7 @@
         <v>9.08500003814697</v>
       </c>
       <c r="G223" t="n">
-        <v>8.27872848510742</v>
+        <v>8.27872753143311</v>
       </c>
       <c r="H223" t="n">
         <v>354365</v>
@@ -6923,7 +6923,7 @@
         <v>8.97000026702881</v>
       </c>
       <c r="G226" t="n">
-        <v>8.17393589019775</v>
+        <v>8.17393493652344</v>
       </c>
       <c r="H226" t="n">
         <v>341347</v>
@@ -7068,7 +7068,7 @@
         <v>8.91499996185303</v>
       </c>
       <c r="G231" t="n">
-        <v>8.12381458282471</v>
+        <v>8.12381649017334</v>
       </c>
       <c r="H231" t="n">
         <v>407773</v>
@@ -7097,7 +7097,7 @@
         <v>9.0649995803833</v>
       </c>
       <c r="G232" t="n">
-        <v>8.26050472259521</v>
+        <v>8.2605037689209</v>
       </c>
       <c r="H232" t="n">
         <v>148889</v>
@@ -7155,7 +7155,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G234" t="n">
-        <v>8.23772144317627</v>
+        <v>8.23772239685059</v>
       </c>
       <c r="H234" t="n">
         <v>273364</v>
@@ -7213,7 +7213,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G236" t="n">
-        <v>8.24683570861816</v>
+        <v>8.24683380126953</v>
       </c>
       <c r="H236" t="n">
         <v>486715</v>
@@ -7242,7 +7242,7 @@
         <v>9.10999965667725</v>
       </c>
       <c r="G237" t="n">
-        <v>8.3015079498291</v>
+        <v>8.30150985717773</v>
       </c>
       <c r="H237" t="n">
         <v>744477</v>
@@ -7271,7 +7271,7 @@
         <v>9.125</v>
       </c>
       <c r="G238" t="n">
-        <v>8.31517791748047</v>
+        <v>8.31517696380615</v>
       </c>
       <c r="H238" t="n">
         <v>639451</v>
@@ -7358,7 +7358,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G241" t="n">
-        <v>8.82092475891113</v>
+        <v>8.82092380523682</v>
       </c>
       <c r="H241" t="n">
         <v>747306</v>
@@ -7387,7 +7387,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G242" t="n">
-        <v>8.29239749908447</v>
+        <v>8.29239940643311</v>
       </c>
       <c r="H242" t="n">
         <v>2462121</v>
@@ -7416,7 +7416,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G243" t="n">
-        <v>7.94612216949463</v>
+        <v>7.94612121582031</v>
       </c>
       <c r="H243" t="n">
         <v>2648877</v>
@@ -7474,7 +7474,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G245" t="n">
-        <v>7.70919561386108</v>
+        <v>7.7091965675354</v>
       </c>
       <c r="H245" t="n">
         <v>2408111</v>
@@ -7503,7 +7503,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G246" t="n">
-        <v>7.24445724487305</v>
+        <v>7.24445676803589</v>
       </c>
       <c r="H246" t="n">
         <v>3425984</v>
@@ -7532,7 +7532,7 @@
         <v>8.52999973297119</v>
       </c>
       <c r="G247" t="n">
-        <v>7.77298402786255</v>
+        <v>7.77298259735107</v>
       </c>
       <c r="H247" t="n">
         <v>4637885</v>
@@ -7561,7 +7561,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G248" t="n">
-        <v>7.67274522781372</v>
+        <v>7.67274570465088</v>
       </c>
       <c r="H248" t="n">
         <v>1242397</v>
@@ -7590,7 +7590,7 @@
         <v>8.5</v>
       </c>
       <c r="G249" t="n">
-        <v>7.74564552307129</v>
+        <v>7.74564599990845</v>
       </c>
       <c r="H249" t="n">
         <v>1192746</v>
@@ -7677,7 +7677,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G252" t="n">
-        <v>7.88233375549316</v>
+        <v>7.88233470916748</v>
       </c>
       <c r="H252" t="n">
         <v>1417077</v>
@@ -7706,7 +7706,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G253" t="n">
-        <v>8.12837314605713</v>
+        <v>8.12837219238281</v>
       </c>
       <c r="H253" t="n">
         <v>1024617</v>
@@ -7793,7 +7793,7 @@
         <v>9.02499961853027</v>
       </c>
       <c r="G256" t="n">
-        <v>8.22405433654785</v>
+        <v>8.22405338287354</v>
       </c>
       <c r="H256" t="n">
         <v>583724</v>
@@ -7822,7 +7822,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G257" t="n">
-        <v>8.24683570861816</v>
+        <v>8.24683380126953</v>
       </c>
       <c r="H257" t="n">
         <v>340164</v>
@@ -7996,7 +7996,7 @@
         <v>8.94499969482422</v>
       </c>
       <c r="G263" t="n">
-        <v>8.15115261077881</v>
+        <v>8.15115356445312</v>
       </c>
       <c r="H263" t="n">
         <v>537728</v>
@@ -8025,7 +8025,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G264" t="n">
-        <v>8.11014747619629</v>
+        <v>8.11014556884766</v>
       </c>
       <c r="H264" t="n">
         <v>839757</v>
@@ -8054,7 +8054,7 @@
         <v>8.79500007629395</v>
       </c>
       <c r="G265" t="n">
-        <v>8.01446533203125</v>
+        <v>8.01446437835693</v>
       </c>
       <c r="H265" t="n">
         <v>664107</v>
@@ -8083,7 +8083,7 @@
         <v>8.74499988555908</v>
       </c>
       <c r="G266" t="n">
-        <v>7.96890163421631</v>
+        <v>7.96890354156494</v>
       </c>
       <c r="H266" t="n">
         <v>1269447</v>
@@ -8141,7 +8141,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G268" t="n">
-        <v>8.23772144317627</v>
+        <v>8.23772239685059</v>
       </c>
       <c r="H268" t="n">
         <v>780038</v>
@@ -8199,7 +8199,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G270" t="n">
-        <v>8.41997146606445</v>
+        <v>8.41997241973877</v>
       </c>
       <c r="H270" t="n">
         <v>1136948</v>
@@ -8315,7 +8315,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G274" t="n">
-        <v>8.49287128448486</v>
+        <v>8.49287223815918</v>
       </c>
       <c r="H274" t="n">
         <v>305494</v>
@@ -8460,7 +8460,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G279" t="n">
-        <v>8.52932262420654</v>
+        <v>8.52932167053223</v>
       </c>
       <c r="H279" t="n">
         <v>390050</v>
@@ -8489,7 +8489,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G280" t="n">
-        <v>8.83003616333008</v>
+        <v>8.83003520965576</v>
       </c>
       <c r="H280" t="n">
         <v>941306</v>
@@ -8576,7 +8576,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G283" t="n">
-        <v>8.72979736328125</v>
+        <v>8.72979927062988</v>
       </c>
       <c r="H283" t="n">
         <v>373207</v>
@@ -8605,7 +8605,7 @@
         <v>9.76500034332275</v>
       </c>
       <c r="G284" t="n">
-        <v>8.89838123321533</v>
+        <v>8.89838027954102</v>
       </c>
       <c r="H284" t="n">
         <v>295331</v>
@@ -8634,7 +8634,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G285" t="n">
-        <v>9.02139854431152</v>
+        <v>9.02139949798584</v>
       </c>
       <c r="H285" t="n">
         <v>495715</v>
@@ -8663,7 +8663,7 @@
         <v>9.97500038146973</v>
       </c>
       <c r="G286" t="n">
-        <v>9.08974266052246</v>
+        <v>9.08974361419678</v>
       </c>
       <c r="H286" t="n">
         <v>512942</v>
@@ -8692,7 +8692,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G287" t="n">
-        <v>9.1580867767334</v>
+        <v>9.15808773040771</v>
       </c>
       <c r="H287" t="n">
         <v>455330</v>
@@ -8721,7 +8721,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G288" t="n">
-        <v>9.13074970245361</v>
+        <v>9.13075065612793</v>
       </c>
       <c r="H288" t="n">
         <v>866361</v>
@@ -8750,7 +8750,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G289" t="n">
-        <v>9.04873657226562</v>
+        <v>9.04873752593994</v>
       </c>
       <c r="H289" t="n">
         <v>751516</v>
@@ -8779,7 +8779,7 @@
         <v>10</v>
       </c>
       <c r="G290" t="n">
-        <v>9.11252593994141</v>
+        <v>9.11252307891846</v>
       </c>
       <c r="H290" t="n">
         <v>459937</v>
@@ -8808,7 +8808,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G291" t="n">
-        <v>9.04873657226562</v>
+        <v>9.04873752593994</v>
       </c>
       <c r="H291" t="n">
         <v>276786</v>
@@ -8924,7 +8924,7 @@
         <v>9.99499988555908</v>
       </c>
       <c r="G295" t="n">
-        <v>9.1079683303833</v>
+        <v>9.10796737670898</v>
       </c>
       <c r="H295" t="n">
         <v>331577</v>
@@ -8982,7 +8982,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G297" t="n">
-        <v>8.86648654937744</v>
+        <v>8.86648750305176</v>
       </c>
       <c r="H297" t="n">
         <v>267140</v>
@@ -9040,7 +9040,7 @@
         <v>10.1099996566772</v>
       </c>
       <c r="G299" t="n">
-        <v>9.2127628326416</v>
+        <v>9.21276187896729</v>
       </c>
       <c r="H299" t="n">
         <v>390202</v>
@@ -9069,7 +9069,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G300" t="n">
-        <v>9.54992580413818</v>
+        <v>9.54992485046387</v>
       </c>
       <c r="H300" t="n">
         <v>752475</v>
@@ -9127,7 +9127,7 @@
         <v>10.5</v>
       </c>
       <c r="G302" t="n">
-        <v>9.56815052032471</v>
+        <v>9.56815242767334</v>
       </c>
       <c r="H302" t="n">
         <v>392036</v>
@@ -9156,7 +9156,7 @@
         <v>10.5</v>
       </c>
       <c r="G303" t="n">
-        <v>9.56815052032471</v>
+        <v>9.56815242767334</v>
       </c>
       <c r="H303" t="n">
         <v>298983</v>
@@ -9214,7 +9214,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G305" t="n">
-        <v>9.38590049743652</v>
+        <v>9.38590145111084</v>
       </c>
       <c r="H305" t="n">
         <v>524742</v>
@@ -9330,7 +9330,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G309" t="n">
-        <v>9.53170108795166</v>
+        <v>9.53170013427734</v>
       </c>
       <c r="H309" t="n">
         <v>255003</v>
@@ -9388,7 +9388,7 @@
         <v>10.6899995803833</v>
       </c>
       <c r="G311" t="n">
-        <v>9.74128818511963</v>
+        <v>9.74128913879395</v>
       </c>
       <c r="H311" t="n">
         <v>299410</v>
@@ -9446,7 +9446,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G313" t="n">
-        <v>9.96910095214844</v>
+        <v>9.96910190582275</v>
       </c>
       <c r="H313" t="n">
         <v>277760</v>
@@ -9504,7 +9504,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G315" t="n">
-        <v>10.1513519287109</v>
+        <v>10.1513528823853</v>
       </c>
       <c r="H315" t="n">
         <v>420947</v>
@@ -9533,7 +9533,7 @@
         <v>11.1899995803833</v>
       </c>
       <c r="G316" t="n">
-        <v>10.1969146728516</v>
+        <v>10.1969137191772</v>
       </c>
       <c r="H316" t="n">
         <v>401559</v>
@@ -9562,7 +9562,7 @@
         <v>11.0699996948242</v>
       </c>
       <c r="G317" t="n">
-        <v>10.0875654220581</v>
+        <v>10.0875635147095</v>
       </c>
       <c r="H317" t="n">
         <v>370875</v>
@@ -9591,7 +9591,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G318" t="n">
-        <v>10.060227394104</v>
+        <v>10.0602264404297</v>
       </c>
       <c r="H318" t="n">
         <v>380987</v>
@@ -9678,7 +9678,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G321" t="n">
-        <v>10.2242527008057</v>
+        <v>10.2242517471313</v>
       </c>
       <c r="H321" t="n">
         <v>287306</v>
@@ -9765,7 +9765,7 @@
         <v>11.6300001144409</v>
       </c>
       <c r="G324" t="n">
-        <v>10.5978670120239</v>
+        <v>10.5978660583496</v>
       </c>
       <c r="H324" t="n">
         <v>516773</v>
@@ -9852,7 +9852,7 @@
         <v>11.3699998855591</v>
       </c>
       <c r="G327" t="n">
-        <v>10.3609399795532</v>
+        <v>10.3609418869019</v>
       </c>
       <c r="H327" t="n">
         <v>231720</v>
@@ -9881,7 +9881,7 @@
         <v>11.3699998855591</v>
       </c>
       <c r="G328" t="n">
-        <v>10.3609399795532</v>
+        <v>10.3609418869019</v>
       </c>
       <c r="H328" t="n">
         <v>366667</v>
@@ -9910,7 +9910,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G329" t="n">
-        <v>10.342716217041</v>
+        <v>10.3427171707153</v>
       </c>
       <c r="H329" t="n">
         <v>218443</v>
@@ -9939,7 +9939,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G330" t="n">
-        <v>10.424729347229</v>
+        <v>10.4247274398804</v>
       </c>
       <c r="H330" t="n">
         <v>221139</v>
@@ -9997,7 +9997,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G332" t="n">
-        <v>10.6069774627686</v>
+        <v>10.6069765090942</v>
       </c>
       <c r="H332" t="n">
         <v>302779</v>
@@ -10026,7 +10026,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G333" t="n">
-        <v>10.552303314209</v>
+        <v>10.5523023605347</v>
       </c>
       <c r="H333" t="n">
         <v>298694</v>
@@ -10055,7 +10055,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G334" t="n">
-        <v>10.6434297561646</v>
+        <v>10.6434288024902</v>
       </c>
       <c r="H334" t="n">
         <v>435443</v>
@@ -10258,7 +10258,7 @@
         <v>11.9700002670288</v>
       </c>
       <c r="G341" t="n">
-        <v>10.9076929092407</v>
+        <v>10.9076919555664</v>
       </c>
       <c r="H341" t="n">
         <v>647523</v>
@@ -10345,7 +10345,7 @@
         <v>11.9099998474121</v>
       </c>
       <c r="G344" t="n">
-        <v>10.8530149459839</v>
+        <v>10.8530168533325</v>
       </c>
       <c r="H344" t="n">
         <v>477041</v>
@@ -10403,7 +10403,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G346" t="n">
-        <v>10.8894653320312</v>
+        <v>10.8894662857056</v>
       </c>
       <c r="H346" t="n">
         <v>399692</v>
@@ -10432,7 +10432,7 @@
         <v>11.9700002670288</v>
       </c>
       <c r="G347" t="n">
-        <v>10.9076929092407</v>
+        <v>10.9076919555664</v>
       </c>
       <c r="H347" t="n">
         <v>370654</v>
@@ -10490,7 +10490,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G349" t="n">
-        <v>10.9805936813354</v>
+        <v>10.9805917739868</v>
       </c>
       <c r="H349" t="n">
         <v>270298</v>
@@ -10519,7 +10519,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G350" t="n">
-        <v>10.9805936813354</v>
+        <v>10.9805917739868</v>
       </c>
       <c r="H350" t="n">
         <v>218300</v>
@@ -10577,7 +10577,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G352" t="n">
-        <v>10.8894653320312</v>
+        <v>10.8894662857056</v>
       </c>
       <c r="H352" t="n">
         <v>556240</v>
@@ -10664,7 +10664,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G355" t="n">
-        <v>11.272873878479</v>
+        <v>11.2728748321533</v>
       </c>
       <c r="H355" t="n">
         <v>333523</v>
@@ -10693,7 +10693,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G356" t="n">
-        <v>11.5111646652222</v>
+        <v>11.5111637115479</v>
       </c>
       <c r="H356" t="n">
         <v>316194</v>
@@ -10722,7 +10722,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G357" t="n">
-        <v>11.5478229522705</v>
+        <v>11.5478239059448</v>
       </c>
       <c r="H357" t="n">
         <v>337438</v>
@@ -10751,7 +10751,7 @@
         <v>12.6899995803833</v>
       </c>
       <c r="G358" t="n">
-        <v>11.6303081512451</v>
+        <v>11.6303071975708</v>
       </c>
       <c r="H358" t="n">
         <v>711596</v>
@@ -10780,7 +10780,7 @@
         <v>12.6899995803833</v>
       </c>
       <c r="G359" t="n">
-        <v>11.6303081512451</v>
+        <v>11.6303071975708</v>
       </c>
       <c r="H359" t="n">
         <v>549072</v>
@@ -10838,7 +10838,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G361" t="n">
-        <v>11.6119775772095</v>
+        <v>11.6119766235352</v>
       </c>
       <c r="H361" t="n">
         <v>531814</v>
@@ -10867,7 +10867,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G362" t="n">
-        <v>11.6211414337158</v>
+        <v>11.6211423873901</v>
       </c>
       <c r="H362" t="n">
         <v>527700</v>
@@ -10925,7 +10925,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G364" t="n">
-        <v>11.7402858734131</v>
+        <v>11.7402868270874</v>
       </c>
       <c r="H364" t="n">
         <v>465952</v>
@@ -10954,7 +10954,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G365" t="n">
-        <v>11.7769460678101</v>
+        <v>11.7769470214844</v>
       </c>
       <c r="H365" t="n">
         <v>290469</v>
@@ -11012,7 +11012,7 @@
         <v>12.9700002670288</v>
       </c>
       <c r="G367" t="n">
-        <v>11.886923789978</v>
+        <v>11.886926651001</v>
       </c>
       <c r="H367" t="n">
         <v>306712</v>
@@ -11041,7 +11041,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G368" t="n">
-        <v>11.8594303131104</v>
+        <v>11.859432220459</v>
       </c>
       <c r="H368" t="n">
         <v>312096</v>
@@ -11099,7 +11099,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G370" t="n">
-        <v>11.5936479568481</v>
+        <v>11.5936470031738</v>
       </c>
       <c r="H370" t="n">
         <v>680831</v>
@@ -11157,7 +11157,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G372" t="n">
-        <v>11.1812257766724</v>
+        <v>11.181224822998</v>
       </c>
       <c r="H372" t="n">
         <v>7618194</v>
@@ -11186,7 +11186,7 @@
         <v>12</v>
       </c>
       <c r="G373" t="n">
-        <v>10.9979257583618</v>
+        <v>10.9979267120361</v>
       </c>
       <c r="H373" t="n">
         <v>881664</v>
@@ -11244,7 +11244,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G375" t="n">
-        <v>11.4195137023926</v>
+        <v>11.4195117950439</v>
       </c>
       <c r="H375" t="n">
         <v>551385</v>
@@ -11273,7 +11273,7 @@
         <v>12.5</v>
       </c>
       <c r="G376" t="n">
-        <v>11.4561729431152</v>
+        <v>11.4561719894409</v>
       </c>
       <c r="H376" t="n">
         <v>1170218</v>
@@ -11302,7 +11302,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G377" t="n">
-        <v>11.4470071792603</v>
+        <v>11.4470081329346</v>
       </c>
       <c r="H377" t="n">
         <v>529348</v>
@@ -11331,7 +11331,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G378" t="n">
-        <v>11.3186988830566</v>
+        <v>11.318699836731</v>
       </c>
       <c r="H378" t="n">
         <v>681227</v>
@@ -11360,7 +11360,7 @@
         <v>12.289999961853</v>
       </c>
       <c r="G379" t="n">
-        <v>11.2637100219727</v>
+        <v>11.2637090682983</v>
       </c>
       <c r="H379" t="n">
         <v>391619</v>
@@ -11389,7 +11389,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G380" t="n">
-        <v>11.2178840637207</v>
+        <v>11.217885017395</v>
       </c>
       <c r="H380" t="n">
         <v>441991</v>
@@ -11447,7 +11447,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G382" t="n">
-        <v>11.0712451934814</v>
+        <v>11.0712461471558</v>
       </c>
       <c r="H382" t="n">
         <v>670650</v>
@@ -11476,7 +11476,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G383" t="n">
-        <v>10.7871322631836</v>
+        <v>10.7871332168579</v>
       </c>
       <c r="H383" t="n">
         <v>375515</v>
@@ -11505,7 +11505,7 @@
         <v>11.5600004196167</v>
       </c>
       <c r="G384" t="n">
-        <v>10.5946683883667</v>
+        <v>10.594669342041</v>
       </c>
       <c r="H384" t="n">
         <v>511403</v>
@@ -11621,7 +11621,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G388" t="n">
-        <v>10.4571943283081</v>
+        <v>10.4571952819824</v>
       </c>
       <c r="H388" t="n">
         <v>737198</v>
@@ -11679,7 +11679,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G390" t="n">
-        <v>10.6129989624023</v>
+        <v>10.612998008728</v>
       </c>
       <c r="H390" t="n">
         <v>328953</v>
@@ -11766,7 +11766,7 @@
         <v>12</v>
       </c>
       <c r="G393" t="n">
-        <v>10.9979257583618</v>
+        <v>10.9979267120361</v>
       </c>
       <c r="H393" t="n">
         <v>661500</v>
@@ -11824,7 +11824,7 @@
         <v>12.1700000762939</v>
       </c>
       <c r="G395" t="n">
-        <v>11.1537313461304</v>
+        <v>11.1537303924561</v>
       </c>
       <c r="H395" t="n">
         <v>248958</v>
@@ -11882,7 +11882,7 @@
         <v>12.1700000762939</v>
       </c>
       <c r="G397" t="n">
-        <v>11.1537313461304</v>
+        <v>11.1537303924561</v>
       </c>
       <c r="H397" t="n">
         <v>332694</v>
@@ -11911,7 +11911,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G398" t="n">
-        <v>11.0437517166138</v>
+        <v>11.0437507629395</v>
       </c>
       <c r="H398" t="n">
         <v>291058</v>
@@ -11940,7 +11940,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G399" t="n">
-        <v>11.1079044342041</v>
+        <v>11.1079053878784</v>
       </c>
       <c r="H399" t="n">
         <v>292003</v>
@@ -11969,7 +11969,7 @@
         <v>12.1700000762939</v>
       </c>
       <c r="G400" t="n">
-        <v>11.1537313461304</v>
+        <v>11.1537303924561</v>
       </c>
       <c r="H400" t="n">
         <v>229290</v>
@@ -12056,7 +12056,7 @@
         <v>12</v>
       </c>
       <c r="G403" t="n">
-        <v>10.9979257583618</v>
+        <v>10.9979267120361</v>
       </c>
       <c r="H403" t="n">
         <v>268306</v>
@@ -12085,7 +12085,7 @@
         <v>12</v>
       </c>
       <c r="G404" t="n">
-        <v>10.9979257583618</v>
+        <v>10.9979267120361</v>
       </c>
       <c r="H404" t="n">
         <v>240257</v>
@@ -12172,7 +12172,7 @@
         <v>12.1700000762939</v>
       </c>
       <c r="G407" t="n">
-        <v>11.1537313461304</v>
+        <v>11.1537303924561</v>
       </c>
       <c r="H407" t="n">
         <v>246249</v>
@@ -12230,7 +12230,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G409" t="n">
-        <v>10.9521007537842</v>
+        <v>10.9521017074585</v>
       </c>
       <c r="H409" t="n">
         <v>301472</v>
@@ -12259,7 +12259,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G410" t="n">
-        <v>10.8146286010742</v>
+        <v>10.8146276473999</v>
       </c>
       <c r="H410" t="n">
         <v>280628</v>
@@ -12288,7 +12288,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G411" t="n">
-        <v>10.8146286010742</v>
+        <v>10.8146276473999</v>
       </c>
       <c r="H411" t="n">
         <v>353877</v>
@@ -12375,7 +12375,7 @@
         <v>11.3299999237061</v>
       </c>
       <c r="G414" t="n">
-        <v>10.3838739395142</v>
+        <v>10.3838758468628</v>
       </c>
       <c r="H414" t="n">
         <v>401583</v>
@@ -12404,7 +12404,7 @@
         <v>11.5100002288818</v>
       </c>
       <c r="G415" t="n">
-        <v>10.5488433837891</v>
+        <v>10.5488443374634</v>
       </c>
       <c r="H415" t="n">
         <v>479102</v>
@@ -12462,7 +12462,7 @@
         <v>11.8900003433228</v>
       </c>
       <c r="G417" t="n">
-        <v>10.8971128463745</v>
+        <v>10.8971118927002</v>
       </c>
       <c r="H417" t="n">
         <v>518914</v>
@@ -12491,7 +12491,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G418" t="n">
-        <v>10.8696174621582</v>
+        <v>10.8696155548096</v>
       </c>
       <c r="H418" t="n">
         <v>572906</v>
@@ -12578,7 +12578,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G421" t="n">
-        <v>11.0162563323975</v>
+        <v>11.0162553787231</v>
       </c>
       <c r="H421" t="n">
         <v>310610</v>
@@ -12636,7 +12636,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G423" t="n">
-        <v>10.9429368972778</v>
+        <v>10.9429359436035</v>
       </c>
       <c r="H423" t="n">
         <v>151173</v>
@@ -12694,7 +12694,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G425" t="n">
-        <v>10.7962970733643</v>
+        <v>10.7962980270386</v>
       </c>
       <c r="H425" t="n">
         <v>384245</v>
@@ -12723,7 +12723,7 @@
         <v>11.8699998855591</v>
       </c>
       <c r="G426" t="n">
-        <v>10.8787803649902</v>
+        <v>10.8787813186646</v>
       </c>
       <c r="H426" t="n">
         <v>135871</v>
@@ -12781,7 +12781,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G428" t="n">
-        <v>11.4103479385376</v>
+        <v>11.4103469848633</v>
       </c>
       <c r="H428" t="n">
         <v>666349</v>
@@ -12839,7 +12839,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G430" t="n">
-        <v>11.4470071792603</v>
+        <v>11.4470081329346</v>
       </c>
       <c r="H430" t="n">
         <v>520128</v>
@@ -12897,7 +12897,7 @@
         <v>12.6899995803833</v>
       </c>
       <c r="G432" t="n">
-        <v>11.6303081512451</v>
+        <v>11.6303071975708</v>
       </c>
       <c r="H432" t="n">
         <v>538292</v>
@@ -12926,7 +12926,7 @@
         <v>12.7299995422363</v>
       </c>
       <c r="G433" t="n">
-        <v>11.6669635772705</v>
+        <v>11.6669664382935</v>
       </c>
       <c r="H433" t="n">
         <v>332312</v>
@@ -12955,7 +12955,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G434" t="n">
-        <v>11.5936479568481</v>
+        <v>11.5936470031738</v>
       </c>
       <c r="H434" t="n">
         <v>262413</v>
@@ -12984,7 +12984,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G435" t="n">
-        <v>11.6944608688354</v>
+        <v>11.6944618225098</v>
       </c>
       <c r="H435" t="n">
         <v>379109</v>
@@ -13100,7 +13100,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G439" t="n">
-        <v>11.7586154937744</v>
+        <v>11.7586145401001</v>
       </c>
       <c r="H439" t="n">
         <v>440079</v>
@@ -13129,7 +13129,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G440" t="n">
-        <v>11.6578016281128</v>
+        <v>11.6578006744385</v>
       </c>
       <c r="H440" t="n">
         <v>263385</v>
@@ -13216,7 +13216,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G443" t="n">
-        <v>11.7586154937744</v>
+        <v>11.7586145401001</v>
       </c>
       <c r="H443" t="n">
         <v>249369</v>
@@ -13274,7 +13274,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G445" t="n">
-        <v>11.896089553833</v>
+        <v>11.8960905075073</v>
       </c>
       <c r="H445" t="n">
         <v>264823</v>
@@ -13332,7 +13332,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G447" t="n">
-        <v>11.896089553833</v>
+        <v>11.8960905075073</v>
       </c>
       <c r="H447" t="n">
         <v>262220</v>
@@ -13361,7 +13361,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G448" t="n">
-        <v>11.7861099243164</v>
+        <v>11.7861108779907</v>
       </c>
       <c r="H448" t="n">
         <v>563606</v>
@@ -13419,7 +13419,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G450" t="n">
-        <v>12.1893692016602</v>
+        <v>12.1893672943115</v>
       </c>
       <c r="H450" t="n">
         <v>501652</v>
@@ -13448,7 +13448,7 @@
         <v>13.4300003051758</v>
       </c>
       <c r="G451" t="n">
-        <v>12.3085126876831</v>
+        <v>12.3085117340088</v>
       </c>
       <c r="H451" t="n">
         <v>362656</v>
@@ -13506,7 +13506,7 @@
         <v>13.6099996566772</v>
       </c>
       <c r="G453" t="n">
-        <v>12.473482131958</v>
+        <v>12.4734811782837</v>
       </c>
       <c r="H453" t="n">
         <v>314493</v>
@@ -13709,7 +13709,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G460" t="n">
-        <v>11.7861099243164</v>
+        <v>11.7861108779907</v>
       </c>
       <c r="H460" t="n">
         <v>292356</v>
@@ -13738,7 +13738,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G461" t="n">
-        <v>11.7769460678101</v>
+        <v>11.7769470214844</v>
       </c>
       <c r="H461" t="n">
         <v>196373</v>
@@ -13796,7 +13796,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G463" t="n">
-        <v>11.4195137023926</v>
+        <v>11.4195117950439</v>
       </c>
       <c r="H463" t="n">
         <v>441079</v>
@@ -13825,7 +13825,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G464" t="n">
-        <v>11.272873878479</v>
+        <v>11.2728748321533</v>
       </c>
       <c r="H464" t="n">
         <v>522934</v>
@@ -13854,7 +13854,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G465" t="n">
-        <v>11.5386581420898</v>
+        <v>11.5386571884155</v>
       </c>
       <c r="H465" t="n">
         <v>434732</v>
@@ -13883,7 +13883,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G466" t="n">
-        <v>11.4195137023926</v>
+        <v>11.4195117950439</v>
       </c>
       <c r="H466" t="n">
         <v>1223412</v>
@@ -13970,7 +13970,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G469" t="n">
-        <v>11.896089553833</v>
+        <v>11.8960905075073</v>
       </c>
       <c r="H469" t="n">
         <v>212043</v>
@@ -14028,7 +14028,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G471" t="n">
-        <v>11.7586154937744</v>
+        <v>11.7586145401001</v>
       </c>
       <c r="H471" t="n">
         <v>170866</v>
@@ -14057,7 +14057,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G472" t="n">
-        <v>11.5844831466675</v>
+        <v>11.5844841003418</v>
       </c>
       <c r="H472" t="n">
         <v>327472</v>
@@ -14086,7 +14086,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G473" t="n">
-        <v>11.6119775772095</v>
+        <v>11.6119766235352</v>
       </c>
       <c r="H473" t="n">
         <v>286619</v>
@@ -14115,7 +14115,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G474" t="n">
-        <v>11.6119775772095</v>
+        <v>11.6119766235352</v>
       </c>
       <c r="H474" t="n">
         <v>377291</v>
@@ -14144,7 +14144,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G475" t="n">
-        <v>11.5936479568481</v>
+        <v>11.5936470031738</v>
       </c>
       <c r="H475" t="n">
         <v>347028</v>
@@ -14173,7 +14173,7 @@
         <v>12.7299995422363</v>
       </c>
       <c r="G476" t="n">
-        <v>11.6669635772705</v>
+        <v>11.6669664382935</v>
       </c>
       <c r="H476" t="n">
         <v>464654</v>
@@ -14202,7 +14202,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G477" t="n">
-        <v>11.4470071792603</v>
+        <v>11.4470081329346</v>
       </c>
       <c r="H477" t="n">
         <v>567106</v>
@@ -14231,7 +14231,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G478" t="n">
-        <v>11.1445646286011</v>
+        <v>11.1445655822754</v>
       </c>
       <c r="H478" t="n">
         <v>593467</v>
@@ -14260,7 +14260,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G479" t="n">
-        <v>11.272873878479</v>
+        <v>11.2728748321533</v>
       </c>
       <c r="H479" t="n">
         <v>434416</v>
@@ -14289,7 +14289,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G480" t="n">
-        <v>11.254545211792</v>
+        <v>11.2545442581177</v>
       </c>
       <c r="H480" t="n">
         <v>485178</v>
@@ -14318,7 +14318,7 @@
         <v>12.1099996566772</v>
       </c>
       <c r="G481" t="n">
-        <v>11.0987386703491</v>
+        <v>11.0987396240234</v>
       </c>
       <c r="H481" t="n">
         <v>320910</v>
@@ -14376,7 +14376,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G483" t="n">
-        <v>11.4103479385376</v>
+        <v>11.4103469848633</v>
       </c>
       <c r="H483" t="n">
         <v>473801</v>
@@ -14405,7 +14405,7 @@
         <v>12.5100002288818</v>
       </c>
       <c r="G484" t="n">
-        <v>11.4653387069702</v>
+        <v>11.4653377532959</v>
       </c>
       <c r="H484" t="n">
         <v>266150</v>
@@ -14434,7 +14434,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G485" t="n">
-        <v>11.7677803039551</v>
+        <v>11.7677812576294</v>
       </c>
       <c r="H485" t="n">
         <v>280681</v>
@@ -14521,7 +14521,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G488" t="n">
-        <v>11.8777599334717</v>
+        <v>11.8777618408203</v>
       </c>
       <c r="H488" t="n">
         <v>486058</v>
@@ -14637,7 +14637,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G492" t="n">
-        <v>12.0335645675659</v>
+        <v>12.0335636138916</v>
       </c>
       <c r="H492" t="n">
         <v>525882</v>
@@ -14695,7 +14695,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G494" t="n">
-        <v>11.8594303131104</v>
+        <v>11.859432220459</v>
       </c>
       <c r="H494" t="n">
         <v>339861</v>
@@ -14782,7 +14782,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G497" t="n">
-        <v>11.7769460678101</v>
+        <v>11.7769470214844</v>
       </c>
       <c r="H497" t="n">
         <v>223529</v>
@@ -14811,7 +14811,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G498" t="n">
-        <v>12.0060682296753</v>
+        <v>12.0060691833496</v>
       </c>
       <c r="H498" t="n">
         <v>252211</v>
@@ -14898,7 +14898,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G501" t="n">
-        <v>11.8410987854004</v>
+        <v>11.841100692749</v>
       </c>
       <c r="H501" t="n">
         <v>196697</v>
@@ -14927,7 +14927,7 @@
         <v>12.5100002288818</v>
       </c>
       <c r="G502" t="n">
-        <v>11.4653387069702</v>
+        <v>11.4653377532959</v>
       </c>
       <c r="H502" t="n">
         <v>432814</v>
@@ -15014,7 +15014,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G505" t="n">
-        <v>11.5111646652222</v>
+        <v>11.5111637115479</v>
       </c>
       <c r="H505" t="n">
         <v>306696</v>
@@ -15043,7 +15043,7 @@
         <v>12.5</v>
       </c>
       <c r="G506" t="n">
-        <v>11.4561729431152</v>
+        <v>11.4561719894409</v>
       </c>
       <c r="H506" t="n">
         <v>287468</v>
@@ -15101,7 +15101,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G508" t="n">
-        <v>11.8044404983521</v>
+        <v>11.8044414520264</v>
       </c>
       <c r="H508" t="n">
         <v>327923</v>
@@ -15159,7 +15159,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G510" t="n">
-        <v>12.0060682296753</v>
+        <v>12.0060691833496</v>
       </c>
       <c r="H510" t="n">
         <v>352907</v>
@@ -15188,7 +15188,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G511" t="n">
-        <v>11.7677803039551</v>
+        <v>11.7677812576294</v>
       </c>
       <c r="H511" t="n">
         <v>205866</v>
@@ -15217,7 +15217,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G512" t="n">
-        <v>11.8410987854004</v>
+        <v>11.841100692749</v>
       </c>
       <c r="H512" t="n">
         <v>235973</v>
@@ -15246,7 +15246,7 @@
         <v>12.9700002670288</v>
       </c>
       <c r="G513" t="n">
-        <v>11.886923789978</v>
+        <v>11.886926651001</v>
       </c>
       <c r="H513" t="n">
         <v>207250</v>
@@ -15275,7 +15275,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G514" t="n">
-        <v>12.2076978683472</v>
+        <v>12.2076969146729</v>
       </c>
       <c r="H514" t="n">
         <v>380385</v>
@@ -15304,7 +15304,7 @@
         <v>13.3299999237061</v>
       </c>
       <c r="G515" t="n">
-        <v>12.2168617248535</v>
+        <v>12.2168626785278</v>
       </c>
       <c r="H515" t="n">
         <v>354817</v>
@@ -15333,7 +15333,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G516" t="n">
-        <v>12.1710367202759</v>
+        <v>12.1710376739502</v>
       </c>
       <c r="H516" t="n">
         <v>208904</v>
@@ -15362,7 +15362,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G517" t="n">
-        <v>12.2993488311768</v>
+        <v>12.2993469238281</v>
       </c>
       <c r="H517" t="n">
         <v>354241</v>
@@ -15507,7 +15507,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G522" t="n">
-        <v>12.7392644882202</v>
+        <v>12.7392625808716</v>
       </c>
       <c r="H522" t="n">
         <v>360660</v>
@@ -15536,7 +15536,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G523" t="n">
-        <v>12.6109561920166</v>
+        <v>12.6109571456909</v>
       </c>
       <c r="H523" t="n">
         <v>346966</v>
@@ -15594,7 +15594,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G525" t="n">
-        <v>13.06920337677</v>
+        <v>13.0692014694214</v>
       </c>
       <c r="H525" t="n">
         <v>564071</v>
@@ -15623,7 +15623,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G526" t="n">
-        <v>13.1058626174927</v>
+        <v>13.1058616638184</v>
       </c>
       <c r="H526" t="n">
         <v>630337</v>
@@ -15652,7 +15652,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G527" t="n">
-        <v>13.1058626174927</v>
+        <v>13.1058616638184</v>
       </c>
       <c r="H527" t="n">
         <v>400242</v>
@@ -15681,7 +15681,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G528" t="n">
-        <v>13.1791801452637</v>
+        <v>13.1791820526123</v>
       </c>
       <c r="H528" t="n">
         <v>351654</v>
@@ -15710,7 +15710,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G529" t="n">
-        <v>13.197509765625</v>
+        <v>13.1975126266479</v>
       </c>
       <c r="H529" t="n">
         <v>302848</v>
@@ -15739,7 +15739,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G530" t="n">
-        <v>13.2433347702026</v>
+        <v>13.2433366775513</v>
       </c>
       <c r="H530" t="n">
         <v>458884</v>
@@ -15884,7 +15884,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G535" t="n">
-        <v>12.6292839050293</v>
+        <v>12.6292848587036</v>
       </c>
       <c r="H535" t="n">
         <v>437204</v>
@@ -15913,7 +15913,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G536" t="n">
-        <v>12.2810182571411</v>
+        <v>12.2810173034668</v>
       </c>
       <c r="H536" t="n">
         <v>487602</v>
@@ -15942,7 +15942,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G537" t="n">
-        <v>12.0793886184692</v>
+        <v>12.0793876647949</v>
       </c>
       <c r="H537" t="n">
         <v>780711</v>
@@ -15971,7 +15971,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G538" t="n">
-        <v>12.2810182571411</v>
+        <v>12.2810173034668</v>
       </c>
       <c r="H538" t="n">
         <v>594812</v>
@@ -16029,7 +16029,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G540" t="n">
-        <v>11.7861099243164</v>
+        <v>11.7861108779907</v>
       </c>
       <c r="H540" t="n">
         <v>438376</v>
@@ -16087,7 +16087,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G542" t="n">
-        <v>12.1343784332275</v>
+        <v>12.1343793869019</v>
       </c>
       <c r="H542" t="n">
         <v>396961</v>
@@ -16145,7 +16145,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G544" t="n">
-        <v>12.48264503479</v>
+        <v>12.4826459884644</v>
       </c>
       <c r="H544" t="n">
         <v>200313</v>
@@ -16174,7 +16174,7 @@
         <v>13.6800003051758</v>
       </c>
       <c r="G545" t="n">
-        <v>12.5376358032227</v>
+        <v>12.537636756897</v>
       </c>
       <c r="H545" t="n">
         <v>198835</v>
@@ -16203,7 +16203,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G546" t="n">
-        <v>12.5101404190063</v>
+        <v>12.5101413726807</v>
       </c>
       <c r="H546" t="n">
         <v>89479</v>
@@ -16232,7 +16232,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G547" t="n">
-        <v>12.2626886367798</v>
+        <v>12.2626876831055</v>
       </c>
       <c r="H547" t="n">
         <v>303843</v>
@@ -16261,7 +16261,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G548" t="n">
-        <v>12.2993488311768</v>
+        <v>12.2993469238281</v>
       </c>
       <c r="H548" t="n">
         <v>240897</v>
@@ -16290,7 +16290,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G549" t="n">
-        <v>12.1343784332275</v>
+        <v>12.1343793869019</v>
       </c>
       <c r="H549" t="n">
         <v>199368</v>
@@ -16319,7 +16319,7 @@
         <v>12.9700002670288</v>
       </c>
       <c r="G550" t="n">
-        <v>11.886923789978</v>
+        <v>11.886926651001</v>
       </c>
       <c r="H550" t="n">
         <v>492590</v>
@@ -16348,7 +16348,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G551" t="n">
-        <v>12.0335645675659</v>
+        <v>12.0335636138916</v>
       </c>
       <c r="H551" t="n">
         <v>298107</v>
@@ -16377,7 +16377,7 @@
         <v>12.9700002670288</v>
       </c>
       <c r="G552" t="n">
-        <v>11.886923789978</v>
+        <v>11.886926651001</v>
       </c>
       <c r="H552" t="n">
         <v>271753</v>
@@ -16406,7 +16406,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G553" t="n">
-        <v>11.960244178772</v>
+        <v>11.9602451324463</v>
       </c>
       <c r="H553" t="n">
         <v>390827</v>
@@ -16435,7 +16435,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G554" t="n">
-        <v>11.9327507019043</v>
+        <v>11.93274974823</v>
       </c>
       <c r="H554" t="n">
         <v>848951</v>
@@ -16464,7 +16464,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G555" t="n">
-        <v>12.0793886184692</v>
+        <v>12.0793876647949</v>
       </c>
       <c r="H555" t="n">
         <v>541293</v>
@@ -16493,7 +16493,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G556" t="n">
-        <v>11.960244178772</v>
+        <v>11.9602451324463</v>
       </c>
       <c r="H556" t="n">
         <v>312364</v>
@@ -16522,7 +16522,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G557" t="n">
-        <v>12.3909959793091</v>
+        <v>12.3909969329834</v>
       </c>
       <c r="H557" t="n">
         <v>365559</v>
@@ -16551,7 +16551,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G558" t="n">
-        <v>12.6934404373169</v>
+        <v>12.6934394836426</v>
       </c>
       <c r="H558" t="n">
         <v>379344</v>
@@ -16580,7 +16580,7 @@
         <v>13.9099998474121</v>
       </c>
       <c r="G559" t="n">
-        <v>12.7484283447266</v>
+        <v>12.7484273910522</v>
       </c>
       <c r="H559" t="n">
         <v>255107</v>
@@ -16609,7 +16609,7 @@
         <v>14.0900001525879</v>
       </c>
       <c r="G560" t="n">
-        <v>12.9133977890015</v>
+        <v>12.9133987426758</v>
       </c>
       <c r="H560" t="n">
         <v>279069</v>
@@ -16667,7 +16667,7 @@
         <v>14.1599998474121</v>
       </c>
       <c r="G562" t="n">
-        <v>12.9775533676147</v>
+        <v>12.9775524139404</v>
       </c>
       <c r="H562" t="n">
         <v>402227</v>
@@ -16696,7 +16696,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G563" t="n">
-        <v>12.9683876037598</v>
+        <v>12.9683885574341</v>
       </c>
       <c r="H563" t="n">
         <v>286686</v>
@@ -16725,7 +16725,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G564" t="n">
-        <v>12.9683876037598</v>
+        <v>12.9683885574341</v>
       </c>
       <c r="H564" t="n">
         <v>355879</v>
@@ -16754,7 +16754,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G565" t="n">
-        <v>12.8125839233398</v>
+        <v>12.8125829696655</v>
       </c>
       <c r="H565" t="n">
         <v>271588</v>
@@ -16783,7 +16783,7 @@
         <v>14.0900001525879</v>
       </c>
       <c r="G566" t="n">
-        <v>12.9133977890015</v>
+        <v>12.9133987426758</v>
       </c>
       <c r="H566" t="n">
         <v>295169</v>
@@ -16899,7 +16899,7 @@
         <v>13.6899995803833</v>
       </c>
       <c r="G570" t="n">
-        <v>12.5468015670776</v>
+        <v>12.5468006134033</v>
       </c>
       <c r="H570" t="n">
         <v>372997</v>
@@ -16986,7 +16986,7 @@
         <v>14.4099998474121</v>
       </c>
       <c r="G573" t="n">
-        <v>13.2066764831543</v>
+        <v>13.2066774368286</v>
       </c>
       <c r="H573" t="n">
         <v>733613</v>
@@ -17015,7 +17015,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G574" t="n">
-        <v>13.2433347702026</v>
+        <v>13.2433366775513</v>
       </c>
       <c r="H574" t="n">
         <v>244093</v>
@@ -17044,7 +17044,7 @@
         <v>14.4899997711182</v>
       </c>
       <c r="G575" t="n">
-        <v>13.2799968719482</v>
+        <v>13.2799959182739</v>
       </c>
       <c r="H575" t="n">
         <v>290211</v>
@@ -17073,7 +17073,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G576" t="n">
-        <v>12.9592227935791</v>
+        <v>12.9592237472534</v>
       </c>
       <c r="H576" t="n">
         <v>377726</v>
@@ -17102,7 +17102,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G577" t="n">
-        <v>13.4266357421875</v>
+        <v>13.4266338348389</v>
       </c>
       <c r="H577" t="n">
         <v>302211</v>
@@ -17131,7 +17131,7 @@
         <v>14.8699998855591</v>
       </c>
       <c r="G578" t="n">
-        <v>13.6282625198364</v>
+        <v>13.6282644271851</v>
       </c>
       <c r="H578" t="n">
         <v>319486</v>
@@ -17160,7 +17160,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G579" t="n">
-        <v>13.7657384872437</v>
+        <v>13.7657375335693</v>
       </c>
       <c r="H579" t="n">
         <v>643667</v>
@@ -17189,7 +17189,7 @@
         <v>15.289999961853</v>
       </c>
       <c r="G580" t="n">
-        <v>14.0131902694702</v>
+        <v>14.0131893157959</v>
       </c>
       <c r="H580" t="n">
         <v>346993</v>
@@ -17218,7 +17218,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G581" t="n">
-        <v>13.9215412139893</v>
+        <v>13.9215431213379</v>
       </c>
       <c r="H581" t="n">
         <v>618862</v>
@@ -17276,7 +17276,7 @@
         <v>15.5100002288818</v>
       </c>
       <c r="G583" t="n">
-        <v>14.2148208618164</v>
+        <v>14.2148189544678</v>
       </c>
       <c r="H583" t="n">
         <v>268996</v>
@@ -17305,7 +17305,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G584" t="n">
-        <v>14.2973031997681</v>
+        <v>14.2973051071167</v>
       </c>
       <c r="H584" t="n">
         <v>373204</v>
@@ -17334,7 +17334,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G585" t="n">
-        <v>14.5172624588013</v>
+        <v>14.5172634124756</v>
       </c>
       <c r="H585" t="n">
         <v>408965</v>
@@ -17363,7 +17363,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G586" t="n">
-        <v>14.4622716903687</v>
+        <v>14.462272644043</v>
       </c>
       <c r="H586" t="n">
         <v>534589</v>
@@ -17421,7 +17421,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G588" t="n">
-        <v>14.5722522735596</v>
+        <v>14.5722513198853</v>
       </c>
       <c r="H588" t="n">
         <v>226046</v>
@@ -17479,7 +17479,7 @@
         <v>15.9700002670288</v>
       </c>
       <c r="G590" t="n">
-        <v>14.6364059448242</v>
+        <v>14.6364068984985</v>
       </c>
       <c r="H590" t="n">
         <v>398491</v>
@@ -17537,7 +17537,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G592" t="n">
-        <v>14.4989337921143</v>
+        <v>14.4989328384399</v>
       </c>
       <c r="H592" t="n">
         <v>293784</v>
@@ -17595,7 +17595,7 @@
         <v>15.5</v>
       </c>
       <c r="G594" t="n">
-        <v>14.2056541442871</v>
+        <v>14.2056531906128</v>
       </c>
       <c r="H594" t="n">
         <v>516183</v>
@@ -17711,7 +17711,7 @@
         <v>16.1900005340576</v>
       </c>
       <c r="G598" t="n">
-        <v>14.8380374908447</v>
+        <v>14.8380346298218</v>
       </c>
       <c r="H598" t="n">
         <v>234572</v>
@@ -17740,7 +17740,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G599" t="n">
-        <v>14.8472013473511</v>
+        <v>14.8472023010254</v>
       </c>
       <c r="H599" t="n">
         <v>458422</v>
@@ -17769,7 +17769,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G600" t="n">
-        <v>15.0304985046387</v>
+        <v>15.030499458313</v>
       </c>
       <c r="H600" t="n">
         <v>339526</v>
@@ -17798,7 +17798,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G601" t="n">
-        <v>14.9846744537354</v>
+        <v>14.9846754074097</v>
       </c>
       <c r="H601" t="n">
         <v>176282</v>
@@ -17827,7 +17827,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G602" t="n">
-        <v>15.1404800415039</v>
+        <v>15.1404809951782</v>
       </c>
       <c r="H602" t="n">
         <v>362242</v>
@@ -17856,7 +17856,7 @@
         <v>16.6299991607666</v>
       </c>
       <c r="G603" t="n">
-        <v>15.2412900924683</v>
+        <v>15.2412910461426</v>
       </c>
       <c r="H603" t="n">
         <v>220058</v>
@@ -17885,7 +17885,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G604" t="n">
-        <v>15.012167930603</v>
+        <v>15.0121688842773</v>
       </c>
       <c r="H604" t="n">
         <v>318129</v>
@@ -17943,7 +17943,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G606" t="n">
-        <v>14.9388484954834</v>
+        <v>14.9388494491577</v>
       </c>
       <c r="H606" t="n">
         <v>287577</v>
@@ -17972,7 +17972,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G607" t="n">
-        <v>14.4622716903687</v>
+        <v>14.462272644043</v>
       </c>
       <c r="H607" t="n">
         <v>476778</v>
@@ -18088,7 +18088,7 @@
         <v>15.4099998474121</v>
       </c>
       <c r="G611" t="n">
-        <v>14.2223110198975</v>
+        <v>14.2223100662231</v>
       </c>
       <c r="H611" t="n">
         <v>287110</v>
@@ -18117,7 +18117,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G612" t="n">
-        <v>14.3422908782959</v>
+        <v>14.3422918319702</v>
       </c>
       <c r="H612" t="n">
         <v>258569</v>
@@ -18175,7 +18175,7 @@
         <v>14.6899995803833</v>
       </c>
       <c r="G614" t="n">
-        <v>13.5578031539917</v>
+        <v>13.5578022003174</v>
       </c>
       <c r="H614" t="n">
         <v>892131</v>
@@ -18204,7 +18204,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G615" t="n">
-        <v>14.01926612854</v>
+        <v>14.0192680358887</v>
       </c>
       <c r="H615" t="n">
         <v>468628</v>
@@ -18320,7 +18320,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G619" t="n">
-        <v>15.0806322097778</v>
+        <v>15.0806331634521</v>
       </c>
       <c r="H619" t="n">
         <v>537916</v>
@@ -18378,7 +18378,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G621" t="n">
-        <v>16.0220222473145</v>
+        <v>16.0220203399658</v>
       </c>
       <c r="H621" t="n">
         <v>491436</v>
@@ -18436,7 +18436,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G623" t="n">
-        <v>15.7359094619751</v>
+        <v>15.735912322998</v>
       </c>
       <c r="H623" t="n">
         <v>211974</v>
@@ -18465,7 +18465,7 @@
         <v>17.0900001525879</v>
       </c>
       <c r="G624" t="n">
-        <v>15.7728319168091</v>
+        <v>15.7728309631348</v>
       </c>
       <c r="H624" t="n">
         <v>257159</v>
@@ -18523,7 +18523,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G626" t="n">
-        <v>15.7820606231689</v>
+        <v>15.7820587158203</v>
       </c>
       <c r="H626" t="n">
         <v>245282</v>
@@ -18552,7 +18552,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G627" t="n">
-        <v>15.8928098678589</v>
+        <v>15.8928079605103</v>
       </c>
       <c r="H627" t="n">
         <v>360704</v>
@@ -18581,7 +18581,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G628" t="n">
-        <v>15.6805381774902</v>
+        <v>15.680534362793</v>
       </c>
       <c r="H628" t="n">
         <v>390829</v>
@@ -18610,7 +18610,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G629" t="n">
-        <v>15.6436195373535</v>
+        <v>15.6436214447021</v>
       </c>
       <c r="H629" t="n">
         <v>321726</v>
@@ -18639,7 +18639,7 @@
         <v>17.4300003051758</v>
       </c>
       <c r="G630" t="n">
-        <v>16.0866241455078</v>
+        <v>16.0866260528564</v>
       </c>
       <c r="H630" t="n">
         <v>401751</v>
@@ -18726,7 +18726,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G633" t="n">
-        <v>16.1327705383301</v>
+        <v>16.1327743530273</v>
       </c>
       <c r="H633" t="n">
         <v>251004</v>
@@ -18755,7 +18755,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G634" t="n">
-        <v>15.8743534088135</v>
+        <v>15.8743515014648</v>
       </c>
       <c r="H634" t="n">
         <v>304376</v>
@@ -18784,7 +18784,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G635" t="n">
-        <v>15.8282041549683</v>
+        <v>15.8282032012939</v>
       </c>
       <c r="H635" t="n">
         <v>457761</v>
@@ -18871,7 +18871,7 @@
         <v>17.8099994659424</v>
       </c>
       <c r="G638" t="n">
-        <v>16.4373378753662</v>
+        <v>16.4373359680176</v>
       </c>
       <c r="H638" t="n">
         <v>494330</v>
@@ -18900,7 +18900,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G639" t="n">
-        <v>16.5942344665527</v>
+        <v>16.5942325592041</v>
       </c>
       <c r="H639" t="n">
         <v>453526</v>
@@ -19016,7 +19016,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G643" t="n">
-        <v>16.1327705383301</v>
+        <v>16.1327743530273</v>
       </c>
       <c r="H643" t="n">
         <v>329276</v>
@@ -19074,7 +19074,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G645" t="n">
-        <v>15.6805381774902</v>
+        <v>15.680534362793</v>
       </c>
       <c r="H645" t="n">
         <v>252321</v>
@@ -19161,7 +19161,7 @@
         <v>17.1100006103516</v>
       </c>
       <c r="G648" t="n">
-        <v>15.7912893295288</v>
+        <v>15.7912902832031</v>
       </c>
       <c r="H648" t="n">
         <v>286677</v>
@@ -19277,7 +19277,7 @@
         <v>17.4300003051758</v>
       </c>
       <c r="G652" t="n">
-        <v>16.0866241455078</v>
+        <v>16.0866260528564</v>
       </c>
       <c r="H652" t="n">
         <v>258335</v>
@@ -19306,7 +19306,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G653" t="n">
-        <v>16.0773944854736</v>
+        <v>16.0773963928223</v>
       </c>
       <c r="H653" t="n">
         <v>180698</v>
@@ -19335,7 +19335,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G654" t="n">
-        <v>16.6496124267578</v>
+        <v>16.6496105194092</v>
       </c>
       <c r="H654" t="n">
         <v>1642938</v>
@@ -19422,7 +19422,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G657" t="n">
-        <v>16.9818649291992</v>
+        <v>16.9818630218506</v>
       </c>
       <c r="H657" t="n">
         <v>388250</v>
@@ -19451,7 +19451,7 @@
         <v>19.0699996948242</v>
       </c>
       <c r="G658" t="n">
-        <v>17.6002254486084</v>
+        <v>17.600227355957</v>
       </c>
       <c r="H658" t="n">
         <v>867868</v>
@@ -19480,7 +19480,7 @@
         <v>19.1599998474121</v>
       </c>
       <c r="G659" t="n">
-        <v>17.6832866668701</v>
+        <v>17.6832885742188</v>
       </c>
       <c r="H659" t="n">
         <v>370053</v>
@@ -19509,7 +19509,7 @@
         <v>19.7399997711182</v>
       </c>
       <c r="G660" t="n">
-        <v>18.2185897827148</v>
+        <v>18.2185878753662</v>
       </c>
       <c r="H660" t="n">
         <v>521817</v>
@@ -19538,7 +19538,7 @@
         <v>19.1299991607666</v>
       </c>
       <c r="G661" t="n">
-        <v>17.6555976867676</v>
+        <v>17.6555995941162</v>
       </c>
       <c r="H661" t="n">
         <v>379526</v>
@@ -19596,7 +19596,7 @@
         <v>19.25</v>
       </c>
       <c r="G663" t="n">
-        <v>17.7663555145264</v>
+        <v>17.7663536071777</v>
       </c>
       <c r="H663" t="n">
         <v>232843</v>
@@ -19654,7 +19654,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G665" t="n">
-        <v>17.3879528045654</v>
+        <v>17.3879547119141</v>
       </c>
       <c r="H665" t="n">
         <v>361625</v>
@@ -19683,7 +19683,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G666" t="n">
-        <v>17.1664524078369</v>
+        <v>17.1664505004883</v>
       </c>
       <c r="H666" t="n">
         <v>270935</v>
@@ -19741,7 +19741,7 @@
         <v>18.7299995422363</v>
       </c>
       <c r="G668" t="n">
-        <v>17.2864265441895</v>
+        <v>17.2864303588867</v>
       </c>
       <c r="H668" t="n">
         <v>137761</v>
@@ -19770,7 +19770,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G669" t="n">
-        <v>17.8125</v>
+        <v>17.8124961853027</v>
       </c>
       <c r="H669" t="n">
         <v>363451</v>
@@ -19799,7 +19799,7 @@
         <v>19.3799991607666</v>
       </c>
       <c r="G670" t="n">
-        <v>17.8863315582275</v>
+        <v>17.8863296508789</v>
       </c>
       <c r="H670" t="n">
         <v>391398</v>
@@ -19828,7 +19828,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G671" t="n">
-        <v>17.8125</v>
+        <v>17.8124961853027</v>
       </c>
       <c r="H671" t="n">
         <v>218782</v>
@@ -19886,7 +19886,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G673" t="n">
-        <v>17.5540790557861</v>
+        <v>17.5540809631348</v>
       </c>
       <c r="H673" t="n">
         <v>146861</v>
@@ -19915,7 +19915,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G674" t="n">
-        <v>17.6279144287109</v>
+        <v>17.6279163360596</v>
       </c>
       <c r="H674" t="n">
         <v>211460</v>
@@ -19944,7 +19944,7 @@
         <v>19.2099990844727</v>
       </c>
       <c r="G675" t="n">
-        <v>17.7294311523438</v>
+        <v>17.7294330596924</v>
       </c>
       <c r="H675" t="n">
         <v>131155</v>
@@ -19973,7 +19973,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G676" t="n">
-        <v>17.58176612854</v>
+        <v>17.5817642211914</v>
       </c>
       <c r="H676" t="n">
         <v>173009</v>
@@ -20002,7 +20002,7 @@
         <v>19.1299991607666</v>
       </c>
       <c r="G677" t="n">
-        <v>17.6555976867676</v>
+        <v>17.6555995941162</v>
       </c>
       <c r="H677" t="n">
         <v>99519</v>
@@ -20031,7 +20031,7 @@
         <v>18.9200000762939</v>
       </c>
       <c r="G678" t="n">
-        <v>17.4617862701416</v>
+        <v>17.4617881774902</v>
       </c>
       <c r="H678" t="n">
         <v>195285</v>
@@ -20060,7 +20060,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G679" t="n">
-        <v>17.5540790557861</v>
+        <v>17.5540809631348</v>
       </c>
       <c r="H679" t="n">
         <v>278929</v>
@@ -20147,7 +20147,7 @@
         <v>19.2099990844727</v>
       </c>
       <c r="G682" t="n">
-        <v>17.7294311523438</v>
+        <v>17.7294330596924</v>
       </c>
       <c r="H682" t="n">
         <v>398296</v>
@@ -20205,7 +20205,7 @@
         <v>18.8099994659424</v>
       </c>
       <c r="G684" t="n">
-        <v>17.3602657318115</v>
+        <v>17.3602638244629</v>
       </c>
       <c r="H684" t="n">
         <v>317043</v>
@@ -20234,7 +20234,7 @@
         <v>19</v>
       </c>
       <c r="G685" t="n">
-        <v>17.5356178283691</v>
+        <v>17.5356197357178</v>
       </c>
       <c r="H685" t="n">
         <v>315198</v>
@@ -20263,7 +20263,7 @@
         <v>19.1299991607666</v>
       </c>
       <c r="G686" t="n">
-        <v>17.6555976867676</v>
+        <v>17.6555995941162</v>
       </c>
       <c r="H686" t="n">
         <v>177533</v>
@@ -20292,7 +20292,7 @@
         <v>19.1299991607666</v>
       </c>
       <c r="G687" t="n">
-        <v>17.6555976867676</v>
+        <v>17.6555995941162</v>
       </c>
       <c r="H687" t="n">
         <v>112902</v>
@@ -20321,7 +20321,7 @@
         <v>19.7700004577637</v>
       </c>
       <c r="G688" t="n">
-        <v>18.2462749481201</v>
+        <v>18.2462730407715</v>
       </c>
       <c r="H688" t="n">
         <v>385797</v>
@@ -20350,7 +20350,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G689" t="n">
-        <v>18.8277187347412</v>
+        <v>18.8277206420898</v>
       </c>
       <c r="H689" t="n">
         <v>753567</v>
@@ -20408,7 +20408,7 @@
         <v>20.4400005340576</v>
       </c>
       <c r="G691" t="n">
-        <v>18.8646354675293</v>
+        <v>18.8646373748779</v>
       </c>
       <c r="H691" t="n">
         <v>149726</v>
@@ -20466,7 +20466,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G693" t="n">
-        <v>18.5508403778076</v>
+        <v>18.5508422851562</v>
       </c>
       <c r="H693" t="n">
         <v>180927</v>
@@ -20553,7 +20553,7 @@
         <v>19.4599990844727</v>
       </c>
       <c r="G696" t="n">
-        <v>17.960168838501</v>
+        <v>17.9601669311523</v>
       </c>
       <c r="H696" t="n">
         <v>275387</v>
@@ -20582,7 +20582,7 @@
         <v>19.5400009155273</v>
       </c>
       <c r="G697" t="n">
-        <v>18.0340023040771</v>
+        <v>18.0340003967285</v>
       </c>
       <c r="H697" t="n">
         <v>200536</v>
@@ -20611,7 +20611,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G698" t="n">
-        <v>18.2739601135254</v>
+        <v>18.273962020874</v>
       </c>
       <c r="H698" t="n">
         <v>190880</v>
@@ -20640,7 +20640,7 @@
         <v>20</v>
       </c>
       <c r="G699" t="n">
-        <v>18.4585494995117</v>
+        <v>18.4585475921631</v>
       </c>
       <c r="H699" t="n">
         <v>234866</v>
@@ -20669,7 +20669,7 @@
         <v>19.7099990844727</v>
       </c>
       <c r="G700" t="n">
-        <v>18.1908988952637</v>
+        <v>18.190896987915</v>
       </c>
       <c r="H700" t="n">
         <v>263072</v>
@@ -20698,7 +20698,7 @@
         <v>19.1399993896484</v>
       </c>
       <c r="G701" t="n">
-        <v>17.664831161499</v>
+        <v>17.6648292541504</v>
       </c>
       <c r="H701" t="n">
         <v>1050258</v>
@@ -20727,7 +20727,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G702" t="n">
-        <v>18.0155448913574</v>
+        <v>18.0155429840088</v>
       </c>
       <c r="H702" t="n">
         <v>409455</v>
@@ -20814,7 +20814,7 @@
         <v>18.25</v>
       </c>
       <c r="G705" t="n">
-        <v>16.8434219360352</v>
+        <v>16.8434238433838</v>
       </c>
       <c r="H705" t="n">
         <v>550620</v>
@@ -20901,7 +20901,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G708" t="n">
-        <v>15.6436195373535</v>
+        <v>15.6436214447021</v>
       </c>
       <c r="H708" t="n">
         <v>732364</v>
@@ -20959,7 +20959,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G710" t="n">
-        <v>15.1729278564453</v>
+        <v>15.1729288101196</v>
       </c>
       <c r="H710" t="n">
         <v>518270</v>
@@ -20988,7 +20988,7 @@
         <v>16.5300006866455</v>
       </c>
       <c r="G711" t="n">
-        <v>15.2559900283813</v>
+        <v>15.2559909820557</v>
       </c>
       <c r="H711" t="n">
         <v>683052</v>
@@ -21046,7 +21046,7 @@
         <v>16.2700004577637</v>
       </c>
       <c r="G713" t="n">
-        <v>15.0160293579102</v>
+        <v>15.0160274505615</v>
       </c>
       <c r="H713" t="n">
         <v>807388</v>
@@ -21133,7 +21133,7 @@
         <v>16.6700000762939</v>
       </c>
       <c r="G716" t="n">
-        <v>15.3852005004883</v>
+        <v>15.3851985931396</v>
       </c>
       <c r="H716" t="n">
         <v>613338</v>
@@ -21162,7 +21162,7 @@
         <v>16.5900001525879</v>
       </c>
       <c r="G717" t="n">
-        <v>15.3113641738892</v>
+        <v>15.3113660812378</v>
       </c>
       <c r="H717" t="n">
         <v>367715</v>
@@ -21249,7 +21249,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G720" t="n">
-        <v>14.6007127761841</v>
+        <v>14.6007118225098</v>
       </c>
       <c r="H720" t="n">
         <v>421585</v>
@@ -21278,7 +21278,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G721" t="n">
-        <v>14.58225440979</v>
+        <v>14.5822534561157</v>
       </c>
       <c r="H721" t="n">
         <v>430019</v>
@@ -21307,7 +21307,7 @@
         <v>16.2700004577637</v>
       </c>
       <c r="G722" t="n">
-        <v>15.0160293579102</v>
+        <v>15.0160274505615</v>
       </c>
       <c r="H722" t="n">
         <v>804979</v>
@@ -21365,7 +21365,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G724" t="n">
-        <v>14.4530420303345</v>
+        <v>14.4530429840088</v>
       </c>
       <c r="H724" t="n">
         <v>1020886</v>
@@ -21394,7 +21394,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G725" t="n">
-        <v>14.268458366394</v>
+        <v>14.2684564590454</v>
       </c>
       <c r="H725" t="n">
         <v>569670</v>
@@ -21423,7 +21423,7 @@
         <v>15.5100002288818</v>
       </c>
       <c r="G726" t="n">
-        <v>14.3146047592163</v>
+        <v>14.3146028518677</v>
       </c>
       <c r="H726" t="n">
         <v>439306</v>
@@ -21452,7 +21452,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G727" t="n">
-        <v>14.2869176864624</v>
+        <v>14.2869157791138</v>
       </c>
       <c r="H727" t="n">
         <v>245428</v>
@@ -21481,7 +21481,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G728" t="n">
-        <v>14.2592287063599</v>
+        <v>14.2592277526855</v>
       </c>
       <c r="H728" t="n">
         <v>335130</v>
@@ -21597,7 +21597,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G732" t="n">
-        <v>14.3976669311523</v>
+        <v>14.397668838501</v>
       </c>
       <c r="H732" t="n">
         <v>817521</v>
@@ -21655,7 +21655,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G734" t="n">
-        <v>14.2592287063599</v>
+        <v>14.2592277526855</v>
       </c>
       <c r="H734" t="n">
         <v>284048</v>
@@ -21684,7 +21684,7 @@
         <v>14.5699996948242</v>
       </c>
       <c r="G735" t="n">
-        <v>13.4470520019531</v>
+        <v>13.4470529556274</v>
       </c>
       <c r="H735" t="n">
         <v>787453</v>
@@ -21713,7 +21713,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G736" t="n">
-        <v>13.3639879226685</v>
+        <v>13.3639888763428</v>
       </c>
       <c r="H736" t="n">
         <v>540827</v>
@@ -21771,7 +21771,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G738" t="n">
-        <v>12.7363977432251</v>
+        <v>12.7363986968994</v>
       </c>
       <c r="H738" t="n">
         <v>574095</v>
@@ -21800,7 +21800,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G739" t="n">
-        <v>13.0317354202271</v>
+        <v>13.0317344665527</v>
       </c>
       <c r="H739" t="n">
         <v>500933</v>
@@ -21887,7 +21887,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G742" t="n">
-        <v>13.290153503418</v>
+        <v>13.2901554107666</v>
       </c>
       <c r="H742" t="n">
         <v>418094</v>
@@ -22032,7 +22032,7 @@
         <v>15.289999961853</v>
       </c>
       <c r="G747" t="n">
-        <v>14.1115598678589</v>
+        <v>14.1115589141846</v>
       </c>
       <c r="H747" t="n">
         <v>502201</v>
@@ -22061,7 +22061,7 @@
         <v>15</v>
       </c>
       <c r="G748" t="n">
-        <v>13.8439111709595</v>
+        <v>13.8439121246338</v>
       </c>
       <c r="H748" t="n">
         <v>458058</v>
@@ -22090,7 +22090,7 @@
         <v>14.9399995803833</v>
       </c>
       <c r="G749" t="n">
-        <v>13.7885360717773</v>
+        <v>13.788535118103</v>
       </c>
       <c r="H749" t="n">
         <v>385007</v>
@@ -22119,7 +22119,7 @@
         <v>15.0900001525879</v>
       </c>
       <c r="G750" t="n">
-        <v>13.9269752502441</v>
+        <v>13.9269742965698</v>
       </c>
       <c r="H750" t="n">
         <v>696256</v>
@@ -22148,7 +22148,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G751" t="n">
-        <v>14.2592287063599</v>
+        <v>14.2592277526855</v>
       </c>
       <c r="H751" t="n">
         <v>512043</v>
@@ -22177,7 +22177,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G752" t="n">
-        <v>13.954662322998</v>
+        <v>13.9546613693237</v>
       </c>
       <c r="H752" t="n">
         <v>744530</v>
@@ -22264,7 +22264,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G755" t="n">
-        <v>13.2347793579102</v>
+        <v>13.2347784042358</v>
       </c>
       <c r="H755" t="n">
         <v>366443</v>
@@ -22380,7 +22380,7 @@
         <v>15.210000038147</v>
       </c>
       <c r="G759" t="n">
-        <v>14.0377254486084</v>
+        <v>14.0377264022827</v>
       </c>
       <c r="H759" t="n">
         <v>1051477</v>
@@ -22409,7 +22409,7 @@
         <v>14.5299997329712</v>
       </c>
       <c r="G760" t="n">
-        <v>13.4101343154907</v>
+        <v>13.410135269165</v>
       </c>
       <c r="H760" t="n">
         <v>862062</v>
@@ -22438,7 +22438,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G761" t="n">
-        <v>12.3856868743896</v>
+        <v>12.3856859207153</v>
       </c>
       <c r="H761" t="n">
         <v>3301714</v>
@@ -22525,7 +22525,7 @@
         <v>13.9099998474121</v>
       </c>
       <c r="G764" t="n">
-        <v>12.8379192352295</v>
+        <v>12.8379182815552</v>
       </c>
       <c r="H764" t="n">
         <v>336867</v>
@@ -22554,7 +22554,7 @@
         <v>14.5</v>
       </c>
       <c r="G765" t="n">
-        <v>13.3824481964111</v>
+        <v>13.3824472427368</v>
       </c>
       <c r="H765" t="n">
         <v>713653</v>
@@ -22583,7 +22583,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G766" t="n">
-        <v>13.290153503418</v>
+        <v>13.2901554107666</v>
       </c>
       <c r="H766" t="n">
         <v>510141</v>
@@ -22641,7 +22641,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G768" t="n">
-        <v>14.4438123703003</v>
+        <v>14.4438133239746</v>
       </c>
       <c r="H768" t="n">
         <v>1132085</v>
@@ -22699,7 +22699,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G770" t="n">
-        <v>14.4899606704712</v>
+        <v>14.4899597167969</v>
       </c>
       <c r="H770" t="n">
         <v>764559</v>
@@ -22786,7 +22786,7 @@
         <v>16.0100002288818</v>
       </c>
       <c r="G773" t="n">
-        <v>14.776068687439</v>
+        <v>14.7760677337646</v>
       </c>
       <c r="H773" t="n">
         <v>482664</v>
@@ -22873,7 +22873,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G776" t="n">
-        <v>14.9052782058716</v>
+        <v>14.9052762985229</v>
       </c>
       <c r="H776" t="n">
         <v>565095</v>
@@ -22902,7 +22902,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G777" t="n">
-        <v>14.9514255523682</v>
+        <v>14.9514265060425</v>
       </c>
       <c r="H777" t="n">
         <v>278638</v>
@@ -22960,7 +22960,7 @@
         <v>15.9700002670288</v>
       </c>
       <c r="G779" t="n">
-        <v>14.7391500473022</v>
+        <v>14.7391510009766</v>
       </c>
       <c r="H779" t="n">
         <v>427798</v>
@@ -23018,7 +23018,7 @@
         <v>16.0100002288818</v>
       </c>
       <c r="G781" t="n">
-        <v>14.776068687439</v>
+        <v>14.7760677337646</v>
       </c>
       <c r="H781" t="n">
         <v>411325</v>
@@ -23134,7 +23134,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G785" t="n">
-        <v>14.4345846176147</v>
+        <v>14.4345865249634</v>
       </c>
       <c r="H785" t="n">
         <v>264161</v>
@@ -23163,7 +23163,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G786" t="n">
-        <v>14.4715023040771</v>
+        <v>14.4715013504028</v>
       </c>
       <c r="H786" t="n">
         <v>501025</v>
@@ -23192,7 +23192,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G787" t="n">
-        <v>14.545334815979</v>
+        <v>14.5453367233276</v>
       </c>
       <c r="H787" t="n">
         <v>246349</v>
@@ -23250,7 +23250,7 @@
         <v>16.5699996948242</v>
       </c>
       <c r="G789" t="n">
-        <v>15.2929067611694</v>
+        <v>15.2929077148438</v>
       </c>
       <c r="H789" t="n">
         <v>429639</v>
@@ -23279,7 +23279,7 @@
         <v>15.8900003433228</v>
       </c>
       <c r="G790" t="n">
-        <v>14.6653165817261</v>
+        <v>14.6653156280518</v>
       </c>
       <c r="H790" t="n">
         <v>1022437</v>
@@ -23308,7 +23308,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G791" t="n">
-        <v>14.8129844665527</v>
+        <v>14.8129835128784</v>
       </c>
       <c r="H791" t="n">
         <v>476920</v>
@@ -23337,7 +23337,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G792" t="n">
-        <v>15.1360082626343</v>
+        <v>15.1360092163086</v>
       </c>
       <c r="H792" t="n">
         <v>377010</v>
@@ -23424,7 +23424,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G795" t="n">
-        <v>14.9883403778076</v>
+        <v>14.9883394241333</v>
       </c>
       <c r="H795" t="n">
         <v>237906</v>
@@ -23453,7 +23453,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G796" t="n">
-        <v>15.0806322097778</v>
+        <v>15.0806331634521</v>
       </c>
       <c r="H796" t="n">
         <v>337410</v>
@@ -23482,7 +23482,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G797" t="n">
-        <v>14.9514255523682</v>
+        <v>14.9514265060425</v>
       </c>
       <c r="H797" t="n">
         <v>355800</v>
@@ -23540,7 +23540,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G799" t="n">
-        <v>14.5084199905396</v>
+        <v>14.5084190368652</v>
       </c>
       <c r="H799" t="n">
         <v>627847</v>
@@ -23569,7 +23569,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G800" t="n">
-        <v>14.8222150802612</v>
+        <v>14.8222141265869</v>
       </c>
       <c r="H800" t="n">
         <v>588271</v>
@@ -23598,7 +23598,7 @@
         <v>16.0300006866455</v>
       </c>
       <c r="G801" t="n">
-        <v>14.794527053833</v>
+        <v>14.7945280075073</v>
       </c>
       <c r="H801" t="n">
         <v>310701</v>
@@ -23627,7 +23627,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G802" t="n">
-        <v>15.1360082626343</v>
+        <v>15.1360092163086</v>
       </c>
       <c r="H802" t="n">
         <v>638809</v>
@@ -23656,7 +23656,7 @@
         <v>16.2900009155273</v>
       </c>
       <c r="G803" t="n">
-        <v>15.0344896316528</v>
+        <v>15.0344877243042</v>
       </c>
       <c r="H803" t="n">
         <v>302743</v>
@@ -23685,7 +23685,7 @@
         <v>16.2099990844727</v>
       </c>
       <c r="G804" t="n">
-        <v>14.9606513977051</v>
+        <v>14.9606523513794</v>
       </c>
       <c r="H804" t="n">
         <v>299367</v>
@@ -23714,7 +23714,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G805" t="n">
-        <v>15.0990924835205</v>
+        <v>15.0990962982178</v>
       </c>
       <c r="H805" t="n">
         <v>243436</v>
@@ -23743,7 +23743,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G806" t="n">
-        <v>15.320592880249</v>
+        <v>15.3205976486206</v>
       </c>
       <c r="H806" t="n">
         <v>715375</v>
@@ -23772,7 +23772,7 @@
         <v>17.3299999237061</v>
       </c>
       <c r="G807" t="n">
-        <v>15.9943323135376</v>
+        <v>15.994330406189</v>
       </c>
       <c r="H807" t="n">
         <v>708148</v>
@@ -23801,7 +23801,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G808" t="n">
-        <v>15.5420970916748</v>
+        <v>15.5420989990234</v>
       </c>
       <c r="H808" t="n">
         <v>1964050</v>
@@ -23830,7 +23830,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G809" t="n">
-        <v>14.9883403778076</v>
+        <v>14.9883394241333</v>
       </c>
       <c r="H809" t="n">
         <v>1215683</v>
@@ -23859,7 +23859,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G810" t="n">
-        <v>14.8591318130493</v>
+        <v>14.859130859375</v>
       </c>
       <c r="H810" t="n">
         <v>1167725</v>
@@ -23888,7 +23888,7 @@
         <v>16.2099990844727</v>
       </c>
       <c r="G811" t="n">
-        <v>14.9606513977051</v>
+        <v>14.9606523513794</v>
       </c>
       <c r="H811" t="n">
         <v>824054</v>
@@ -23946,7 +23946,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G813" t="n">
-        <v>15.1360082626343</v>
+        <v>15.1360092163086</v>
       </c>
       <c r="H813" t="n">
         <v>591855</v>
@@ -23975,7 +23975,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G814" t="n">
-        <v>15.3667402267456</v>
+        <v>15.3667411804199</v>
       </c>
       <c r="H814" t="n">
         <v>464429</v>
@@ -24033,7 +24033,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G816" t="n">
-        <v>16.243522644043</v>
+        <v>16.2435245513916</v>
       </c>
       <c r="H816" t="n">
         <v>1004054</v>
@@ -24062,7 +24062,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G817" t="n">
-        <v>16.243522644043</v>
+        <v>16.2435245513916</v>
       </c>
       <c r="H817" t="n">
         <v>998669</v>
@@ -24091,7 +24091,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G818" t="n">
-        <v>16.243522644043</v>
+        <v>16.2435245513916</v>
       </c>
       <c r="H818" t="n">
         <v>704080</v>
@@ -24120,7 +24120,7 @@
         <v>17.7700004577637</v>
       </c>
       <c r="G819" t="n">
-        <v>16.4004211425781</v>
+        <v>16.4004192352295</v>
       </c>
       <c r="H819" t="n">
         <v>620246</v>
@@ -24178,7 +24178,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G821" t="n">
-        <v>16.243522644043</v>
+        <v>16.2435245513916</v>
       </c>
       <c r="H821" t="n">
         <v>623847</v>
@@ -24207,7 +24207,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G822" t="n">
-        <v>16.0589351654053</v>
+        <v>16.0589370727539</v>
       </c>
       <c r="H822" t="n">
         <v>607059</v>
@@ -24236,7 +24236,7 @@
         <v>17.4300003051758</v>
       </c>
       <c r="G823" t="n">
-        <v>16.0866241455078</v>
+        <v>16.0866260528564</v>
       </c>
       <c r="H823" t="n">
         <v>613809</v>
@@ -24265,7 +24265,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G824" t="n">
-        <v>15.7636013031006</v>
+        <v>15.7636022567749</v>
       </c>
       <c r="H824" t="n">
         <v>1436082</v>
@@ -24294,7 +24294,7 @@
         <v>17.1200008392334</v>
       </c>
       <c r="G825" t="n">
-        <v>15.8005199432373</v>
+        <v>15.8005170822144</v>
       </c>
       <c r="H825" t="n">
         <v>566546</v>
@@ -24381,7 +24381,7 @@
         <v>17.8099994659424</v>
       </c>
       <c r="G828" t="n">
-        <v>16.4373378753662</v>
+        <v>16.4373359680176</v>
       </c>
       <c r="H828" t="n">
         <v>468097</v>
@@ -24410,7 +24410,7 @@
         <v>17.6700000762939</v>
       </c>
       <c r="G829" t="n">
-        <v>16.308126449585</v>
+        <v>16.3081283569336</v>
       </c>
       <c r="H829" t="n">
         <v>553207</v>
@@ -24439,7 +24439,7 @@
         <v>17.4300003051758</v>
       </c>
       <c r="G830" t="n">
-        <v>16.0866241455078</v>
+        <v>16.0866260528564</v>
       </c>
       <c r="H830" t="n">
         <v>516967</v>
@@ -24468,7 +24468,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G831" t="n">
-        <v>15.9851036071777</v>
+        <v>15.9851055145264</v>
       </c>
       <c r="H831" t="n">
         <v>664902</v>
@@ -24497,7 +24497,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G832" t="n">
-        <v>16.0589351654053</v>
+        <v>16.0589370727539</v>
       </c>
       <c r="H832" t="n">
         <v>541808</v>
@@ -24526,7 +24526,7 @@
         <v>17.7299995422363</v>
       </c>
       <c r="G833" t="n">
-        <v>16.3635005950928</v>
+        <v>16.3635025024414</v>
       </c>
       <c r="H833" t="n">
         <v>543424</v>
@@ -24555,7 +24555,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G834" t="n">
-        <v>16.2896690368652</v>
+        <v>16.2896709442139</v>
       </c>
       <c r="H834" t="n">
         <v>676737</v>
@@ -24584,7 +24584,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G835" t="n">
-        <v>16.4465675354004</v>
+        <v>16.4465637207031</v>
       </c>
       <c r="H835" t="n">
         <v>467062</v>
@@ -24642,7 +24642,7 @@
         <v>17.7700004577637</v>
       </c>
       <c r="G837" t="n">
-        <v>16.4004211425781</v>
+        <v>16.4004192352295</v>
       </c>
       <c r="H837" t="n">
         <v>329507</v>
@@ -24671,7 +24671,7 @@
         <v>17.7900009155273</v>
       </c>
       <c r="G838" t="n">
-        <v>16.4188804626465</v>
+        <v>16.4188785552979</v>
       </c>
       <c r="H838" t="n">
         <v>262966</v>
@@ -24700,7 +24700,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G839" t="n">
-        <v>15.8189735412598</v>
+        <v>15.8189754486084</v>
       </c>
       <c r="H839" t="n">
         <v>791008</v>
@@ -24729,7 +24729,7 @@
         <v>16.7700004577637</v>
       </c>
       <c r="G840" t="n">
-        <v>15.4774942398071</v>
+        <v>15.4774932861328</v>
       </c>
       <c r="H840" t="n">
         <v>664642</v>
@@ -24758,7 +24758,7 @@
         <v>16.7600002288818</v>
       </c>
       <c r="G841" t="n">
-        <v>15.4682626724243</v>
+        <v>15.4682645797729</v>
       </c>
       <c r="H841" t="n">
         <v>568688</v>
@@ -24787,7 +24787,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G842" t="n">
-        <v>15.5051803588867</v>
+        <v>15.5051794052124</v>
       </c>
       <c r="H842" t="n">
         <v>508915</v>
@@ -24816,7 +24816,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G843" t="n">
-        <v>15.4313449859619</v>
+        <v>15.4313459396362</v>
       </c>
       <c r="H843" t="n">
         <v>311706</v>
@@ -24845,7 +24845,7 @@
         <v>17.1200008392334</v>
       </c>
       <c r="G844" t="n">
-        <v>15.8005199432373</v>
+        <v>15.8005170822144</v>
       </c>
       <c r="H844" t="n">
         <v>609976</v>
@@ -24874,7 +24874,7 @@
         <v>17.25</v>
       </c>
       <c r="G845" t="n">
-        <v>15.9204978942871</v>
+        <v>15.9204998016357</v>
       </c>
       <c r="H845" t="n">
         <v>291161</v>
@@ -24932,7 +24932,7 @@
         <v>16.7700004577637</v>
       </c>
       <c r="G847" t="n">
-        <v>15.4774942398071</v>
+        <v>15.4774932861328</v>
       </c>
       <c r="H847" t="n">
         <v>636111</v>
@@ -24961,7 +24961,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G848" t="n">
-        <v>15.7359094619751</v>
+        <v>15.735912322998</v>
       </c>
       <c r="H848" t="n">
         <v>380267</v>
@@ -25077,7 +25077,7 @@
         <v>19.0799999237061</v>
       </c>
       <c r="G852" t="n">
-        <v>17.6094551086426</v>
+        <v>17.6094570159912</v>
       </c>
       <c r="H852" t="n">
         <v>1742106</v>
@@ -25106,7 +25106,7 @@
         <v>18.2600002288818</v>
       </c>
       <c r="G853" t="n">
-        <v>16.852653503418</v>
+        <v>16.8526554107666</v>
       </c>
       <c r="H853" t="n">
         <v>782109</v>
@@ -25135,7 +25135,7 @@
         <v>18.2299995422363</v>
       </c>
       <c r="G854" t="n">
-        <v>16.8249664306641</v>
+        <v>16.8249645233154</v>
       </c>
       <c r="H854" t="n">
         <v>794074</v>
@@ -25193,7 +25193,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G856" t="n">
-        <v>17.3510341644287</v>
+        <v>17.3510360717773</v>
       </c>
       <c r="H856" t="n">
         <v>480023</v>
@@ -25251,7 +25251,7 @@
         <v>19.3799991607666</v>
       </c>
       <c r="G858" t="n">
-        <v>17.8863315582275</v>
+        <v>17.8863296508789</v>
       </c>
       <c r="H858" t="n">
         <v>647749</v>
@@ -25309,7 +25309,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G860" t="n">
-        <v>18.3697490692139</v>
+        <v>18.3697471618652</v>
       </c>
       <c r="H860" t="n">
         <v>742068</v>
@@ -25338,7 +25338,7 @@
         <v>20.5200004577637</v>
       </c>
       <c r="G861" t="n">
-        <v>19.0762786865234</v>
+        <v>19.0762767791748</v>
       </c>
       <c r="H861" t="n">
         <v>739026</v>
@@ -25367,7 +25367,7 @@
         <v>20.4200000762939</v>
       </c>
       <c r="G862" t="n">
-        <v>18.9833126068115</v>
+        <v>18.9833106994629</v>
       </c>
       <c r="H862" t="n">
         <v>739085</v>
@@ -25396,7 +25396,7 @@
         <v>19.8199996948242</v>
       </c>
       <c r="G863" t="n">
-        <v>18.4255294799805</v>
+        <v>18.4255275726318</v>
       </c>
       <c r="H863" t="n">
         <v>988695</v>
@@ -25425,7 +25425,7 @@
         <v>19.8400001525879</v>
       </c>
       <c r="G864" t="n">
-        <v>18.4441204071045</v>
+        <v>18.4441184997559</v>
       </c>
       <c r="H864" t="n">
         <v>378837</v>
@@ -25454,7 +25454,7 @@
         <v>19.8799991607666</v>
       </c>
       <c r="G865" t="n">
-        <v>18.4813041687012</v>
+        <v>18.4813060760498</v>
       </c>
       <c r="H865" t="n">
         <v>1583768</v>
@@ -25483,7 +25483,7 @@
         <v>19.4699993133545</v>
       </c>
       <c r="G866" t="n">
-        <v>18.1001491546631</v>
+        <v>18.1001510620117</v>
       </c>
       <c r="H866" t="n">
         <v>487161</v>
@@ -25541,7 +25541,7 @@
         <v>19.8600006103516</v>
       </c>
       <c r="G868" t="n">
-        <v>18.4627132415771</v>
+        <v>18.4627113342285</v>
       </c>
       <c r="H868" t="n">
         <v>716148</v>
@@ -25570,7 +25570,7 @@
         <v>19.9300003051758</v>
       </c>
       <c r="G869" t="n">
-        <v>18.5277862548828</v>
+        <v>18.5277881622314</v>
       </c>
       <c r="H869" t="n">
         <v>555019</v>
@@ -25657,7 +25657,7 @@
         <v>19.9899997711182</v>
       </c>
       <c r="G872" t="n">
-        <v>18.5835666656494</v>
+        <v>18.5835647583008</v>
       </c>
       <c r="H872" t="n">
         <v>690158</v>
@@ -25686,7 +25686,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G873" t="n">
-        <v>18.6858234405518</v>
+        <v>18.6858253479004</v>
       </c>
       <c r="H873" t="n">
         <v>389249</v>
@@ -25715,7 +25715,7 @@
         <v>20.0200004577637</v>
       </c>
       <c r="G874" t="n">
-        <v>18.6114540100098</v>
+        <v>18.6114559173584</v>
       </c>
       <c r="H874" t="n">
         <v>349840</v>
@@ -25744,7 +25744,7 @@
         <v>19.9899997711182</v>
       </c>
       <c r="G875" t="n">
-        <v>18.5835666656494</v>
+        <v>18.5835647583008</v>
       </c>
       <c r="H875" t="n">
         <v>394495</v>
@@ -25773,7 +25773,7 @@
         <v>20.1599998474121</v>
       </c>
       <c r="G876" t="n">
-        <v>18.741605758667</v>
+        <v>18.7416038513184</v>
       </c>
       <c r="H876" t="n">
         <v>428321</v>
@@ -25831,7 +25831,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G878" t="n">
-        <v>19.6154689788818</v>
+        <v>19.6154708862305</v>
       </c>
       <c r="H878" t="n">
         <v>854477</v>
@@ -25860,7 +25860,7 @@
         <v>21.2199993133545</v>
       </c>
       <c r="G879" t="n">
-        <v>19.7270278930664</v>
+        <v>19.7270259857178</v>
       </c>
       <c r="H879" t="n">
         <v>582558</v>
@@ -25889,7 +25889,7 @@
         <v>21.5599994659424</v>
       </c>
       <c r="G880" t="n">
-        <v>20.0431022644043</v>
+        <v>20.0431041717529</v>
       </c>
       <c r="H880" t="n">
         <v>838914</v>
@@ -25976,7 +25976,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G883" t="n">
-        <v>19.6154689788818</v>
+        <v>19.6154708862305</v>
       </c>
       <c r="H883" t="n">
         <v>2078059</v>
@@ -26121,7 +26121,7 @@
         <v>20.5599994659424</v>
       </c>
       <c r="G888" t="n">
-        <v>19.1134624481201</v>
+        <v>19.1134643554688</v>
       </c>
       <c r="H888" t="n">
         <v>686811</v>
@@ -26208,7 +26208,7 @@
         <v>21.0400009155273</v>
       </c>
       <c r="G891" t="n">
-        <v>19.5596923828125</v>
+        <v>19.5596942901611</v>
       </c>
       <c r="H891" t="n">
         <v>640141</v>
@@ -26266,7 +26266,7 @@
         <v>20.5799999237061</v>
       </c>
       <c r="G893" t="n">
-        <v>19.1320552825928</v>
+        <v>19.1320571899414</v>
       </c>
       <c r="H893" t="n">
         <v>678998</v>
@@ -26295,7 +26295,7 @@
         <v>20.4200000762939</v>
       </c>
       <c r="G894" t="n">
-        <v>18.9833126068115</v>
+        <v>18.9833106994629</v>
       </c>
       <c r="H894" t="n">
         <v>430409</v>
@@ -26324,7 +26324,7 @@
         <v>20.4200000762939</v>
       </c>
       <c r="G895" t="n">
-        <v>18.9833126068115</v>
+        <v>18.9833106994629</v>
       </c>
       <c r="H895" t="n">
         <v>497870</v>
@@ -26353,7 +26353,7 @@
         <v>20.4799995422363</v>
       </c>
       <c r="G896" t="n">
-        <v>19.0390892028809</v>
+        <v>19.0390911102295</v>
       </c>
       <c r="H896" t="n">
         <v>583143</v>
@@ -26469,7 +26469,7 @@
         <v>21.2399997711182</v>
       </c>
       <c r="G900" t="n">
-        <v>19.7456207275391</v>
+        <v>19.7456188201904</v>
       </c>
       <c r="H900" t="n">
         <v>519366</v>
@@ -26498,7 +26498,7 @@
         <v>21.1800003051758</v>
       </c>
       <c r="G901" t="n">
-        <v>19.6898422241211</v>
+        <v>19.6898403167725</v>
       </c>
       <c r="H901" t="n">
         <v>359927</v>
@@ -26527,7 +26527,7 @@
         <v>21.6800003051758</v>
       </c>
       <c r="G902" t="n">
-        <v>20.1546630859375</v>
+        <v>20.1546611785889</v>
       </c>
       <c r="H902" t="n">
         <v>542105</v>
@@ -26556,7 +26556,7 @@
         <v>21.1800003051758</v>
       </c>
       <c r="G903" t="n">
-        <v>19.6898422241211</v>
+        <v>19.6898403167725</v>
       </c>
       <c r="H903" t="n">
         <v>735549</v>
@@ -26614,7 +26614,7 @@
         <v>21.3799991607666</v>
       </c>
       <c r="G905" t="n">
-        <v>19.8757705688477</v>
+        <v>19.875768661499</v>
       </c>
       <c r="H905" t="n">
         <v>670080</v>
@@ -26643,7 +26643,7 @@
         <v>21.1800003051758</v>
       </c>
       <c r="G906" t="n">
-        <v>19.6898422241211</v>
+        <v>19.6898403167725</v>
       </c>
       <c r="H906" t="n">
         <v>624659</v>
@@ -26788,7 +26788,7 @@
         <v>22.2800006866455</v>
       </c>
       <c r="G911" t="n">
-        <v>20.7124462127686</v>
+        <v>20.7124481201172</v>
       </c>
       <c r="H911" t="n">
         <v>1579293</v>
@@ -26817,7 +26817,7 @@
         <v>22.1800003051758</v>
       </c>
       <c r="G912" t="n">
-        <v>20.6194858551025</v>
+        <v>20.6194839477539</v>
       </c>
       <c r="H912" t="n">
         <v>1045571</v>
@@ -26846,7 +26846,7 @@
         <v>22.1800003051758</v>
       </c>
       <c r="G913" t="n">
-        <v>20.6194858551025</v>
+        <v>20.6194839477539</v>
       </c>
       <c r="H913" t="n">
         <v>1311146</v>
@@ -26904,7 +26904,7 @@
         <v>20.9599990844727</v>
       </c>
       <c r="G915" t="n">
-        <v>19.4853191375732</v>
+        <v>19.4853210449219</v>
       </c>
       <c r="H915" t="n">
         <v>1162375</v>
@@ -26962,7 +26962,7 @@
         <v>21.9799995422363</v>
       </c>
       <c r="G917" t="n">
-        <v>20.4335536956787</v>
+        <v>20.4335556030273</v>
       </c>
       <c r="H917" t="n">
         <v>562348</v>
@@ -26991,7 +26991,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G918" t="n">
-        <v>20.5451145172119</v>
+        <v>20.5451126098633</v>
       </c>
       <c r="H918" t="n">
         <v>512671</v>
@@ -27020,7 +27020,7 @@
         <v>22.1599998474121</v>
       </c>
       <c r="G919" t="n">
-        <v>20.6008911132812</v>
+        <v>20.6008930206299</v>
       </c>
       <c r="H919" t="n">
         <v>597832</v>
@@ -27049,7 +27049,7 @@
         <v>22.2600002288818</v>
       </c>
       <c r="G920" t="n">
-        <v>20.6938533782959</v>
+        <v>20.6938571929932</v>
       </c>
       <c r="H920" t="n">
         <v>443250</v>
@@ -27078,7 +27078,7 @@
         <v>22.0200004577637</v>
       </c>
       <c r="G921" t="n">
-        <v>20.4707431793213</v>
+        <v>20.4707412719727</v>
       </c>
       <c r="H921" t="n">
         <v>778876</v>
@@ -27136,7 +27136,7 @@
         <v>22.8799991607666</v>
       </c>
       <c r="G923" t="n">
-        <v>21.2702350616455</v>
+        <v>21.2702331542969</v>
       </c>
       <c r="H923" t="n">
         <v>575549</v>
@@ -27165,7 +27165,7 @@
         <v>23.5400009155273</v>
       </c>
       <c r="G924" t="n">
-        <v>21.8838005065918</v>
+        <v>21.8837985992432</v>
       </c>
       <c r="H924" t="n">
         <v>1295879</v>
@@ -27194,7 +27194,7 @@
         <v>23.6200008392334</v>
       </c>
       <c r="G925" t="n">
-        <v>21.9581718444824</v>
+        <v>21.9581699371338</v>
       </c>
       <c r="H925" t="n">
         <v>932327</v>
@@ -27223,7 +27223,7 @@
         <v>23.5799999237061</v>
       </c>
       <c r="G926" t="n">
-        <v>21.9209861755371</v>
+        <v>21.9209842681885</v>
       </c>
       <c r="H926" t="n">
         <v>910452</v>
@@ -27252,7 +27252,7 @@
         <v>23.1399993896484</v>
       </c>
       <c r="G927" t="n">
-        <v>21.5119380950928</v>
+        <v>21.5119400024414</v>
       </c>
       <c r="H927" t="n">
         <v>807193</v>
@@ -27310,7 +27310,7 @@
         <v>23.5799999237061</v>
       </c>
       <c r="G929" t="n">
-        <v>21.9209861755371</v>
+        <v>21.9209842681885</v>
       </c>
       <c r="H929" t="n">
         <v>547116</v>
@@ -27339,7 +27339,7 @@
         <v>23</v>
       </c>
       <c r="G930" t="n">
-        <v>21.3817901611328</v>
+        <v>21.3817920684814</v>
       </c>
       <c r="H930" t="n">
         <v>1510595</v>
@@ -27368,7 +27368,7 @@
         <v>22.9799995422363</v>
       </c>
       <c r="G931" t="n">
-        <v>21.3631973266602</v>
+        <v>21.3631992340088</v>
       </c>
       <c r="H931" t="n">
         <v>705479</v>
@@ -27426,7 +27426,7 @@
         <v>23.6599998474121</v>
       </c>
       <c r="G933" t="n">
-        <v>21.9953556060791</v>
+        <v>21.9953536987305</v>
       </c>
       <c r="H933" t="n">
         <v>342581</v>
@@ -27455,7 +27455,7 @@
         <v>23.8199996948242</v>
       </c>
       <c r="G934" t="n">
-        <v>22.1440963745117</v>
+        <v>22.1440982818604</v>
       </c>
       <c r="H934" t="n">
         <v>728625</v>
@@ -27513,7 +27513,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G936" t="n">
-        <v>21.4747562408447</v>
+        <v>21.4747543334961</v>
       </c>
       <c r="H936" t="n">
         <v>1125340</v>
@@ -27571,7 +27571,7 @@
         <v>22.3600006103516</v>
       </c>
       <c r="G938" t="n">
-        <v>20.7868194580078</v>
+        <v>20.7868213653564</v>
       </c>
       <c r="H938" t="n">
         <v>2173111</v>
@@ -27600,7 +27600,7 @@
         <v>21.4400005340576</v>
       </c>
       <c r="G939" t="n">
-        <v>19.931547164917</v>
+        <v>19.9315509796143</v>
       </c>
       <c r="H939" t="n">
         <v>1879641</v>
@@ -27716,7 +27716,7 @@
         <v>21.8600006103516</v>
       </c>
       <c r="G943" t="n">
-        <v>20.3220024108887</v>
+        <v>20.32200050354</v>
       </c>
       <c r="H943" t="n">
         <v>1104326</v>
@@ -27745,7 +27745,7 @@
         <v>22.0799999237061</v>
       </c>
       <c r="G944" t="n">
-        <v>20.5265197753906</v>
+        <v>20.526517868042</v>
       </c>
       <c r="H944" t="n">
         <v>1107208</v>
@@ -27774,7 +27774,7 @@
         <v>22.7600002288818</v>
       </c>
       <c r="G945" t="n">
-        <v>21.1586780548096</v>
+        <v>21.1586761474609</v>
       </c>
       <c r="H945" t="n">
         <v>1308345</v>
@@ -27803,7 +27803,7 @@
         <v>22.5200004577637</v>
       </c>
       <c r="G946" t="n">
-        <v>20.9355640411377</v>
+        <v>20.9355659484863</v>
       </c>
       <c r="H946" t="n">
         <v>1001961</v>
@@ -27890,7 +27890,7 @@
         <v>23</v>
       </c>
       <c r="G949" t="n">
-        <v>21.3817901611328</v>
+        <v>21.3817920684814</v>
       </c>
       <c r="H949" t="n">
         <v>1499942</v>
@@ -27919,7 +27919,7 @@
         <v>22.5200004577637</v>
       </c>
       <c r="G950" t="n">
-        <v>20.9355640411377</v>
+        <v>20.9355659484863</v>
       </c>
       <c r="H950" t="n">
         <v>1999412</v>
@@ -27977,7 +27977,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G952" t="n">
-        <v>21.1028995513916</v>
+        <v>21.102897644043</v>
       </c>
       <c r="H952" t="n">
         <v>628815</v>
@@ -28006,7 +28006,7 @@
         <v>22.5</v>
       </c>
       <c r="G953" t="n">
-        <v>20.9169692993164</v>
+        <v>20.916971206665</v>
       </c>
       <c r="H953" t="n">
         <v>1528400</v>
@@ -28035,7 +28035,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G954" t="n">
-        <v>21.0099353790283</v>
+        <v>21.0099334716797</v>
       </c>
       <c r="H954" t="n">
         <v>1010100</v>
@@ -28122,7 +28122,7 @@
         <v>21.4599990844727</v>
       </c>
       <c r="G957" t="n">
-        <v>19.950138092041</v>
+        <v>19.9501399993896</v>
       </c>
       <c r="H957" t="n">
         <v>963393</v>
@@ -28151,7 +28151,7 @@
         <v>22.2600002288818</v>
       </c>
       <c r="G958" t="n">
-        <v>20.6938533782959</v>
+        <v>20.6938571929932</v>
       </c>
       <c r="H958" t="n">
         <v>849338</v>
@@ -28180,7 +28180,7 @@
         <v>21.8400001525879</v>
       </c>
       <c r="G959" t="n">
-        <v>20.3034076690674</v>
+        <v>20.3034057617188</v>
       </c>
       <c r="H959" t="n">
         <v>1054390</v>
@@ -28209,7 +28209,7 @@
         <v>21.8600006103516</v>
       </c>
       <c r="G960" t="n">
-        <v>20.3220024108887</v>
+        <v>20.32200050354</v>
       </c>
       <c r="H960" t="n">
         <v>885202</v>
@@ -28383,7 +28383,7 @@
         <v>22.1800003051758</v>
       </c>
       <c r="G966" t="n">
-        <v>20.6194858551025</v>
+        <v>20.6194839477539</v>
       </c>
       <c r="H966" t="n">
         <v>584434</v>
@@ -28441,7 +28441,7 @@
         <v>21.2800006866455</v>
       </c>
       <c r="G968" t="n">
-        <v>19.7828063964844</v>
+        <v>19.7828044891357</v>
       </c>
       <c r="H968" t="n">
         <v>1830133</v>
@@ -28470,7 +28470,7 @@
         <v>21.2399997711182</v>
       </c>
       <c r="G969" t="n">
-        <v>19.7456207275391</v>
+        <v>19.7456188201904</v>
       </c>
       <c r="H969" t="n">
         <v>1190444</v>
@@ -28615,7 +28615,7 @@
         <v>21.8400001525879</v>
       </c>
       <c r="G974" t="n">
-        <v>20.3034076690674</v>
+        <v>20.3034057617188</v>
       </c>
       <c r="H974" t="n">
         <v>900739</v>
@@ -28644,7 +28644,7 @@
         <v>23</v>
       </c>
       <c r="G975" t="n">
-        <v>21.3817901611328</v>
+        <v>21.3817920684814</v>
       </c>
       <c r="H975" t="n">
         <v>2003137</v>
@@ -28673,7 +28673,7 @@
         <v>22.5200004577637</v>
       </c>
       <c r="G976" t="n">
-        <v>20.9355640411377</v>
+        <v>20.9355659484863</v>
       </c>
       <c r="H976" t="n">
         <v>1207509</v>
@@ -28702,7 +28702,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G977" t="n">
-        <v>21.4747562408447</v>
+        <v>21.4747543334961</v>
       </c>
       <c r="H977" t="n">
         <v>737688</v>
@@ -28731,7 +28731,7 @@
         <v>22.8600006103516</v>
       </c>
       <c r="G978" t="n">
-        <v>21.2516441345215</v>
+        <v>21.2516403198242</v>
       </c>
       <c r="H978" t="n">
         <v>1227279</v>
@@ -28760,7 +28760,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G979" t="n">
-        <v>21.1028995513916</v>
+        <v>21.102897644043</v>
       </c>
       <c r="H979" t="n">
         <v>918329</v>
@@ -28847,7 +28847,7 @@
         <v>23.8199996948242</v>
       </c>
       <c r="G982" t="n">
-        <v>22.1440963745117</v>
+        <v>22.1440982818604</v>
       </c>
       <c r="H982" t="n">
         <v>768936</v>
@@ -28876,7 +28876,7 @@
         <v>23.7199993133545</v>
       </c>
       <c r="G983" t="n">
-        <v>22.0511360168457</v>
+        <v>22.0511341094971</v>
       </c>
       <c r="H983" t="n">
         <v>662553</v>
@@ -28905,7 +28905,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G984" t="n">
-        <v>22.4044017791748</v>
+        <v>22.4043998718262</v>
       </c>
       <c r="H984" t="n">
         <v>589611</v>
@@ -28963,7 +28963,7 @@
         <v>24.8400001525879</v>
       </c>
       <c r="G986" t="n">
-        <v>23.0923328399658</v>
+        <v>23.0923347473145</v>
       </c>
       <c r="H986" t="n">
         <v>677199</v>
@@ -29050,7 +29050,7 @@
         <v>24.6800003051758</v>
       </c>
       <c r="G989" t="n">
-        <v>22.9435882568359</v>
+        <v>22.9435901641846</v>
       </c>
       <c r="H989" t="n">
         <v>501358</v>
@@ -29166,7 +29166,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G993" t="n">
-        <v>23.3340435028076</v>
+        <v>23.3340396881104</v>
       </c>
       <c r="H993" t="n">
         <v>347861</v>
@@ -29224,7 +29224,7 @@
         <v>26.0400009155273</v>
       </c>
       <c r="G995" t="n">
-        <v>24.2079067230225</v>
+        <v>24.2079048156738</v>
       </c>
       <c r="H995" t="n">
         <v>1013350</v>
@@ -29253,7 +29253,7 @@
         <v>26.2800006866455</v>
       </c>
       <c r="G996" t="n">
-        <v>24.431022644043</v>
+        <v>24.4310245513916</v>
       </c>
       <c r="H996" t="n">
         <v>894679</v>
@@ -29340,7 +29340,7 @@
         <v>26.1599998474121</v>
       </c>
       <c r="G999" t="n">
-        <v>24.3194618225098</v>
+        <v>24.3194637298584</v>
       </c>
       <c r="H999" t="n">
         <v>765788</v>
@@ -29427,7 +29427,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1002" t="n">
-        <v>24.3566474914551</v>
+        <v>24.3566493988037</v>
       </c>
       <c r="H1002" t="n">
         <v>390442</v>
@@ -29456,7 +29456,7 @@
         <v>25.7800006866455</v>
       </c>
       <c r="G1003" t="n">
-        <v>23.9661998748779</v>
+        <v>23.9662017822266</v>
       </c>
       <c r="H1003" t="n">
         <v>511714</v>
@@ -29485,7 +29485,7 @@
         <v>26.1200008392334</v>
       </c>
       <c r="G1004" t="n">
-        <v>24.2822780609131</v>
+        <v>24.2822799682617</v>
       </c>
       <c r="H1004" t="n">
         <v>843143</v>
@@ -29514,7 +29514,7 @@
         <v>26</v>
       </c>
       <c r="G1005" t="n">
-        <v>24.1707210540771</v>
+        <v>24.1707191467285</v>
       </c>
       <c r="H1005" t="n">
         <v>483765</v>
@@ -29572,7 +29572,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G1007" t="n">
-        <v>23.3340435028076</v>
+        <v>23.3340396881104</v>
       </c>
       <c r="H1007" t="n">
         <v>898561</v>
@@ -29630,7 +29630,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G1009" t="n">
-        <v>23.8918285369873</v>
+        <v>23.8918304443359</v>
       </c>
       <c r="H1009" t="n">
         <v>419347</v>
@@ -29659,7 +29659,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G1010" t="n">
-        <v>23.8918285369873</v>
+        <v>23.8918304443359</v>
       </c>
       <c r="H1010" t="n">
         <v>307496</v>
@@ -29746,7 +29746,7 @@
         <v>25.8400001525879</v>
       </c>
       <c r="G1013" t="n">
-        <v>24.0219764709473</v>
+        <v>24.0219783782959</v>
       </c>
       <c r="H1013" t="n">
         <v>345226</v>
@@ -29804,7 +29804,7 @@
         <v>25.6399993896484</v>
       </c>
       <c r="G1015" t="n">
-        <v>23.8360500335693</v>
+        <v>23.8360481262207</v>
       </c>
       <c r="H1015" t="n">
         <v>260947</v>
@@ -30007,7 +30007,7 @@
         <v>26.2800006866455</v>
       </c>
       <c r="G1022" t="n">
-        <v>24.431022644043</v>
+        <v>24.4310245513916</v>
       </c>
       <c r="H1022" t="n">
         <v>545734</v>
@@ -30036,7 +30036,7 @@
         <v>25.7800006866455</v>
       </c>
       <c r="G1023" t="n">
-        <v>23.9661998748779</v>
+        <v>23.9662017822266</v>
       </c>
       <c r="H1023" t="n">
         <v>503380</v>
@@ -30065,7 +30065,7 @@
         <v>26</v>
       </c>
       <c r="G1024" t="n">
-        <v>24.1707210540771</v>
+        <v>24.1707191467285</v>
       </c>
       <c r="H1024" t="n">
         <v>451145</v>
@@ -30094,7 +30094,7 @@
         <v>26.5400009155273</v>
       </c>
       <c r="G1025" t="n">
-        <v>24.6727275848389</v>
+        <v>24.6727294921875</v>
       </c>
       <c r="H1025" t="n">
         <v>838622</v>
@@ -30181,7 +30181,7 @@
         <v>26.1800003051758</v>
       </c>
       <c r="G1028" t="n">
-        <v>24.3380565643311</v>
+        <v>24.3380584716797</v>
       </c>
       <c r="H1028" t="n">
         <v>551258</v>
@@ -30239,7 +30239,7 @@
         <v>26.9799995422363</v>
       </c>
       <c r="G1030" t="n">
-        <v>25.0817699432373</v>
+        <v>25.0817680358887</v>
       </c>
       <c r="H1030" t="n">
         <v>1073117</v>
@@ -30268,7 +30268,7 @@
         <v>26.8199996948242</v>
       </c>
       <c r="G1031" t="n">
-        <v>24.9330272674561</v>
+        <v>24.9330253601074</v>
       </c>
       <c r="H1031" t="n">
         <v>531475</v>
@@ -30297,7 +30297,7 @@
         <v>26.7600002288818</v>
       </c>
       <c r="G1032" t="n">
-        <v>24.8772525787354</v>
+        <v>24.8772506713867</v>
       </c>
       <c r="H1032" t="n">
         <v>432014</v>
@@ -30355,7 +30355,7 @@
         <v>26.8199996948242</v>
       </c>
       <c r="G1034" t="n">
-        <v>24.9330272674561</v>
+        <v>24.9330253601074</v>
       </c>
       <c r="H1034" t="n">
         <v>520777</v>
@@ -30384,7 +30384,7 @@
         <v>27.0400009155273</v>
       </c>
       <c r="G1035" t="n">
-        <v>25.1375503540039</v>
+        <v>25.1375522613525</v>
       </c>
       <c r="H1035" t="n">
         <v>570683</v>
@@ -30471,7 +30471,7 @@
         <v>26.0799999237061</v>
       </c>
       <c r="G1038" t="n">
-        <v>24.2450942993164</v>
+        <v>24.2450923919678</v>
       </c>
       <c r="H1038" t="n">
         <v>618808</v>
@@ -30500,7 +30500,7 @@
         <v>26.5400009155273</v>
       </c>
       <c r="G1039" t="n">
-        <v>24.6727275848389</v>
+        <v>24.6727294921875</v>
       </c>
       <c r="H1039" t="n">
         <v>489257</v>
@@ -30558,7 +30558,7 @@
         <v>27.4599990844727</v>
       </c>
       <c r="G1041" t="n">
-        <v>25.5279998779297</v>
+        <v>25.5279979705811</v>
       </c>
       <c r="H1041" t="n">
         <v>636028</v>
@@ -30587,7 +30587,7 @@
         <v>27.5200004577637</v>
       </c>
       <c r="G1042" t="n">
-        <v>25.5837802886963</v>
+        <v>25.5837783813477</v>
       </c>
       <c r="H1042" t="n">
         <v>439288</v>
@@ -30616,7 +30616,7 @@
         <v>27.6399993896484</v>
       </c>
       <c r="G1043" t="n">
-        <v>25.6953353881836</v>
+        <v>25.695333480835</v>
       </c>
       <c r="H1043" t="n">
         <v>368628</v>
@@ -30645,7 +30645,7 @@
         <v>28.4200000762939</v>
       </c>
       <c r="G1044" t="n">
-        <v>26.4204578399658</v>
+        <v>26.4204559326172</v>
       </c>
       <c r="H1044" t="n">
         <v>607074</v>
@@ -30732,7 +30732,7 @@
         <v>29</v>
       </c>
       <c r="G1047" t="n">
-        <v>26.9596519470215</v>
+        <v>26.9596500396729</v>
       </c>
       <c r="H1047" t="n">
         <v>478021</v>
@@ -30819,7 +30819,7 @@
         <v>30.1399993896484</v>
       </c>
       <c r="G1050" t="n">
-        <v>28.0194435119629</v>
+        <v>28.0194454193115</v>
       </c>
       <c r="H1050" t="n">
         <v>653214</v>
@@ -30848,7 +30848,7 @@
         <v>29.6200008392334</v>
       </c>
       <c r="G1051" t="n">
-        <v>27.5360317230225</v>
+        <v>27.5360298156738</v>
       </c>
       <c r="H1051" t="n">
         <v>598589</v>
@@ -30877,7 +30877,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1052" t="n">
-        <v>27.145580291748</v>
+        <v>27.1455783843994</v>
       </c>
       <c r="H1052" t="n">
         <v>763043</v>
@@ -30935,7 +30935,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1054" t="n">
-        <v>24.3566474914551</v>
+        <v>24.3566493988037</v>
       </c>
       <c r="H1054" t="n">
         <v>1296254</v>
@@ -30964,7 +30964,7 @@
         <v>26.4200000762939</v>
       </c>
       <c r="G1055" t="n">
-        <v>24.5611724853516</v>
+        <v>24.5611705780029</v>
       </c>
       <c r="H1055" t="n">
         <v>1506419</v>
@@ -30993,7 +30993,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G1056" t="n">
-        <v>23.3340435028076</v>
+        <v>23.3340396881104</v>
       </c>
       <c r="H1056" t="n">
         <v>1258993</v>
@@ -31051,7 +31051,7 @@
         <v>24.7199993133545</v>
       </c>
       <c r="G1058" t="n">
-        <v>22.9807777404785</v>
+        <v>22.9807758331299</v>
       </c>
       <c r="H1058" t="n">
         <v>1679791</v>
@@ -31109,7 +31109,7 @@
         <v>24.5400009155273</v>
       </c>
       <c r="G1060" t="n">
-        <v>22.8134441375732</v>
+        <v>22.813440322876</v>
       </c>
       <c r="H1060" t="n">
         <v>1888760</v>
@@ -31167,7 +31167,7 @@
         <v>23.8199996948242</v>
       </c>
       <c r="G1062" t="n">
-        <v>22.1440963745117</v>
+        <v>22.1440982818604</v>
       </c>
       <c r="H1062" t="n">
         <v>1953098</v>
@@ -31341,7 +31341,7 @@
         <v>16.4699993133545</v>
       </c>
       <c r="G1068" t="n">
-        <v>15.3112211227417</v>
+        <v>15.3112201690674</v>
       </c>
       <c r="H1068" t="n">
         <v>3117569</v>
@@ -31370,7 +31370,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G1069" t="n">
-        <v>15.6923751831055</v>
+        <v>15.6923742294312</v>
       </c>
       <c r="H1069" t="n">
         <v>3072720</v>
@@ -31399,7 +31399,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1070" t="n">
-        <v>16.4546813964844</v>
+        <v>16.454683303833</v>
       </c>
       <c r="H1070" t="n">
         <v>1176888</v>
@@ -31428,7 +31428,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G1071" t="n">
-        <v>17.0589504241943</v>
+        <v>17.058952331543</v>
       </c>
       <c r="H1071" t="n">
         <v>1776004</v>
@@ -31457,7 +31457,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G1072" t="n">
-        <v>17.2727661132812</v>
+        <v>17.2727680206299</v>
       </c>
       <c r="H1072" t="n">
         <v>1889130</v>
@@ -31486,7 +31486,7 @@
         <v>18.9899997711182</v>
       </c>
       <c r="G1073" t="n">
-        <v>17.653923034668</v>
+        <v>17.6539211273193</v>
       </c>
       <c r="H1073" t="n">
         <v>1353168</v>
@@ -31544,7 +31544,7 @@
         <v>19.8600006103516</v>
       </c>
       <c r="G1075" t="n">
-        <v>18.4627132415771</v>
+        <v>18.4627113342285</v>
       </c>
       <c r="H1075" t="n">
         <v>842190</v>
@@ -31660,7 +31660,7 @@
         <v>18.7199993133545</v>
       </c>
       <c r="G1079" t="n">
-        <v>17.4029197692871</v>
+        <v>17.4029178619385</v>
       </c>
       <c r="H1079" t="n">
         <v>934547</v>
@@ -31689,7 +31689,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1080" t="n">
-        <v>16.9195079803467</v>
+        <v>16.919506072998</v>
       </c>
       <c r="H1080" t="n">
         <v>738294</v>
@@ -31747,7 +31747,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1082" t="n">
-        <v>16.3617153167725</v>
+        <v>16.3617191314697</v>
       </c>
       <c r="H1082" t="n">
         <v>591977</v>
@@ -31776,7 +31776,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G1083" t="n">
-        <v>17.1798038482666</v>
+        <v>17.179801940918</v>
       </c>
       <c r="H1083" t="n">
         <v>682675</v>
@@ -31863,7 +31863,7 @@
         <v>19.3150005340576</v>
       </c>
       <c r="G1086" t="n">
-        <v>17.9560585021973</v>
+        <v>17.9560565948486</v>
       </c>
       <c r="H1086" t="n">
         <v>403478</v>
@@ -31892,7 +31892,7 @@
         <v>19.6499996185303</v>
       </c>
       <c r="G1087" t="n">
-        <v>18.2674865722656</v>
+        <v>18.267484664917</v>
       </c>
       <c r="H1087" t="n">
         <v>815346</v>
@@ -31921,7 +31921,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G1088" t="n">
-        <v>17.0589504241943</v>
+        <v>17.058952331543</v>
       </c>
       <c r="H1088" t="n">
         <v>863041</v>
@@ -31950,7 +31950,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1089" t="n">
-        <v>17.4772911071777</v>
+        <v>17.4772891998291</v>
       </c>
       <c r="H1089" t="n">
         <v>573179</v>
@@ -32037,7 +32037,7 @@
         <v>21.0400009155273</v>
       </c>
       <c r="G1092" t="n">
-        <v>19.5596923828125</v>
+        <v>19.5596942901611</v>
       </c>
       <c r="H1092" t="n">
         <v>663908</v>
@@ -32124,7 +32124,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1095" t="n">
-        <v>18.6858234405518</v>
+        <v>18.6858253479004</v>
       </c>
       <c r="H1095" t="n">
         <v>516513</v>
@@ -32182,7 +32182,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G1097" t="n">
-        <v>19.7084350585938</v>
+        <v>19.7084331512451</v>
       </c>
       <c r="H1097" t="n">
         <v>745506</v>
@@ -32240,7 +32240,7 @@
         <v>20.9099998474121</v>
       </c>
       <c r="G1099" t="n">
-        <v>19.438835144043</v>
+        <v>19.4388370513916</v>
       </c>
       <c r="H1099" t="n">
         <v>514938</v>
@@ -32269,7 +32269,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1100" t="n">
-        <v>19.2436141967773</v>
+        <v>19.2436122894287</v>
       </c>
       <c r="H1100" t="n">
         <v>379972</v>
@@ -32298,7 +32298,7 @@
         <v>21.6499996185303</v>
       </c>
       <c r="G1101" t="n">
-        <v>20.1267719268799</v>
+        <v>20.1267738342285</v>
       </c>
       <c r="H1101" t="n">
         <v>668222</v>
@@ -32327,7 +32327,7 @@
         <v>22.7900009155273</v>
       </c>
       <c r="G1102" t="n">
-        <v>21.1865653991699</v>
+        <v>21.1865673065186</v>
       </c>
       <c r="H1102" t="n">
         <v>1089546</v>
@@ -32356,7 +32356,7 @@
         <v>22.3899993896484</v>
       </c>
       <c r="G1103" t="n">
-        <v>20.8147087097168</v>
+        <v>20.8147068023682</v>
       </c>
       <c r="H1103" t="n">
         <v>705481</v>
@@ -32414,7 +32414,7 @@
         <v>22.8600006103516</v>
       </c>
       <c r="G1105" t="n">
-        <v>21.2516441345215</v>
+        <v>21.2516403198242</v>
       </c>
       <c r="H1105" t="n">
         <v>394586</v>
@@ -32501,7 +32501,7 @@
         <v>22.0100002288818</v>
       </c>
       <c r="G1108" t="n">
-        <v>20.4614448547363</v>
+        <v>20.4614429473877</v>
       </c>
       <c r="H1108" t="n">
         <v>518904</v>
@@ -32559,7 +32559,7 @@
         <v>22.8899993896484</v>
       </c>
       <c r="G1110" t="n">
-        <v>21.2795314788818</v>
+        <v>21.2795295715332</v>
       </c>
       <c r="H1110" t="n">
         <v>388582</v>
@@ -32588,7 +32588,7 @@
         <v>21.9400005340576</v>
       </c>
       <c r="G1111" t="n">
-        <v>20.3963718414307</v>
+        <v>20.396369934082</v>
       </c>
       <c r="H1111" t="n">
         <v>1485879</v>
@@ -32646,7 +32646,7 @@
         <v>22.6800003051758</v>
       </c>
       <c r="G1113" t="n">
-        <v>21.0843086242676</v>
+        <v>21.0843067169189</v>
       </c>
       <c r="H1113" t="n">
         <v>643036</v>
@@ -32675,7 +32675,7 @@
         <v>23</v>
       </c>
       <c r="G1114" t="n">
-        <v>21.3817901611328</v>
+        <v>21.3817920684814</v>
       </c>
       <c r="H1114" t="n">
         <v>756438</v>
@@ -32704,7 +32704,7 @@
         <v>24.1200008392334</v>
       </c>
       <c r="G1115" t="n">
-        <v>22.4229946136475</v>
+        <v>22.4229927062988</v>
       </c>
       <c r="H1115" t="n">
         <v>783958</v>
@@ -32762,7 +32762,7 @@
         <v>23.3299999237061</v>
       </c>
       <c r="G1117" t="n">
-        <v>21.6885719299316</v>
+        <v>21.6885738372803</v>
       </c>
       <c r="H1117" t="n">
         <v>1064983</v>
@@ -32791,7 +32791,7 @@
         <v>24.6100006103516</v>
       </c>
       <c r="G1118" t="n">
-        <v>22.8785171508789</v>
+        <v>22.8785190582275</v>
       </c>
       <c r="H1118" t="n">
         <v>997396</v>
@@ -32820,7 +32820,7 @@
         <v>24.9500007629395</v>
       </c>
       <c r="G1119" t="n">
-        <v>23.1945953369141</v>
+        <v>23.1945972442627</v>
       </c>
       <c r="H1119" t="n">
         <v>1102502</v>
@@ -32849,7 +32849,7 @@
         <v>24.6299991607666</v>
       </c>
       <c r="G1120" t="n">
-        <v>22.8971080780029</v>
+        <v>22.8971099853516</v>
       </c>
       <c r="H1120" t="n">
         <v>578121</v>
@@ -32878,7 +32878,7 @@
         <v>24.9699993133545</v>
       </c>
       <c r="G1121" t="n">
-        <v>23.2131862640381</v>
+        <v>23.2131881713867</v>
       </c>
       <c r="H1121" t="n">
         <v>1038253</v>
@@ -32907,7 +32907,7 @@
         <v>24.9400005340576</v>
       </c>
       <c r="G1122" t="n">
-        <v>23.1852989196777</v>
+        <v>23.1853008270264</v>
       </c>
       <c r="H1122" t="n">
         <v>1014334</v>
@@ -32965,7 +32965,7 @@
         <v>23.7600002288818</v>
       </c>
       <c r="G1124" t="n">
-        <v>22.088321685791</v>
+        <v>22.0883197784424</v>
       </c>
       <c r="H1124" t="n">
         <v>1946394</v>
@@ -32994,7 +32994,7 @@
         <v>23.3299999237061</v>
       </c>
       <c r="G1125" t="n">
-        <v>21.6885719299316</v>
+        <v>21.6885738372803</v>
       </c>
       <c r="H1125" t="n">
         <v>1319512</v>
@@ -33023,7 +33023,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1126" t="n">
-        <v>22.032543182373</v>
+        <v>22.0325412750244</v>
       </c>
       <c r="H1126" t="n">
         <v>1155011</v>
@@ -33052,7 +33052,7 @@
         <v>23.7199993133545</v>
       </c>
       <c r="G1127" t="n">
-        <v>22.0511360168457</v>
+        <v>22.0511341094971</v>
       </c>
       <c r="H1127" t="n">
         <v>752477</v>
@@ -33081,7 +33081,7 @@
         <v>22.9200000762939</v>
       </c>
       <c r="G1128" t="n">
-        <v>21.3074207305908</v>
+        <v>21.3074226379395</v>
       </c>
       <c r="H1128" t="n">
         <v>866357</v>
@@ -33168,7 +33168,7 @@
         <v>24.0200004577637</v>
       </c>
       <c r="G1131" t="n">
-        <v>22.3300285339355</v>
+        <v>22.3300266265869</v>
       </c>
       <c r="H1131" t="n">
         <v>891370</v>
@@ -33255,7 +33255,7 @@
         <v>23.7800006866455</v>
       </c>
       <c r="G1134" t="n">
-        <v>22.106912612915</v>
+        <v>22.1069164276123</v>
       </c>
       <c r="H1134" t="n">
         <v>996330</v>
@@ -33313,7 +33313,7 @@
         <v>24.5699996948242</v>
       </c>
       <c r="G1136" t="n">
-        <v>22.841329574585</v>
+        <v>22.8413314819336</v>
       </c>
       <c r="H1136" t="n">
         <v>529862</v>
@@ -33371,7 +33371,7 @@
         <v>23.5400009155273</v>
       </c>
       <c r="G1138" t="n">
-        <v>21.8838005065918</v>
+        <v>21.8837985992432</v>
       </c>
       <c r="H1138" t="n">
         <v>539948</v>
@@ -33400,7 +33400,7 @@
         <v>23.6200008392334</v>
       </c>
       <c r="G1139" t="n">
-        <v>21.9581718444824</v>
+        <v>21.9581699371338</v>
       </c>
       <c r="H1139" t="n">
         <v>500622</v>
@@ -33429,7 +33429,7 @@
         <v>23.5200004577637</v>
       </c>
       <c r="G1140" t="n">
-        <v>21.8652057647705</v>
+        <v>21.8652076721191</v>
       </c>
       <c r="H1140" t="n">
         <v>398594</v>
@@ -33516,7 +33516,7 @@
         <v>24.3700008392334</v>
       </c>
       <c r="G1143" t="n">
-        <v>22.6554069519043</v>
+        <v>22.655403137207</v>
       </c>
       <c r="H1143" t="n">
         <v>547648</v>
@@ -33574,7 +33574,7 @@
         <v>24.6499996185303</v>
       </c>
       <c r="G1145" t="n">
-        <v>22.9157028198242</v>
+        <v>22.9157047271729</v>
       </c>
       <c r="H1145" t="n">
         <v>601276</v>
@@ -33603,7 +33603,7 @@
         <v>24.8600006103516</v>
       </c>
       <c r="G1146" t="n">
-        <v>23.1109275817871</v>
+        <v>23.1109294891357</v>
       </c>
       <c r="H1146" t="n">
         <v>620239</v>
@@ -33632,7 +33632,7 @@
         <v>24.9599990844727</v>
       </c>
       <c r="G1147" t="n">
-        <v>23.2038917541504</v>
+        <v>23.203893661499</v>
       </c>
       <c r="H1147" t="n">
         <v>570066</v>
@@ -33661,7 +33661,7 @@
         <v>24.8299999237061</v>
       </c>
       <c r="G1148" t="n">
-        <v>23.0830383300781</v>
+        <v>23.0830364227295</v>
       </c>
       <c r="H1148" t="n">
         <v>552283</v>
@@ -33690,7 +33690,7 @@
         <v>24.8799991607666</v>
       </c>
       <c r="G1149" t="n">
-        <v>23.1295223236084</v>
+        <v>23.1295204162598</v>
       </c>
       <c r="H1149" t="n">
         <v>382370</v>
@@ -33748,7 +33748,7 @@
         <v>24.9699993133545</v>
       </c>
       <c r="G1151" t="n">
-        <v>23.2131862640381</v>
+        <v>23.2131881713867</v>
       </c>
       <c r="H1151" t="n">
         <v>387471</v>
@@ -33777,7 +33777,7 @@
         <v>25.4699993133545</v>
       </c>
       <c r="G1152" t="n">
-        <v>23.6780090332031</v>
+        <v>23.6780109405518</v>
       </c>
       <c r="H1152" t="n">
         <v>611011</v>
@@ -33806,7 +33806,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1153" t="n">
-        <v>24.0777587890625</v>
+        <v>24.0777568817139</v>
       </c>
       <c r="H1153" t="n">
         <v>664354</v>
@@ -33864,7 +33864,7 @@
         <v>26.4699993133545</v>
       </c>
       <c r="G1155" t="n">
-        <v>24.6076526641846</v>
+        <v>24.6076507568359</v>
       </c>
       <c r="H1155" t="n">
         <v>466539</v>
@@ -33893,7 +33893,7 @@
         <v>26.25</v>
       </c>
       <c r="G1156" t="n">
-        <v>24.403133392334</v>
+        <v>24.4031314849854</v>
       </c>
       <c r="H1156" t="n">
         <v>630076</v>
@@ -33980,7 +33980,7 @@
         <v>25.9200000762939</v>
       </c>
       <c r="G1159" t="n">
-        <v>24.0963497161865</v>
+        <v>24.0963516235352</v>
       </c>
       <c r="H1159" t="n">
         <v>533026</v>
@@ -34009,7 +34009,7 @@
         <v>26.1200008392334</v>
       </c>
       <c r="G1160" t="n">
-        <v>24.2822780609131</v>
+        <v>24.2822799682617</v>
       </c>
       <c r="H1160" t="n">
         <v>246730</v>
@@ -34125,7 +34125,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G1164" t="n">
-        <v>26.9131717681885</v>
+        <v>26.9131698608398</v>
       </c>
       <c r="H1164" t="n">
         <v>1361860</v>
@@ -34154,7 +34154,7 @@
         <v>29.5599994659424</v>
       </c>
       <c r="G1165" t="n">
-        <v>27.4802513122559</v>
+        <v>27.4802494049072</v>
       </c>
       <c r="H1165" t="n">
         <v>926013</v>
@@ -34212,7 +34212,7 @@
         <v>28.8899993896484</v>
       </c>
       <c r="G1167" t="n">
-        <v>26.8573875427246</v>
+        <v>26.8573894500732</v>
       </c>
       <c r="H1167" t="n">
         <v>802172</v>
@@ -34241,7 +34241,7 @@
         <v>28.4400005340576</v>
       </c>
       <c r="G1168" t="n">
-        <v>26.4390506744385</v>
+        <v>26.4390468597412</v>
       </c>
       <c r="H1168" t="n">
         <v>703183</v>
@@ -34270,7 +34270,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G1169" t="n">
-        <v>26.8202037811279</v>
+        <v>26.8202018737793</v>
       </c>
       <c r="H1169" t="n">
         <v>418926</v>
@@ -34299,7 +34299,7 @@
         <v>28.2900009155273</v>
       </c>
       <c r="G1170" t="n">
-        <v>26.2996063232422</v>
+        <v>26.2996044158936</v>
       </c>
       <c r="H1170" t="n">
         <v>543942</v>
@@ -34386,7 +34386,7 @@
         <v>28.5100002288818</v>
       </c>
       <c r="G1173" t="n">
-        <v>26.5041236877441</v>
+        <v>26.5041275024414</v>
       </c>
       <c r="H1173" t="n">
         <v>477433</v>
@@ -34444,7 +34444,7 @@
         <v>28.5699996948242</v>
       </c>
       <c r="G1175" t="n">
-        <v>26.5599021911621</v>
+        <v>26.5599040985107</v>
       </c>
       <c r="H1175" t="n">
         <v>317286</v>
@@ -34473,7 +34473,7 @@
         <v>27.8199996948242</v>
       </c>
       <c r="G1176" t="n">
-        <v>25.8626708984375</v>
+        <v>25.8626728057861</v>
       </c>
       <c r="H1176" t="n">
         <v>596546</v>
@@ -34560,7 +34560,7 @@
         <v>27.75</v>
       </c>
       <c r="G1179" t="n">
-        <v>25.7975959777832</v>
+        <v>25.7975978851318</v>
       </c>
       <c r="H1179" t="n">
         <v>339043</v>
@@ -34589,7 +34589,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1180" t="n">
-        <v>25.7511138916016</v>
+        <v>25.7511177062988</v>
       </c>
       <c r="H1180" t="n">
         <v>346849</v>
@@ -34618,7 +34618,7 @@
         <v>27.9200000762939</v>
       </c>
       <c r="G1181" t="n">
-        <v>25.9556369781494</v>
+        <v>25.9556350708008</v>
       </c>
       <c r="H1181" t="n">
         <v>662320</v>
@@ -34647,7 +34647,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1182" t="n">
-        <v>25.7511138916016</v>
+        <v>25.7511177062988</v>
       </c>
       <c r="H1182" t="n">
         <v>330840</v>
@@ -34676,7 +34676,7 @@
         <v>27.7900009155273</v>
       </c>
       <c r="G1183" t="n">
-        <v>25.8347835540771</v>
+        <v>25.8347816467285</v>
       </c>
       <c r="H1183" t="n">
         <v>513533</v>
@@ -34734,7 +34734,7 @@
         <v>27.9200000762939</v>
       </c>
       <c r="G1185" t="n">
-        <v>25.9556369781494</v>
+        <v>25.9556350708008</v>
       </c>
       <c r="H1185" t="n">
         <v>381523</v>
@@ -34763,7 +34763,7 @@
         <v>27.7099990844727</v>
       </c>
       <c r="G1186" t="n">
-        <v>25.7604084014893</v>
+        <v>25.7604103088379</v>
       </c>
       <c r="H1186" t="n">
         <v>529723</v>
@@ -34966,7 +34966,7 @@
         <v>28.7399997711182</v>
       </c>
       <c r="G1193" t="n">
-        <v>26.7179431915283</v>
+        <v>26.717945098877</v>
       </c>
       <c r="H1193" t="n">
         <v>465250</v>
@@ -35024,7 +35024,7 @@
         <v>29.6900005340576</v>
       </c>
       <c r="G1195" t="n">
-        <v>27.6011047363281</v>
+        <v>27.6011066436768</v>
       </c>
       <c r="H1195" t="n">
         <v>689548</v>
@@ -35111,7 +35111,7 @@
         <v>30.1499996185303</v>
       </c>
       <c r="G1198" t="n">
-        <v>28.0287380218506</v>
+        <v>28.0287399291992</v>
       </c>
       <c r="H1198" t="n">
         <v>595090</v>
@@ -35140,7 +35140,7 @@
         <v>30.0499992370605</v>
       </c>
       <c r="G1199" t="n">
-        <v>27.9357738494873</v>
+        <v>27.9357757568359</v>
       </c>
       <c r="H1199" t="n">
         <v>758144</v>
@@ -35169,7 +35169,7 @@
         <v>28.8799991607666</v>
       </c>
       <c r="G1200" t="n">
-        <v>26.8480911254883</v>
+        <v>26.8480930328369</v>
       </c>
       <c r="H1200" t="n">
         <v>704174</v>
@@ -35256,7 +35256,7 @@
         <v>28.7700004577637</v>
       </c>
       <c r="G1203" t="n">
-        <v>26.7458324432373</v>
+        <v>26.7458305358887</v>
       </c>
       <c r="H1203" t="n">
         <v>578038</v>
@@ -35285,7 +35285,7 @@
         <v>28.9899997711182</v>
       </c>
       <c r="G1204" t="n">
-        <v>26.9503536224365</v>
+        <v>26.9503555297852</v>
       </c>
       <c r="H1204" t="n">
         <v>680353</v>
@@ -35372,7 +35372,7 @@
         <v>30.5499992370605</v>
       </c>
       <c r="G1207" t="n">
-        <v>28.4005966186523</v>
+        <v>28.400598526001</v>
       </c>
       <c r="H1207" t="n">
         <v>877195</v>
@@ -35401,7 +35401,7 @@
         <v>30.8700008392334</v>
       </c>
       <c r="G1208" t="n">
-        <v>28.6980819702148</v>
+        <v>28.6980838775635</v>
       </c>
       <c r="H1208" t="n">
         <v>575908</v>
@@ -35488,7 +35488,7 @@
         <v>30.5400009155273</v>
       </c>
       <c r="G1211" t="n">
-        <v>28.3913021087646</v>
+        <v>28.391300201416</v>
       </c>
       <c r="H1211" t="n">
         <v>756663</v>
@@ -35604,7 +35604,7 @@
         <v>32.4500007629395</v>
       </c>
       <c r="G1215" t="n">
-        <v>30.1669158935547</v>
+        <v>30.1669178009033</v>
       </c>
       <c r="H1215" t="n">
         <v>542479</v>
@@ -35720,7 +35720,7 @@
         <v>32.3800010681152</v>
       </c>
       <c r="G1219" t="n">
-        <v>30.1018447875977</v>
+        <v>30.1018466949463</v>
       </c>
       <c r="H1219" t="n">
         <v>693257</v>
@@ -35807,7 +35807,7 @@
         <v>32.1699981689453</v>
       </c>
       <c r="G1222" t="n">
-        <v>29.9066181182861</v>
+        <v>29.9066162109375</v>
       </c>
       <c r="H1222" t="n">
         <v>578613</v>
@@ -35894,7 +35894,7 @@
         <v>31.9200000762939</v>
       </c>
       <c r="G1225" t="n">
-        <v>29.6742076873779</v>
+        <v>29.6742095947266</v>
       </c>
       <c r="H1225" t="n">
         <v>457639</v>
@@ -35952,7 +35952,7 @@
         <v>30.0799999237061</v>
       </c>
       <c r="G1227" t="n">
-        <v>27.9636650085449</v>
+        <v>27.9636669158936</v>
       </c>
       <c r="H1227" t="n">
         <v>1746598</v>
@@ -35981,7 +35981,7 @@
         <v>30.5900001525879</v>
       </c>
       <c r="G1228" t="n">
-        <v>28.4377841949463</v>
+        <v>28.4377822875977</v>
       </c>
       <c r="H1228" t="n">
         <v>1164042</v>
@@ -36039,7 +36039,7 @@
         <v>32.3600006103516</v>
       </c>
       <c r="G1230" t="n">
-        <v>30.083251953125</v>
+        <v>30.0832538604736</v>
       </c>
       <c r="H1230" t="n">
         <v>942033</v>
@@ -36068,7 +36068,7 @@
         <v>33.5</v>
       </c>
       <c r="G1231" t="n">
-        <v>31.143045425415</v>
+        <v>31.1430416107178</v>
       </c>
       <c r="H1231" t="n">
         <v>1002014</v>
@@ -36126,7 +36126,7 @@
         <v>35.2400016784668</v>
       </c>
       <c r="G1233" t="n">
-        <v>32.7606201171875</v>
+        <v>32.7606239318848</v>
       </c>
       <c r="H1233" t="n">
         <v>915245</v>
@@ -36184,7 +36184,7 @@
         <v>34</v>
       </c>
       <c r="G1235" t="n">
-        <v>31.6078662872314</v>
+        <v>31.6078643798828</v>
       </c>
       <c r="H1235" t="n">
         <v>1794751</v>
@@ -36213,7 +36213,7 @@
         <v>34.9000015258789</v>
       </c>
       <c r="G1236" t="n">
-        <v>32.4445457458496</v>
+        <v>32.4445495605469</v>
       </c>
       <c r="H1236" t="n">
         <v>1131373</v>
@@ -36271,7 +36271,7 @@
         <v>35.7400016784668</v>
       </c>
       <c r="G1238" t="n">
-        <v>33.2254447937012</v>
+        <v>33.2254486083984</v>
       </c>
       <c r="H1238" t="n">
         <v>985655</v>
@@ -36387,7 +36387,7 @@
         <v>35.5299987792969</v>
       </c>
       <c r="G1242" t="n">
-        <v>33.0302200317383</v>
+        <v>33.0302238464355</v>
       </c>
       <c r="H1242" t="n">
         <v>738557</v>
@@ -36474,7 +36474,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1245" t="n">
-        <v>31.9797267913818</v>
+        <v>31.9797229766846</v>
       </c>
       <c r="H1245" t="n">
         <v>894850</v>
@@ -36503,7 +36503,7 @@
         <v>33</v>
       </c>
       <c r="G1246" t="n">
-        <v>30.67822265625</v>
+        <v>30.6782188415527</v>
       </c>
       <c r="H1246" t="n">
         <v>1279735</v>
@@ -36561,7 +36561,7 @@
         <v>33.4799995422363</v>
       </c>
       <c r="G1248" t="n">
-        <v>31.124454498291</v>
+        <v>31.1244506835938</v>
       </c>
       <c r="H1248" t="n">
         <v>645679</v>
@@ -36619,7 +36619,7 @@
         <v>33.5699996948242</v>
       </c>
       <c r="G1250" t="n">
-        <v>31.208122253418</v>
+        <v>31.2081203460693</v>
       </c>
       <c r="H1250" t="n">
         <v>9363539</v>
@@ -36648,7 +36648,7 @@
         <v>32.3800010681152</v>
       </c>
       <c r="G1251" t="n">
-        <v>30.1018447875977</v>
+        <v>30.1018466949463</v>
       </c>
       <c r="H1251" t="n">
         <v>1186381</v>
@@ -36706,7 +36706,7 @@
         <v>32.3800010681152</v>
       </c>
       <c r="G1253" t="n">
-        <v>30.1018447875977</v>
+        <v>30.1018466949463</v>
       </c>
       <c r="H1253" t="n">
         <v>668759</v>
@@ -36735,7 +36735,7 @@
         <v>32.3400001525879</v>
       </c>
       <c r="G1254" t="n">
-        <v>30.0646591186523</v>
+        <v>30.0646572113037</v>
       </c>
       <c r="H1254" t="n">
         <v>535624</v>
@@ -36793,7 +36793,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1256" t="n">
-        <v>30.3063621520996</v>
+        <v>30.3063640594482</v>
       </c>
       <c r="H1256" t="n">
         <v>418721</v>
@@ -36851,7 +36851,7 @@
         <v>32.5499992370605</v>
       </c>
       <c r="G1258" t="n">
-        <v>30.2598819732666</v>
+        <v>30.2598838806152</v>
       </c>
       <c r="H1258" t="n">
         <v>493351</v>
@@ -36880,7 +36880,7 @@
         <v>33.1100006103516</v>
       </c>
       <c r="G1259" t="n">
-        <v>30.7804851531982</v>
+        <v>30.780481338501</v>
       </c>
       <c r="H1259" t="n">
         <v>453967</v>
@@ -36909,7 +36909,7 @@
         <v>33.6100006103516</v>
       </c>
       <c r="G1260" t="n">
-        <v>31.245304107666</v>
+        <v>31.2453060150146</v>
       </c>
       <c r="H1260" t="n">
         <v>541414</v>
@@ -36938,7 +36938,7 @@
         <v>32.8400001525879</v>
       </c>
       <c r="G1261" t="n">
-        <v>30.5294818878174</v>
+        <v>30.5294780731201</v>
       </c>
       <c r="H1261" t="n">
         <v>550644</v>
@@ -36967,7 +36967,7 @@
         <v>33.6699981689453</v>
       </c>
       <c r="G1262" t="n">
-        <v>31.3010845184326</v>
+        <v>31.3010807037354</v>
       </c>
       <c r="H1262" t="n">
         <v>612088</v>
@@ -36996,7 +36996,7 @@
         <v>33.4500007629395</v>
       </c>
       <c r="G1263" t="n">
-        <v>31.0965595245361</v>
+        <v>31.096565246582</v>
       </c>
       <c r="H1263" t="n">
         <v>368695</v>
@@ -37025,7 +37025,7 @@
         <v>33.9500007629395</v>
       </c>
       <c r="G1264" t="n">
-        <v>31.5613861083984</v>
+        <v>31.5613880157471</v>
       </c>
       <c r="H1264" t="n">
         <v>683063</v>
@@ -37054,7 +37054,7 @@
         <v>33.189998626709</v>
       </c>
       <c r="G1265" t="n">
-        <v>30.8548545837402</v>
+        <v>30.8548526763916</v>
       </c>
       <c r="H1265" t="n">
         <v>518840</v>
@@ -37083,7 +37083,7 @@
         <v>33.7299995422363</v>
       </c>
       <c r="G1266" t="n">
-        <v>31.3568630218506</v>
+        <v>31.356861114502</v>
       </c>
       <c r="H1266" t="n">
         <v>416411</v>
@@ -37141,7 +37141,7 @@
         <v>33.5</v>
       </c>
       <c r="G1268" t="n">
-        <v>31.143045425415</v>
+        <v>31.1430416107178</v>
       </c>
       <c r="H1268" t="n">
         <v>291451</v>
@@ -37199,7 +37199,7 @@
         <v>34.0400009155273</v>
       </c>
       <c r="G1270" t="n">
-        <v>31.6450519561768</v>
+        <v>31.6450538635254</v>
       </c>
       <c r="H1270" t="n">
         <v>337021</v>
@@ -37228,7 +37228,7 @@
         <v>33.939998626709</v>
       </c>
       <c r="G1271" t="n">
-        <v>31.5520858764648</v>
+        <v>31.5520915985107</v>
       </c>
       <c r="H1271" t="n">
         <v>390614</v>
@@ -37257,7 +37257,7 @@
         <v>33.560001373291</v>
       </c>
       <c r="G1272" t="n">
-        <v>31.198823928833</v>
+        <v>31.1988220214844</v>
       </c>
       <c r="H1272" t="n">
         <v>379992</v>
@@ -37286,7 +37286,7 @@
         <v>33.0200004577637</v>
       </c>
       <c r="G1273" t="n">
-        <v>30.6968173980713</v>
+        <v>30.6968193054199</v>
       </c>
       <c r="H1273" t="n">
         <v>532654</v>
@@ -37344,7 +37344,7 @@
         <v>33.8400001525879</v>
       </c>
       <c r="G1275" t="n">
-        <v>31.4591197967529</v>
+        <v>31.4591236114502</v>
       </c>
       <c r="H1275" t="n">
         <v>591205</v>
@@ -37431,7 +37431,7 @@
         <v>33.9099998474121</v>
       </c>
       <c r="G1278" t="n">
-        <v>31.5242004394531</v>
+        <v>31.5241985321045</v>
       </c>
       <c r="H1278" t="n">
         <v>472719</v>
@@ -37460,7 +37460,7 @@
         <v>34.1599998474121</v>
       </c>
       <c r="G1279" t="n">
-        <v>31.7566051483154</v>
+        <v>31.7566089630127</v>
       </c>
       <c r="H1279" t="n">
         <v>465842</v>
@@ -37489,7 +37489,7 @@
         <v>34</v>
       </c>
       <c r="G1280" t="n">
-        <v>31.6078662872314</v>
+        <v>31.6078643798828</v>
       </c>
       <c r="H1280" t="n">
         <v>572579</v>
@@ -37518,7 +37518,7 @@
         <v>34.189998626709</v>
       </c>
       <c r="G1281" t="n">
-        <v>31.7844924926758</v>
+        <v>31.784496307373</v>
       </c>
       <c r="H1281" t="n">
         <v>327784</v>
@@ -37576,7 +37576,7 @@
         <v>34.1199989318848</v>
       </c>
       <c r="G1283" t="n">
-        <v>31.7194194793701</v>
+        <v>31.7194232940674</v>
       </c>
       <c r="H1283" t="n">
         <v>705836</v>
@@ -37634,7 +37634,7 @@
         <v>33.5800018310547</v>
       </c>
       <c r="G1285" t="n">
-        <v>31.217414855957</v>
+        <v>31.2174167633057</v>
       </c>
       <c r="H1285" t="n">
         <v>327434</v>
@@ -37663,7 +37663,7 @@
         <v>33.189998626709</v>
       </c>
       <c r="G1286" t="n">
-        <v>30.8548545837402</v>
+        <v>30.8548526763916</v>
       </c>
       <c r="H1286" t="n">
         <v>329789</v>
@@ -37692,7 +37692,7 @@
         <v>33.5499992370605</v>
       </c>
       <c r="G1287" t="n">
-        <v>31.1895236968994</v>
+        <v>31.189525604248</v>
       </c>
       <c r="H1287" t="n">
         <v>433382</v>
@@ -37721,7 +37721,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G1288" t="n">
-        <v>31.7008285522461</v>
+        <v>31.7008247375488</v>
       </c>
       <c r="H1288" t="n">
         <v>535834</v>
@@ -37808,7 +37808,7 @@
         <v>33.4300003051758</v>
       </c>
       <c r="G1291" t="n">
-        <v>31.0779685974121</v>
+        <v>31.0779705047607</v>
       </c>
       <c r="H1291" t="n">
         <v>446373</v>
@@ -37837,7 +37837,7 @@
         <v>34.1599998474121</v>
       </c>
       <c r="G1292" t="n">
-        <v>31.7566051483154</v>
+        <v>31.7566089630127</v>
       </c>
       <c r="H1292" t="n">
         <v>430183</v>
@@ -37866,7 +37866,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G1293" t="n">
-        <v>32.1656532287598</v>
+        <v>32.1656494140625</v>
       </c>
       <c r="H1293" t="n">
         <v>624778</v>
@@ -37924,7 +37924,7 @@
         <v>36.2299995422363</v>
       </c>
       <c r="G1295" t="n">
-        <v>33.6809730529785</v>
+        <v>33.6809692382812</v>
       </c>
       <c r="H1295" t="n">
         <v>632561</v>
@@ -37982,7 +37982,7 @@
         <v>36.5900001525879</v>
       </c>
       <c r="G1297" t="n">
-        <v>34.0156478881836</v>
+        <v>34.0156440734863</v>
       </c>
       <c r="H1297" t="n">
         <v>602926</v>
@@ -38069,7 +38069,7 @@
         <v>37.4900016784668</v>
       </c>
       <c r="G1300" t="n">
-        <v>34.8523216247559</v>
+        <v>34.8523254394531</v>
       </c>
       <c r="H1300" t="n">
         <v>450978</v>
@@ -38156,7 +38156,7 @@
         <v>35.8699989318848</v>
       </c>
       <c r="G1303" t="n">
-        <v>33.3462944030762</v>
+        <v>33.3462982177734</v>
       </c>
       <c r="H1303" t="n">
         <v>364724</v>
@@ -38185,7 +38185,7 @@
         <v>35.5</v>
       </c>
       <c r="G1304" t="n">
-        <v>33.0023307800293</v>
+        <v>33.0023345947266</v>
       </c>
       <c r="H1304" t="n">
         <v>424023</v>
@@ -38214,7 +38214,7 @@
         <v>34.939998626709</v>
       </c>
       <c r="G1305" t="n">
-        <v>32.4817314147949</v>
+        <v>32.4817276000977</v>
       </c>
       <c r="H1305" t="n">
         <v>526224</v>
@@ -38272,7 +38272,7 @@
         <v>33.2799987792969</v>
       </c>
       <c r="G1307" t="n">
-        <v>30.9385223388672</v>
+        <v>30.9385261535645</v>
       </c>
       <c r="H1307" t="n">
         <v>966226</v>
@@ -38301,7 +38301,7 @@
         <v>33.310001373291</v>
       </c>
       <c r="G1308" t="n">
-        <v>30.9664154052734</v>
+        <v>30.9664134979248</v>
       </c>
       <c r="H1308" t="n">
         <v>507966</v>
@@ -38330,7 +38330,7 @@
         <v>33.2799987792969</v>
       </c>
       <c r="G1309" t="n">
-        <v>30.9385223388672</v>
+        <v>30.9385261535645</v>
       </c>
       <c r="H1309" t="n">
         <v>332923</v>
@@ -38359,7 +38359,7 @@
         <v>33</v>
       </c>
       <c r="G1310" t="n">
-        <v>30.67822265625</v>
+        <v>30.6782188415527</v>
       </c>
       <c r="H1310" t="n">
         <v>584748</v>
@@ -38388,7 +38388,7 @@
         <v>33.9900016784668</v>
       </c>
       <c r="G1311" t="n">
-        <v>31.5985679626465</v>
+        <v>31.5985698699951</v>
       </c>
       <c r="H1311" t="n">
         <v>592052</v>
@@ -38446,7 +38446,7 @@
         <v>31.3899993896484</v>
       </c>
       <c r="G1313" t="n">
-        <v>29.1814956665039</v>
+        <v>29.1814975738525</v>
       </c>
       <c r="H1313" t="n">
         <v>2026130</v>
@@ -38504,7 +38504,7 @@
         <v>30.0400009155273</v>
       </c>
       <c r="G1315" t="n">
-        <v>27.926477432251</v>
+        <v>27.9264793395996</v>
       </c>
       <c r="H1315" t="n">
         <v>1122108</v>
@@ -38533,7 +38533,7 @@
         <v>30.3700008392334</v>
       </c>
       <c r="G1316" t="n">
-        <v>28.2332630157471</v>
+        <v>28.2332611083984</v>
       </c>
       <c r="H1316" t="n">
         <v>1091879</v>
@@ -38562,7 +38562,7 @@
         <v>31.8199996948242</v>
       </c>
       <c r="G1317" t="n">
-        <v>29.581241607666</v>
+        <v>29.5812435150146</v>
       </c>
       <c r="H1317" t="n">
         <v>1199977</v>
@@ -38591,7 +38591,7 @@
         <v>32.0900001525879</v>
       </c>
       <c r="G1318" t="n">
-        <v>29.8322467803955</v>
+        <v>29.8322486877441</v>
       </c>
       <c r="H1318" t="n">
         <v>795869</v>
@@ -38649,7 +38649,7 @@
         <v>31.9599990844727</v>
       </c>
       <c r="G1320" t="n">
-        <v>29.7113952636719</v>
+        <v>29.7113914489746</v>
       </c>
       <c r="H1320" t="n">
         <v>595142</v>
@@ -38678,7 +38678,7 @@
         <v>32.1800003051758</v>
       </c>
       <c r="G1321" t="n">
-        <v>29.9159164428711</v>
+        <v>29.9159183502197</v>
       </c>
       <c r="H1321" t="n">
         <v>384825</v>
@@ -38707,7 +38707,7 @@
         <v>32.5900001525879</v>
       </c>
       <c r="G1322" t="n">
-        <v>30.2970695495605</v>
+        <v>30.2970714569092</v>
       </c>
       <c r="H1322" t="n">
         <v>554376</v>
@@ -38736,7 +38736,7 @@
         <v>31.9899997711182</v>
       </c>
       <c r="G1323" t="n">
-        <v>29.7392864227295</v>
+        <v>29.7392845153809</v>
       </c>
       <c r="H1323" t="n">
         <v>651675</v>
@@ -38794,7 +38794,7 @@
         <v>30.9300003051758</v>
       </c>
       <c r="G1325" t="n">
-        <v>28.7538585662842</v>
+        <v>28.7538623809814</v>
       </c>
       <c r="H1325" t="n">
         <v>1455075</v>
@@ -38823,7 +38823,7 @@
         <v>31.5699996948242</v>
       </c>
       <c r="G1326" t="n">
-        <v>29.3488311767578</v>
+        <v>29.3488330841064</v>
       </c>
       <c r="H1326" t="n">
         <v>546970</v>
@@ -38852,7 +38852,7 @@
         <v>33.1599998474121</v>
       </c>
       <c r="G1327" t="n">
-        <v>30.8269691467285</v>
+        <v>30.8269672393799</v>
       </c>
       <c r="H1327" t="n">
         <v>1435909</v>
@@ -39026,7 +39026,7 @@
         <v>31.7399997711182</v>
       </c>
       <c r="G1333" t="n">
-        <v>29.5068702697754</v>
+        <v>29.5068740844727</v>
       </c>
       <c r="H1333" t="n">
         <v>431492</v>
@@ -39084,7 +39084,7 @@
         <v>32.75</v>
       </c>
       <c r="G1335" t="n">
-        <v>30.4458103179932</v>
+        <v>30.4458141326904</v>
       </c>
       <c r="H1335" t="n">
         <v>490235</v>
@@ -39113,7 +39113,7 @@
         <v>32.4199981689453</v>
       </c>
       <c r="G1336" t="n">
-        <v>30.1390266418457</v>
+        <v>30.1390247344971</v>
       </c>
       <c r="H1336" t="n">
         <v>498064</v>
@@ -39171,7 +39171,7 @@
         <v>33.0699996948242</v>
       </c>
       <c r="G1338" t="n">
-        <v>30.7432975769043</v>
+        <v>30.7432956695557</v>
       </c>
       <c r="H1338" t="n">
         <v>539028</v>
@@ -39200,7 +39200,7 @@
         <v>32.8199996948242</v>
       </c>
       <c r="G1339" t="n">
-        <v>30.5108871459961</v>
+        <v>30.5108890533447</v>
       </c>
       <c r="H1339" t="n">
         <v>328228</v>
@@ -39229,7 +39229,7 @@
         <v>35.0800018310547</v>
       </c>
       <c r="G1340" t="n">
-        <v>32.6118774414062</v>
+        <v>32.6118812561035</v>
       </c>
       <c r="H1340" t="n">
         <v>1513964</v>
@@ -39287,7 +39287,7 @@
         <v>35.4700012207031</v>
       </c>
       <c r="G1342" t="n">
-        <v>32.9744415283203</v>
+        <v>32.9744453430176</v>
       </c>
       <c r="H1342" t="n">
         <v>512681</v>
@@ -39374,7 +39374,7 @@
         <v>35.5299987792969</v>
       </c>
       <c r="G1345" t="n">
-        <v>33.0302200317383</v>
+        <v>33.0302238464355</v>
       </c>
       <c r="H1345" t="n">
         <v>485449</v>
@@ -39403,7 +39403,7 @@
         <v>35.2099990844727</v>
       </c>
       <c r="G1346" t="n">
-        <v>32.7327270507812</v>
+        <v>32.7327308654785</v>
       </c>
       <c r="H1346" t="n">
         <v>457763</v>
@@ -39432,7 +39432,7 @@
         <v>35.7900009155273</v>
       </c>
       <c r="G1347" t="n">
-        <v>33.2719268798828</v>
+        <v>33.2719306945801</v>
       </c>
       <c r="H1347" t="n">
         <v>508331</v>
@@ -39490,7 +39490,7 @@
         <v>36.6399993896484</v>
       </c>
       <c r="G1349" t="n">
-        <v>34.0621223449707</v>
+        <v>34.0621185302734</v>
       </c>
       <c r="H1349" t="n">
         <v>792977</v>
@@ -39548,7 +39548,7 @@
         <v>35.9199981689453</v>
       </c>
       <c r="G1351" t="n">
-        <v>33.3927803039551</v>
+        <v>33.3927764892578</v>
       </c>
       <c r="H1351" t="n">
         <v>445529</v>
@@ -39577,7 +39577,7 @@
         <v>34.6699981689453</v>
       </c>
       <c r="G1352" t="n">
-        <v>32.2307281494141</v>
+        <v>32.2307319641113</v>
       </c>
       <c r="H1352" t="n">
         <v>893143</v>
@@ -39635,7 +39635,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G1354" t="n">
-        <v>32.9093627929688</v>
+        <v>32.909366607666</v>
       </c>
       <c r="H1354" t="n">
         <v>306038</v>
@@ -39780,7 +39780,7 @@
         <v>35.2400016784668</v>
       </c>
       <c r="G1359" t="n">
-        <v>32.7606201171875</v>
+        <v>32.7606239318848</v>
       </c>
       <c r="H1359" t="n">
         <v>379088</v>
@@ -39896,7 +39896,7 @@
         <v>33.5</v>
       </c>
       <c r="G1363" t="n">
-        <v>31.143045425415</v>
+        <v>31.1430416107178</v>
       </c>
       <c r="H1363" t="n">
         <v>522923</v>
@@ -39925,7 +39925,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1364" t="n">
-        <v>31.2360095977783</v>
+        <v>31.2360038757324</v>
       </c>
       <c r="H1364" t="n">
         <v>336882</v>
@@ -39954,7 +39954,7 @@
         <v>34.5</v>
       </c>
       <c r="G1365" t="n">
-        <v>32.0726852416992</v>
+        <v>32.0726890563965</v>
       </c>
       <c r="H1365" t="n">
         <v>745662</v>
@@ -39983,7 +39983,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G1366" t="n">
-        <v>32.258617401123</v>
+        <v>32.2586212158203</v>
       </c>
       <c r="H1366" t="n">
         <v>459434</v>
@@ -40012,7 +40012,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G1367" t="n">
-        <v>32.9093627929688</v>
+        <v>32.909366607666</v>
       </c>
       <c r="H1367" t="n">
         <v>502691</v>
@@ -40128,7 +40128,7 @@
         <v>37.4300003051758</v>
       </c>
       <c r="G1371" t="n">
-        <v>35.0078926086426</v>
+        <v>35.0078964233398</v>
       </c>
       <c r="H1371" t="n">
         <v>672385</v>
@@ -40157,7 +40157,7 @@
         <v>38.2700004577637</v>
       </c>
       <c r="G1372" t="n">
-        <v>35.7935371398926</v>
+        <v>35.7935409545898</v>
       </c>
       <c r="H1372" t="n">
         <v>1822903</v>
@@ -40331,7 +40331,7 @@
         <v>39.2200012207031</v>
       </c>
       <c r="G1378" t="n">
-        <v>36.6820602416992</v>
+        <v>36.6820640563965</v>
       </c>
       <c r="H1378" t="n">
         <v>494051</v>
@@ -40476,7 +40476,7 @@
         <v>39.5699996948242</v>
       </c>
       <c r="G1383" t="n">
-        <v>37.0094146728516</v>
+        <v>37.0094184875488</v>
       </c>
       <c r="H1383" t="n">
         <v>246385</v>
@@ -40505,7 +40505,7 @@
         <v>40.8499984741211</v>
       </c>
       <c r="G1384" t="n">
-        <v>38.2065849304199</v>
+        <v>38.2065811157227</v>
       </c>
       <c r="H1384" t="n">
         <v>759072</v>
@@ -40621,7 +40621,7 @@
         <v>40.1699981689453</v>
       </c>
       <c r="G1388" t="n">
-        <v>37.5705871582031</v>
+        <v>37.5705909729004</v>
       </c>
       <c r="H1388" t="n">
         <v>790419</v>
@@ -40737,7 +40737,7 @@
         <v>41.2299995422363</v>
       </c>
       <c r="G1392" t="n">
-        <v>38.5619926452637</v>
+        <v>38.5619964599609</v>
       </c>
       <c r="H1392" t="n">
         <v>614005</v>
@@ -40766,7 +40766,7 @@
         <v>41.2700004577637</v>
       </c>
       <c r="G1393" t="n">
-        <v>38.5994071960449</v>
+        <v>38.5994110107422</v>
       </c>
       <c r="H1393" t="n">
         <v>313945</v>
@@ -40795,7 +40795,7 @@
         <v>41.3699989318848</v>
       </c>
       <c r="G1394" t="n">
-        <v>38.6929397583008</v>
+        <v>38.6929359436035</v>
       </c>
       <c r="H1394" t="n">
         <v>260446</v>
@@ -40824,7 +40824,7 @@
         <v>42.1500015258789</v>
       </c>
       <c r="G1395" t="n">
-        <v>39.4224624633789</v>
+        <v>39.4224662780762</v>
       </c>
       <c r="H1395" t="n">
         <v>415362</v>
@@ -40882,7 +40882,7 @@
         <v>41.4300003051758</v>
       </c>
       <c r="G1397" t="n">
-        <v>38.7490577697754</v>
+        <v>38.7490539550781</v>
       </c>
       <c r="H1397" t="n">
         <v>356423</v>
@@ -40911,7 +40911,7 @@
         <v>41.5999984741211</v>
       </c>
       <c r="G1398" t="n">
-        <v>38.9080505371094</v>
+        <v>38.9080543518066</v>
       </c>
       <c r="H1398" t="n">
         <v>327436</v>
@@ -40940,7 +40940,7 @@
         <v>41.2200012207031</v>
       </c>
       <c r="G1399" t="n">
-        <v>38.5526428222656</v>
+        <v>38.5526466369629</v>
       </c>
       <c r="H1399" t="n">
         <v>284279</v>
@@ -41027,7 +41027,7 @@
         <v>40.6699981689453</v>
       </c>
       <c r="G1402" t="n">
-        <v>38.0382347106934</v>
+        <v>38.0382308959961</v>
       </c>
       <c r="H1402" t="n">
         <v>477423</v>
@@ -41085,7 +41085,7 @@
         <v>39.0999984741211</v>
       </c>
       <c r="G1404" t="n">
-        <v>36.5698280334473</v>
+        <v>36.56982421875</v>
       </c>
       <c r="H1404" t="n">
         <v>768643</v>
@@ -41230,7 +41230,7 @@
         <v>40.7599983215332</v>
       </c>
       <c r="G1409" t="n">
-        <v>38.1224098205566</v>
+        <v>38.1224060058594</v>
       </c>
       <c r="H1409" t="n">
         <v>530520</v>
@@ -41288,7 +41288,7 @@
         <v>40.8499984741211</v>
       </c>
       <c r="G1411" t="n">
-        <v>38.2065849304199</v>
+        <v>38.2065811157227</v>
       </c>
       <c r="H1411" t="n">
         <v>415892</v>
@@ -41317,7 +41317,7 @@
         <v>41.060001373291</v>
       </c>
       <c r="G1412" t="n">
-        <v>38.4029998779297</v>
+        <v>38.4029960632324</v>
       </c>
       <c r="H1412" t="n">
         <v>325257</v>
@@ -41346,7 +41346,7 @@
         <v>41.3699989318848</v>
       </c>
       <c r="G1413" t="n">
-        <v>38.6929397583008</v>
+        <v>38.6929359436035</v>
       </c>
       <c r="H1413" t="n">
         <v>419042</v>
@@ -41375,7 +41375,7 @@
         <v>40.7799987792969</v>
       </c>
       <c r="G1414" t="n">
-        <v>38.14111328125</v>
+        <v>38.1411094665527</v>
       </c>
       <c r="H1414" t="n">
         <v>657581</v>
@@ -41433,7 +41433,7 @@
         <v>41.0400009155273</v>
       </c>
       <c r="G1416" t="n">
-        <v>38.3842926025391</v>
+        <v>38.3842887878418</v>
       </c>
       <c r="H1416" t="n">
         <v>641548</v>
@@ -41491,7 +41491,7 @@
         <v>41.6800003051758</v>
       </c>
       <c r="G1418" t="n">
-        <v>38.9828758239746</v>
+        <v>38.9828720092773</v>
       </c>
       <c r="H1418" t="n">
         <v>996037</v>
@@ -41520,7 +41520,7 @@
         <v>42.2999992370605</v>
       </c>
       <c r="G1419" t="n">
-        <v>39.5627517700195</v>
+        <v>39.5627555847168</v>
       </c>
       <c r="H1419" t="n">
         <v>499566</v>
@@ -41578,7 +41578,7 @@
         <v>42</v>
       </c>
       <c r="G1421" t="n">
-        <v>39.282169342041</v>
+        <v>39.2821655273438</v>
       </c>
       <c r="H1421" t="n">
         <v>416641</v>
@@ -41636,7 +41636,7 @@
         <v>41.9000015258789</v>
       </c>
       <c r="G1423" t="n">
-        <v>39.1886444091797</v>
+        <v>39.1886405944824</v>
       </c>
       <c r="H1423" t="n">
         <v>546092</v>
@@ -41665,7 +41665,7 @@
         <v>41.9799995422363</v>
       </c>
       <c r="G1424" t="n">
-        <v>39.2634582519531</v>
+        <v>39.2634620666504</v>
       </c>
       <c r="H1424" t="n">
         <v>487170</v>
@@ -41694,7 +41694,7 @@
         <v>41.9099998474121</v>
       </c>
       <c r="G1425" t="n">
-        <v>39.1979904174805</v>
+        <v>39.1979866027832</v>
       </c>
       <c r="H1425" t="n">
         <v>345247</v>
@@ -41810,7 +41810,7 @@
         <v>43.0299987792969</v>
       </c>
       <c r="G1429" t="n">
-        <v>40.2455139160156</v>
+        <v>40.2455177307129</v>
       </c>
       <c r="H1429" t="n">
         <v>383531</v>
@@ -41897,7 +41897,7 @@
         <v>43.2599983215332</v>
       </c>
       <c r="G1432" t="n">
-        <v>40.4606285095215</v>
+        <v>40.4606323242188</v>
       </c>
       <c r="H1432" t="n">
         <v>557923</v>
@@ -41984,7 +41984,7 @@
         <v>43.9700012207031</v>
       </c>
       <c r="G1435" t="n">
-        <v>41.1246910095215</v>
+        <v>41.1246871948242</v>
       </c>
       <c r="H1435" t="n">
         <v>313660</v>
@@ -42013,7 +42013,7 @@
         <v>43.75</v>
       </c>
       <c r="G1436" t="n">
-        <v>40.9189300537109</v>
+        <v>40.9189262390137</v>
       </c>
       <c r="H1436" t="n">
         <v>268689</v>
@@ -42042,7 +42042,7 @@
         <v>43.4700012207031</v>
       </c>
       <c r="G1437" t="n">
-        <v>40.6570434570312</v>
+        <v>40.6570472717285</v>
       </c>
       <c r="H1437" t="n">
         <v>210532</v>
@@ -42071,7 +42071,7 @@
         <v>43.6800003051758</v>
       </c>
       <c r="G1438" t="n">
-        <v>40.853458404541</v>
+        <v>40.8534545898438</v>
       </c>
       <c r="H1438" t="n">
         <v>162145</v>
@@ -42274,7 +42274,7 @@
         <v>43.7400016784668</v>
       </c>
       <c r="G1445" t="n">
-        <v>40.9095764160156</v>
+        <v>40.9095726013184</v>
       </c>
       <c r="H1445" t="n">
         <v>427583</v>
@@ -42303,7 +42303,7 @@
         <v>43.689998626709</v>
       </c>
       <c r="G1446" t="n">
-        <v>40.8628120422363</v>
+        <v>40.8628044128418</v>
       </c>
       <c r="H1446" t="n">
         <v>383460</v>
@@ -42361,7 +42361,7 @@
         <v>43.1500015258789</v>
       </c>
       <c r="G1448" t="n">
-        <v>40.3577537536621</v>
+        <v>40.3577499389648</v>
       </c>
       <c r="H1448" t="n">
         <v>295759</v>
@@ -42477,7 +42477,7 @@
         <v>42.2999992370605</v>
       </c>
       <c r="G1452" t="n">
-        <v>39.5627517700195</v>
+        <v>39.5627555847168</v>
       </c>
       <c r="H1452" t="n">
         <v>328612</v>
@@ -42535,7 +42535,7 @@
         <v>42.7400016784668</v>
       </c>
       <c r="G1454" t="n">
-        <v>39.9742813110352</v>
+        <v>39.9742851257324</v>
       </c>
       <c r="H1454" t="n">
         <v>443270</v>
@@ -42564,7 +42564,7 @@
         <v>44.8300018310547</v>
       </c>
       <c r="G1455" t="n">
-        <v>41.9290390014648</v>
+        <v>41.9290351867676</v>
       </c>
       <c r="H1455" t="n">
         <v>901470</v>
@@ -42593,7 +42593,7 @@
         <v>44.9300003051758</v>
       </c>
       <c r="G1456" t="n">
-        <v>42.0225715637207</v>
+        <v>42.0225677490234</v>
       </c>
       <c r="H1456" t="n">
         <v>492527</v>
@@ -42651,7 +42651,7 @@
         <v>44.9799995422363</v>
       </c>
       <c r="G1458" t="n">
-        <v>42.0693283081055</v>
+        <v>42.0693321228027</v>
       </c>
       <c r="H1458" t="n">
         <v>433286</v>
@@ -42680,7 +42680,7 @@
         <v>43.6599998474121</v>
       </c>
       <c r="G1459" t="n">
-        <v>40.8347511291504</v>
+        <v>40.8347473144531</v>
       </c>
       <c r="H1459" t="n">
         <v>639655</v>
@@ -42912,7 +42912,7 @@
         <v>41.7400016784668</v>
       </c>
       <c r="G1467" t="n">
-        <v>39.0389976501465</v>
+        <v>39.0389938354492</v>
       </c>
       <c r="H1467" t="n">
         <v>484549</v>
@@ -43028,7 +43028,7 @@
         <v>41.2700004577637</v>
       </c>
       <c r="G1471" t="n">
-        <v>38.5994071960449</v>
+        <v>38.5994110107422</v>
       </c>
       <c r="H1471" t="n">
         <v>702211</v>
@@ -43086,7 +43086,7 @@
         <v>41.5400009155273</v>
       </c>
       <c r="G1473" t="n">
-        <v>38.8519325256348</v>
+        <v>38.851936340332</v>
       </c>
       <c r="H1473" t="n">
         <v>340759</v>
@@ -43115,7 +43115,7 @@
         <v>41.8499984741211</v>
       </c>
       <c r="G1474" t="n">
-        <v>39.1418685913086</v>
+        <v>39.1418724060059</v>
       </c>
       <c r="H1474" t="n">
         <v>342794</v>
@@ -43144,7 +43144,7 @@
         <v>42</v>
       </c>
       <c r="G1475" t="n">
-        <v>39.282169342041</v>
+        <v>39.2821655273438</v>
       </c>
       <c r="H1475" t="n">
         <v>857228</v>
@@ -43202,7 +43202,7 @@
         <v>43.3199996948242</v>
       </c>
       <c r="G1477" t="n">
-        <v>40.5167465209961</v>
+        <v>40.5167541503906</v>
       </c>
       <c r="H1477" t="n">
         <v>425403</v>
@@ -43231,7 +43231,7 @@
         <v>43.689998626709</v>
       </c>
       <c r="G1478" t="n">
-        <v>40.8628120422363</v>
+        <v>40.8628044128418</v>
       </c>
       <c r="H1478" t="n">
         <v>511321</v>
@@ -43289,7 +43289,7 @@
         <v>43.2700004577637</v>
       </c>
       <c r="G1480" t="n">
-        <v>40.4699859619141</v>
+        <v>40.4699897766113</v>
       </c>
       <c r="H1480" t="n">
         <v>654400</v>
@@ -43318,7 +43318,7 @@
         <v>42.8499984741211</v>
       </c>
       <c r="G1481" t="n">
-        <v>40.0771675109863</v>
+        <v>40.0771636962891</v>
       </c>
       <c r="H1481" t="n">
         <v>659451</v>
@@ -43405,7 +43405,7 @@
         <v>44.7000007629395</v>
       </c>
       <c r="G1484" t="n">
-        <v>41.8074569702148</v>
+        <v>41.8074531555176</v>
       </c>
       <c r="H1484" t="n">
         <v>568492</v>
@@ -43434,7 +43434,7 @@
         <v>44.1100006103516</v>
       </c>
       <c r="G1485" t="n">
-        <v>41.2556304931641</v>
+        <v>41.2556343078613</v>
       </c>
       <c r="H1485" t="n">
         <v>541206</v>
@@ -43521,7 +43521,7 @@
         <v>45.7599983215332</v>
       </c>
       <c r="G1488" t="n">
-        <v>42.7988624572754</v>
+        <v>42.7988586425781</v>
       </c>
       <c r="H1488" t="n">
         <v>814303</v>
@@ -43608,7 +43608,7 @@
         <v>46.0699996948242</v>
       </c>
       <c r="G1491" t="n">
-        <v>43.0888023376465</v>
+        <v>43.0887985229492</v>
       </c>
       <c r="H1491" t="n">
         <v>453203</v>
@@ -43695,7 +43695,7 @@
         <v>46.0099983215332</v>
       </c>
       <c r="G1494" t="n">
-        <v>43.0326766967773</v>
+        <v>43.0326805114746</v>
       </c>
       <c r="H1494" t="n">
         <v>399375</v>
@@ -43811,7 +43811,7 @@
         <v>44.5499992370605</v>
       </c>
       <c r="G1498" t="n">
-        <v>41.6671600341797</v>
+        <v>41.6671562194824</v>
       </c>
       <c r="H1498" t="n">
         <v>594524</v>
@@ -43869,7 +43869,7 @@
         <v>42.3400001525879</v>
       </c>
       <c r="G1500" t="n">
-        <v>39.600170135498</v>
+        <v>39.6001663208008</v>
       </c>
       <c r="H1500" t="n">
         <v>499034</v>
@@ -43898,7 +43898,7 @@
         <v>42.7400016784668</v>
       </c>
       <c r="G1501" t="n">
-        <v>39.9742813110352</v>
+        <v>39.9742851257324</v>
       </c>
       <c r="H1501" t="n">
         <v>393603</v>
@@ -43927,7 +43927,7 @@
         <v>43.2999992370605</v>
       </c>
       <c r="G1502" t="n">
-        <v>40.4980430603027</v>
+        <v>40.498046875</v>
       </c>
       <c r="H1502" t="n">
         <v>315394</v>
@@ -43956,7 +43956,7 @@
         <v>42.2000007629395</v>
       </c>
       <c r="G1503" t="n">
-        <v>39.4692230224609</v>
+        <v>39.4692268371582</v>
       </c>
       <c r="H1503" t="n">
         <v>628603</v>
@@ -44014,7 +44014,7 @@
         <v>43.1199989318848</v>
       </c>
       <c r="G1505" t="n">
-        <v>40.3296890258789</v>
+        <v>40.3296928405762</v>
       </c>
       <c r="H1505" t="n">
         <v>971437</v>
@@ -44101,7 +44101,7 @@
         <v>41.9000015258789</v>
       </c>
       <c r="G1508" t="n">
-        <v>39.1886444091797</v>
+        <v>39.1886405944824</v>
       </c>
       <c r="H1508" t="n">
         <v>525863</v>
@@ -44275,7 +44275,7 @@
         <v>41.9599990844727</v>
       </c>
       <c r="G1514" t="n">
-        <v>39.2447547912598</v>
+        <v>39.2447509765625</v>
       </c>
       <c r="H1514" t="n">
         <v>429271</v>
@@ -44304,7 +44304,7 @@
         <v>42.7700004577637</v>
       </c>
       <c r="G1515" t="n">
-        <v>40.0023384094238</v>
+        <v>40.0023345947266</v>
       </c>
       <c r="H1515" t="n">
         <v>755996</v>
@@ -44391,7 +44391,7 @@
         <v>44.0800018310547</v>
       </c>
       <c r="G1518" t="n">
-        <v>41.2275733947754</v>
+        <v>41.2275772094727</v>
       </c>
       <c r="H1518" t="n">
         <v>793149</v>
@@ -44449,7 +44449,7 @@
         <v>44.2999992370605</v>
       </c>
       <c r="G1520" t="n">
-        <v>41.4333267211914</v>
+        <v>41.4333305358887</v>
       </c>
       <c r="H1520" t="n">
         <v>304600</v>
@@ -44507,7 +44507,7 @@
         <v>45.439998626709</v>
       </c>
       <c r="G1522" t="n">
-        <v>42.4995651245117</v>
+        <v>42.4995613098145</v>
       </c>
       <c r="H1522" t="n">
         <v>241173</v>
@@ -44565,7 +44565,7 @@
         <v>46.9099998474121</v>
       </c>
       <c r="G1524" t="n">
-        <v>43.874439239502</v>
+        <v>43.8744430541992</v>
       </c>
       <c r="H1524" t="n">
         <v>480779</v>
@@ -44710,7 +44710,7 @@
         <v>45.8499984741211</v>
       </c>
       <c r="G1529" t="n">
-        <v>42.8830375671387</v>
+        <v>42.8830337524414</v>
       </c>
       <c r="H1529" t="n">
         <v>343240</v>
@@ -44739,7 +44739,7 @@
         <v>44.3300018310547</v>
       </c>
       <c r="G1530" t="n">
-        <v>41.4613914489746</v>
+        <v>41.4613952636719</v>
       </c>
       <c r="H1530" t="n">
         <v>702233</v>
@@ -44768,7 +44768,7 @@
         <v>43.5800018310547</v>
       </c>
       <c r="G1531" t="n">
-        <v>40.7599258422852</v>
+        <v>40.7599296569824</v>
       </c>
       <c r="H1531" t="n">
         <v>486886</v>
@@ -44797,7 +44797,7 @@
         <v>41.6599998474121</v>
       </c>
       <c r="G1532" t="n">
-        <v>38.9641723632812</v>
+        <v>38.964168548584</v>
       </c>
       <c r="H1532" t="n">
         <v>916165</v>
@@ -45087,7 +45087,7 @@
         <v>37.2400016784668</v>
       </c>
       <c r="G1542" t="n">
-        <v>34.8301887512207</v>
+        <v>34.830192565918</v>
       </c>
       <c r="H1542" t="n">
         <v>703425</v>
@@ -45116,7 +45116,7 @@
         <v>35.9300003051758</v>
       </c>
       <c r="G1543" t="n">
-        <v>33.6049652099609</v>
+        <v>33.6049575805664</v>
       </c>
       <c r="H1543" t="n">
         <v>941049</v>
@@ -45145,7 +45145,7 @@
         <v>36.4300003051758</v>
       </c>
       <c r="G1544" t="n">
-        <v>34.0726089477539</v>
+        <v>34.0726051330566</v>
       </c>
       <c r="H1544" t="n">
         <v>768073</v>
@@ -45203,7 +45203,7 @@
         <v>35.8699989318848</v>
       </c>
       <c r="G1546" t="n">
-        <v>33.5488357543945</v>
+        <v>33.5488395690918</v>
       </c>
       <c r="H1546" t="n">
         <v>1124966</v>
@@ -45232,7 +45232,7 @@
         <v>37.5299987792969</v>
       </c>
       <c r="G1547" t="n">
-        <v>35.1014213562012</v>
+        <v>35.1014251708984</v>
       </c>
       <c r="H1547" t="n">
         <v>913110</v>
@@ -45319,7 +45319,7 @@
         <v>37.0099983215332</v>
       </c>
       <c r="G1550" t="n">
-        <v>34.6150741577148</v>
+        <v>34.6150703430176</v>
       </c>
       <c r="H1550" t="n">
         <v>981448</v>
@@ -45406,7 +45406,7 @@
         <v>35.0900001525879</v>
       </c>
       <c r="G1553" t="n">
-        <v>32.8193168640137</v>
+        <v>32.8193130493164</v>
       </c>
       <c r="H1553" t="n">
         <v>789810</v>
@@ -45435,7 +45435,7 @@
         <v>36.5499992370605</v>
       </c>
       <c r="G1554" t="n">
-        <v>34.1848373413086</v>
+        <v>34.1848411560059</v>
       </c>
       <c r="H1554" t="n">
         <v>608794</v>
@@ -45580,7 +45580,7 @@
         <v>35.6699981689453</v>
       </c>
       <c r="G1559" t="n">
-        <v>33.3617858886719</v>
+        <v>33.3617820739746</v>
       </c>
       <c r="H1559" t="n">
         <v>484582</v>
@@ -45638,7 +45638,7 @@
         <v>35.5400009155273</v>
       </c>
       <c r="G1561" t="n">
-        <v>33.2402000427246</v>
+        <v>33.2402038574219</v>
       </c>
       <c r="H1561" t="n">
         <v>430575</v>
@@ -45696,7 +45696,7 @@
         <v>35.2099990844727</v>
       </c>
       <c r="G1563" t="n">
-        <v>32.9315490722656</v>
+        <v>32.9315528869629</v>
       </c>
       <c r="H1563" t="n">
         <v>513894</v>
@@ -45725,7 +45725,7 @@
         <v>35.9799995422363</v>
       </c>
       <c r="G1564" t="n">
-        <v>33.651725769043</v>
+        <v>33.6517219543457</v>
       </c>
       <c r="H1564" t="n">
         <v>697723</v>
@@ -45841,7 +45841,7 @@
         <v>37.9599990844727</v>
       </c>
       <c r="G1568" t="n">
-        <v>35.5036010742188</v>
+        <v>35.5035972595215</v>
       </c>
       <c r="H1568" t="n">
         <v>716145</v>
@@ -45870,7 +45870,7 @@
         <v>37.939998626709</v>
       </c>
       <c r="G1569" t="n">
-        <v>35.4848937988281</v>
+        <v>35.4848899841309</v>
       </c>
       <c r="H1569" t="n">
         <v>574303</v>
@@ -45899,7 +45899,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G1570" t="n">
-        <v>35.1668930053711</v>
+        <v>35.1668891906738</v>
       </c>
       <c r="H1570" t="n">
         <v>577192</v>
@@ -45986,7 +45986,7 @@
         <v>34.9599990844727</v>
       </c>
       <c r="G1573" t="n">
-        <v>32.6977310180664</v>
+        <v>32.6977272033691</v>
       </c>
       <c r="H1573" t="n">
         <v>883610</v>
@@ -46015,7 +46015,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G1574" t="n">
-        <v>34.6992492675781</v>
+        <v>34.6992454528809</v>
       </c>
       <c r="H1574" t="n">
         <v>669229</v>
@@ -46073,7 +46073,7 @@
         <v>35.8400001525879</v>
       </c>
       <c r="G1576" t="n">
-        <v>33.5207824707031</v>
+        <v>33.5207862854004</v>
       </c>
       <c r="H1576" t="n">
         <v>498650</v>
@@ -46102,7 +46102,7 @@
         <v>36.5699996948242</v>
       </c>
       <c r="G1577" t="n">
-        <v>34.2035446166992</v>
+        <v>34.2035484313965</v>
       </c>
       <c r="H1577" t="n">
         <v>304231</v>
@@ -46131,7 +46131,7 @@
         <v>36.3499984741211</v>
       </c>
       <c r="G1578" t="n">
-        <v>33.9977836608887</v>
+        <v>33.9977874755859</v>
       </c>
       <c r="H1578" t="n">
         <v>319176</v>
@@ -46189,7 +46189,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G1580" t="n">
-        <v>35.1668930053711</v>
+        <v>35.1668891906738</v>
       </c>
       <c r="H1580" t="n">
         <v>326066</v>
@@ -46305,7 +46305,7 @@
         <v>36.9700012207031</v>
       </c>
       <c r="G1584" t="n">
-        <v>34.5776672363281</v>
+        <v>34.5776634216309</v>
       </c>
       <c r="H1584" t="n">
         <v>289749</v>
@@ -46334,7 +46334,7 @@
         <v>36.5299987792969</v>
       </c>
       <c r="G1585" t="n">
-        <v>34.166130065918</v>
+        <v>34.1661338806152</v>
       </c>
       <c r="H1585" t="n">
         <v>274920</v>
@@ -46450,7 +46450,7 @@
         <v>40.6100006103516</v>
       </c>
       <c r="G1589" t="n">
-        <v>37.9821128845215</v>
+        <v>37.9821166992188</v>
       </c>
       <c r="H1589" t="n">
         <v>835080</v>
@@ -46479,7 +46479,7 @@
         <v>40.5400009155273</v>
       </c>
       <c r="G1590" t="n">
-        <v>37.9166488647461</v>
+        <v>37.9166450500488</v>
       </c>
       <c r="H1590" t="n">
         <v>518903</v>
@@ -46508,7 +46508,7 @@
         <v>41.8800010681152</v>
       </c>
       <c r="G1591" t="n">
-        <v>39.1699333190918</v>
+        <v>39.1699371337891</v>
       </c>
       <c r="H1591" t="n">
         <v>796747</v>
@@ -46798,7 +46798,7 @@
         <v>40.8199996948242</v>
       </c>
       <c r="G1601" t="n">
-        <v>38.1785278320312</v>
+        <v>38.178524017334</v>
       </c>
       <c r="H1601" t="n">
         <v>963321</v>
@@ -46827,7 +46827,7 @@
         <v>40.2000007629395</v>
       </c>
       <c r="G1602" t="n">
-        <v>37.5986442565918</v>
+        <v>37.5986480712891</v>
       </c>
       <c r="H1602" t="n">
         <v>562715</v>
@@ -46856,7 +46856,7 @@
         <v>39.5299987792969</v>
       </c>
       <c r="G1603" t="n">
-        <v>36.9720001220703</v>
+        <v>36.9720039367676</v>
       </c>
       <c r="H1603" t="n">
         <v>418572</v>
@@ -46885,7 +46885,7 @@
         <v>38.310001373291</v>
       </c>
       <c r="G1604" t="n">
-        <v>35.8309555053711</v>
+        <v>35.8309516906738</v>
       </c>
       <c r="H1604" t="n">
         <v>500745</v>
@@ -46943,7 +46943,7 @@
         <v>37.8199996948242</v>
       </c>
       <c r="G1606" t="n">
-        <v>35.3726577758789</v>
+        <v>35.3726615905762</v>
       </c>
       <c r="H1606" t="n">
         <v>456099</v>
@@ -47059,7 +47059,7 @@
         <v>37.6100006103516</v>
       </c>
       <c r="G1610" t="n">
-        <v>35.1762504577637</v>
+        <v>35.1762466430664</v>
       </c>
       <c r="H1610" t="n">
         <v>360397</v>
@@ -47088,7 +47088,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G1611" t="n">
-        <v>34.6992492675781</v>
+        <v>34.6992454528809</v>
       </c>
       <c r="H1611" t="n">
         <v>474247</v>
@@ -47175,7 +47175,7 @@
         <v>35.4599990844727</v>
       </c>
       <c r="G1614" t="n">
-        <v>33.1653709411621</v>
+        <v>33.1653747558594</v>
       </c>
       <c r="H1614" t="n">
         <v>550722</v>
@@ -47233,7 +47233,7 @@
         <v>34.3300018310547</v>
       </c>
       <c r="G1616" t="n">
-        <v>32.1084976196289</v>
+        <v>32.1084938049316</v>
       </c>
       <c r="H1616" t="n">
         <v>449630</v>
@@ -47320,7 +47320,7 @@
         <v>34.25</v>
       </c>
       <c r="G1619" t="n">
-        <v>32.0336723327637</v>
+        <v>32.0336685180664</v>
       </c>
       <c r="H1619" t="n">
         <v>563990</v>
@@ -47349,7 +47349,7 @@
         <v>34.2599983215332</v>
       </c>
       <c r="G1620" t="n">
-        <v>32.043025970459</v>
+        <v>32.0430221557617</v>
       </c>
       <c r="H1620" t="n">
         <v>286402</v>
@@ -47407,7 +47407,7 @@
         <v>32.5499992370605</v>
       </c>
       <c r="G1622" t="n">
-        <v>30.4436817169189</v>
+        <v>30.4436798095703</v>
       </c>
       <c r="H1622" t="n">
         <v>753388</v>
@@ -47436,7 +47436,7 @@
         <v>31.5799999237061</v>
       </c>
       <c r="G1623" t="n">
-        <v>29.5364513397217</v>
+        <v>29.536449432373</v>
       </c>
       <c r="H1623" t="n">
         <v>848404</v>
@@ -47494,7 +47494,7 @@
         <v>32.2200012207031</v>
       </c>
       <c r="G1625" t="n">
-        <v>30.3824329376221</v>
+        <v>30.3824367523193</v>
       </c>
       <c r="H1625" t="n">
         <v>368159</v>
@@ -47523,7 +47523,7 @@
         <v>32.0099983215332</v>
       </c>
       <c r="G1626" t="n">
-        <v>30.1844081878662</v>
+        <v>30.1844100952148</v>
       </c>
       <c r="H1626" t="n">
         <v>444749</v>
@@ -47610,7 +47610,7 @@
         <v>32.3699989318848</v>
       </c>
       <c r="G1629" t="n">
-        <v>30.5238761901855</v>
+        <v>30.5238780975342</v>
       </c>
       <c r="H1629" t="n">
         <v>283177</v>
@@ -47668,7 +47668,7 @@
         <v>32.060001373291</v>
       </c>
       <c r="G1631" t="n">
-        <v>30.231559753418</v>
+        <v>30.2315616607666</v>
       </c>
       <c r="H1631" t="n">
         <v>940573</v>
@@ -47697,7 +47697,7 @@
         <v>31.1700000762939</v>
       </c>
       <c r="G1632" t="n">
-        <v>29.3923168182373</v>
+        <v>29.3923187255859</v>
       </c>
       <c r="H1632" t="n">
         <v>722275</v>
@@ -47726,7 +47726,7 @@
         <v>31.1700000762939</v>
       </c>
       <c r="G1633" t="n">
-        <v>29.3923168182373</v>
+        <v>29.3923187255859</v>
       </c>
       <c r="H1633" t="n">
         <v>309633</v>
@@ -47784,7 +47784,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G1635" t="n">
-        <v>29.797794342041</v>
+        <v>29.7977924346924</v>
       </c>
       <c r="H1635" t="n">
         <v>188693</v>
@@ -47813,7 +47813,7 @@
         <v>31.3299999237061</v>
       </c>
       <c r="G1636" t="n">
-        <v>29.54319190979</v>
+        <v>29.5431938171387</v>
       </c>
       <c r="H1636" t="n">
         <v>296907</v>
@@ -47900,7 +47900,7 @@
         <v>29.2099990844727</v>
       </c>
       <c r="G1639" t="n">
-        <v>27.5440998077393</v>
+        <v>27.5440979003906</v>
       </c>
       <c r="H1639" t="n">
         <v>562853</v>
@@ -47958,7 +47958,7 @@
         <v>26.3700008392334</v>
       </c>
       <c r="G1641" t="n">
-        <v>24.8660697937012</v>
+        <v>24.8660717010498</v>
       </c>
       <c r="H1641" t="n">
         <v>1292178</v>
@@ -48016,7 +48016,7 @@
         <v>26.2199993133545</v>
       </c>
       <c r="G1643" t="n">
-        <v>24.7246227264404</v>
+        <v>24.7246246337891</v>
       </c>
       <c r="H1643" t="n">
         <v>544592</v>
@@ -48045,7 +48045,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1644" t="n">
-        <v>24.8000621795654</v>
+        <v>24.8000640869141</v>
       </c>
       <c r="H1644" t="n">
         <v>702216</v>
@@ -48074,7 +48074,7 @@
         <v>26.2900009155273</v>
       </c>
       <c r="G1645" t="n">
-        <v>24.7906341552734</v>
+        <v>24.7906322479248</v>
       </c>
       <c r="H1645" t="n">
         <v>383100</v>
@@ -48132,7 +48132,7 @@
         <v>26.7199993133545</v>
       </c>
       <c r="G1647" t="n">
-        <v>25.1961078643799</v>
+        <v>25.1961097717285</v>
       </c>
       <c r="H1647" t="n">
         <v>475290</v>
@@ -48161,7 +48161,7 @@
         <v>28.8400001525879</v>
       </c>
       <c r="G1648" t="n">
-        <v>27.1951999664307</v>
+        <v>27.1952018737793</v>
       </c>
       <c r="H1648" t="n">
         <v>983677</v>
@@ -48248,7 +48248,7 @@
         <v>29.2700004577637</v>
       </c>
       <c r="G1651" t="n">
-        <v>27.6006774902344</v>
+        <v>27.600679397583</v>
       </c>
       <c r="H1651" t="n">
         <v>361035</v>
@@ -48335,7 +48335,7 @@
         <v>30.3899993896484</v>
       </c>
       <c r="G1654" t="n">
-        <v>28.6568031311035</v>
+        <v>28.6567993164062</v>
       </c>
       <c r="H1654" t="n">
         <v>568738</v>
@@ -48393,7 +48393,7 @@
         <v>31.7299995422363</v>
       </c>
       <c r="G1656" t="n">
-        <v>29.9203796386719</v>
+        <v>29.9203777313232</v>
       </c>
       <c r="H1656" t="n">
         <v>1086443</v>
@@ -48422,7 +48422,7 @@
         <v>32.6100006103516</v>
       </c>
       <c r="G1657" t="n">
-        <v>30.7501907348633</v>
+        <v>30.7501926422119</v>
       </c>
       <c r="H1657" t="n">
         <v>748748</v>
@@ -48509,7 +48509,7 @@
         <v>31.3199996948242</v>
       </c>
       <c r="G1660" t="n">
-        <v>29.533763885498</v>
+        <v>29.5337619781494</v>
       </c>
       <c r="H1660" t="n">
         <v>382239</v>
@@ -48567,7 +48567,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G1662" t="n">
-        <v>27.0160369873047</v>
+        <v>27.0160350799561</v>
       </c>
       <c r="H1662" t="n">
         <v>871783</v>
@@ -48625,7 +48625,7 @@
         <v>29.8600006103516</v>
       </c>
       <c r="G1664" t="n">
-        <v>28.1570320129395</v>
+        <v>28.1570301055908</v>
       </c>
       <c r="H1664" t="n">
         <v>418751</v>
@@ -48712,7 +48712,7 @@
         <v>29.7800006866455</v>
       </c>
       <c r="G1667" t="n">
-        <v>28.0815906524658</v>
+        <v>28.0815925598145</v>
       </c>
       <c r="H1667" t="n">
         <v>447140</v>
@@ -48770,7 +48770,7 @@
         <v>31.1599998474121</v>
       </c>
       <c r="G1669" t="n">
-        <v>29.3828887939453</v>
+        <v>29.3828868865967</v>
       </c>
       <c r="H1669" t="n">
         <v>439564</v>
@@ -48799,7 +48799,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1670" t="n">
-        <v>28.8548259735107</v>
+        <v>28.8548278808594</v>
       </c>
       <c r="H1670" t="n">
         <v>261225</v>
@@ -48828,7 +48828,7 @@
         <v>30.4300003051758</v>
       </c>
       <c r="G1671" t="n">
-        <v>28.6945190429688</v>
+        <v>28.694522857666</v>
       </c>
       <c r="H1671" t="n">
         <v>418626</v>
@@ -48857,7 +48857,7 @@
         <v>31.3400001525879</v>
       </c>
       <c r="G1672" t="n">
-        <v>29.5526237487793</v>
+        <v>29.5526218414307</v>
       </c>
       <c r="H1672" t="n">
         <v>551405</v>
@@ -48944,7 +48944,7 @@
         <v>32.439998626709</v>
       </c>
       <c r="G1675" t="n">
-        <v>30.5898876190186</v>
+        <v>30.5898895263672</v>
       </c>
       <c r="H1675" t="n">
         <v>267865</v>
@@ -49002,7 +49002,7 @@
         <v>31.8700008392334</v>
       </c>
       <c r="G1677" t="n">
-        <v>30.0523948669434</v>
+        <v>30.052396774292</v>
       </c>
       <c r="H1677" t="n">
         <v>485376</v>
@@ -49060,7 +49060,7 @@
         <v>30.3799991607666</v>
       </c>
       <c r="G1679" t="n">
-        <v>28.6473731994629</v>
+        <v>28.6473712921143</v>
       </c>
       <c r="H1679" t="n">
         <v>548884</v>
@@ -49118,7 +49118,7 @@
         <v>29.9300003051758</v>
       </c>
       <c r="G1681" t="n">
-        <v>28.2230358123779</v>
+        <v>28.2230377197266</v>
       </c>
       <c r="H1681" t="n">
         <v>324225</v>
@@ -49176,7 +49176,7 @@
         <v>31.3199996948242</v>
       </c>
       <c r="G1683" t="n">
-        <v>29.533763885498</v>
+        <v>29.5337619781494</v>
       </c>
       <c r="H1683" t="n">
         <v>344407</v>
@@ -49234,7 +49234,7 @@
         <v>29.1100006103516</v>
       </c>
       <c r="G1685" t="n">
-        <v>27.4498062133789</v>
+        <v>27.4498043060303</v>
       </c>
       <c r="H1685" t="n">
         <v>2430377</v>
@@ -49292,7 +49292,7 @@
         <v>29.1100006103516</v>
       </c>
       <c r="G1687" t="n">
-        <v>27.4498062133789</v>
+        <v>27.4498043060303</v>
       </c>
       <c r="H1687" t="n">
         <v>436862</v>
@@ -49321,7 +49321,7 @@
         <v>28.7099990844727</v>
       </c>
       <c r="G1688" t="n">
-        <v>27.0726146697998</v>
+        <v>27.0726165771484</v>
       </c>
       <c r="H1688" t="n">
         <v>333206</v>
@@ -49350,7 +49350,7 @@
         <v>28.3299999237061</v>
       </c>
       <c r="G1689" t="n">
-        <v>26.7142887115479</v>
+        <v>26.7142868041992</v>
       </c>
       <c r="H1689" t="n">
         <v>327853</v>
@@ -49408,7 +49408,7 @@
         <v>27.6399993896484</v>
       </c>
       <c r="G1691" t="n">
-        <v>26.0636386871338</v>
+        <v>26.0636405944824</v>
       </c>
       <c r="H1691" t="n">
         <v>511204</v>
@@ -49495,7 +49495,7 @@
         <v>25.8400001525879</v>
       </c>
       <c r="G1694" t="n">
-        <v>24.3662967681885</v>
+        <v>24.3662986755371</v>
       </c>
       <c r="H1694" t="n">
         <v>609117</v>
@@ -49553,7 +49553,7 @@
         <v>26.0499992370605</v>
       </c>
       <c r="G1696" t="n">
-        <v>24.5643196105957</v>
+        <v>24.5643215179443</v>
       </c>
       <c r="H1696" t="n">
         <v>1154022</v>
@@ -49698,7 +49698,7 @@
         <v>25.3099994659424</v>
       </c>
       <c r="G1701" t="n">
-        <v>23.8665218353271</v>
+        <v>23.8665256500244</v>
       </c>
       <c r="H1701" t="n">
         <v>521253</v>
@@ -49727,7 +49727,7 @@
         <v>25.7600002288818</v>
       </c>
       <c r="G1702" t="n">
-        <v>24.2908611297607</v>
+        <v>24.2908592224121</v>
       </c>
       <c r="H1702" t="n">
         <v>442640</v>
@@ -49872,7 +49872,7 @@
         <v>24.9599990844727</v>
       </c>
       <c r="G1707" t="n">
-        <v>23.5364856719971</v>
+        <v>23.5364875793457</v>
       </c>
       <c r="H1707" t="n">
         <v>386328</v>
@@ -49901,7 +49901,7 @@
         <v>24.6700000762939</v>
       </c>
       <c r="G1708" t="n">
-        <v>23.2630252838135</v>
+        <v>23.2630233764648</v>
       </c>
       <c r="H1708" t="n">
         <v>828616</v>
@@ -50017,7 +50017,7 @@
         <v>24.7900009155273</v>
       </c>
       <c r="G1712" t="n">
-        <v>23.3761806488037</v>
+        <v>23.3761825561523</v>
       </c>
       <c r="H1712" t="n">
         <v>545948</v>
@@ -50104,7 +50104,7 @@
         <v>26.6399993896484</v>
       </c>
       <c r="G1715" t="n">
-        <v>25.1206722259521</v>
+        <v>25.1206703186035</v>
       </c>
       <c r="H1715" t="n">
         <v>1038143</v>
@@ -50191,7 +50191,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1718" t="n">
-        <v>25.3658428192139</v>
+        <v>25.3658447265625</v>
       </c>
       <c r="H1718" t="n">
         <v>498342</v>
@@ -50220,7 +50220,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1719" t="n">
-        <v>24.8943576812744</v>
+        <v>24.8943614959717</v>
       </c>
       <c r="H1719" t="n">
         <v>525721</v>
@@ -50278,7 +50278,7 @@
         <v>27.0400009155273</v>
       </c>
       <c r="G1721" t="n">
-        <v>25.4978618621826</v>
+        <v>25.497859954834</v>
       </c>
       <c r="H1721" t="n">
         <v>406526</v>
@@ -50336,7 +50336,7 @@
         <v>26.4599990844727</v>
       </c>
       <c r="G1723" t="n">
-        <v>24.9509372711182</v>
+        <v>24.9509353637695</v>
       </c>
       <c r="H1723" t="n">
         <v>549342</v>
@@ -50365,7 +50365,7 @@
         <v>26.1499996185303</v>
       </c>
       <c r="G1724" t="n">
-        <v>24.658618927002</v>
+        <v>24.6586170196533</v>
       </c>
       <c r="H1724" t="n">
         <v>284073</v>
@@ -50394,7 +50394,7 @@
         <v>25.4200000762939</v>
       </c>
       <c r="G1725" t="n">
-        <v>23.9702529907227</v>
+        <v>23.970251083374</v>
       </c>
       <c r="H1725" t="n">
         <v>633342</v>
@@ -50423,7 +50423,7 @@
         <v>24.6100006103516</v>
       </c>
       <c r="G1726" t="n">
-        <v>23.2064456939697</v>
+        <v>23.2064476013184</v>
       </c>
       <c r="H1726" t="n">
         <v>1237936</v>
@@ -50510,7 +50510,7 @@
         <v>25.2299995422363</v>
       </c>
       <c r="G1729" t="n">
-        <v>23.7910861968994</v>
+        <v>23.7910842895508</v>
       </c>
       <c r="H1729" t="n">
         <v>266249</v>
@@ -50626,7 +50626,7 @@
         <v>26.1900005340576</v>
       </c>
       <c r="G1733" t="n">
-        <v>24.6963367462158</v>
+        <v>24.6963386535645</v>
       </c>
       <c r="H1733" t="n">
         <v>520430</v>
@@ -50771,7 +50771,7 @@
         <v>24.6800003051758</v>
       </c>
       <c r="G1738" t="n">
-        <v>23.2724552154541</v>
+        <v>23.2724571228027</v>
       </c>
       <c r="H1738" t="n">
         <v>612661</v>
@@ -50858,7 +50858,7 @@
         <v>24.6800003051758</v>
       </c>
       <c r="G1741" t="n">
-        <v>23.2724552154541</v>
+        <v>23.2724571228027</v>
       </c>
       <c r="H1741" t="n">
         <v>842643</v>
@@ -51119,7 +51119,7 @@
         <v>28.6399993896484</v>
       </c>
       <c r="G1750" t="n">
-        <v>27.0066108703613</v>
+        <v>27.0066089630127</v>
       </c>
       <c r="H1750" t="n">
         <v>598511</v>
@@ -51264,7 +51264,7 @@
         <v>27.1700000762939</v>
       </c>
       <c r="G1755" t="n">
-        <v>25.6204471588135</v>
+        <v>25.6204452514648</v>
       </c>
       <c r="H1755" t="n">
         <v>541667</v>
@@ -51293,7 +51293,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1756" t="n">
-        <v>26.1202182769775</v>
+        <v>26.1202163696289</v>
       </c>
       <c r="H1756" t="n">
         <v>384912</v>
@@ -51322,7 +51322,7 @@
         <v>27.75</v>
       </c>
       <c r="G1757" t="n">
-        <v>26.1673679351807</v>
+        <v>26.167366027832</v>
       </c>
       <c r="H1757" t="n">
         <v>217161</v>
@@ -51351,7 +51351,7 @@
         <v>27.8799991607666</v>
       </c>
       <c r="G1758" t="n">
-        <v>26.2899513244629</v>
+        <v>26.2899532318115</v>
       </c>
       <c r="H1758" t="n">
         <v>238949</v>
@@ -51438,7 +51438,7 @@
         <v>26.8500003814697</v>
       </c>
       <c r="G1761" t="n">
-        <v>25.318696975708</v>
+        <v>25.3186950683594</v>
       </c>
       <c r="H1761" t="n">
         <v>1391846</v>
@@ -51467,7 +51467,7 @@
         <v>27.6499996185303</v>
       </c>
       <c r="G1762" t="n">
-        <v>26.0730686187744</v>
+        <v>26.073070526123</v>
       </c>
       <c r="H1762" t="n">
         <v>611931</v>
@@ -51554,7 +51554,7 @@
         <v>27</v>
       </c>
       <c r="G1765" t="n">
-        <v>25.4601402282715</v>
+        <v>25.4601421356201</v>
       </c>
       <c r="H1765" t="n">
         <v>1192463</v>
@@ -51728,7 +51728,7 @@
         <v>28.8799991607666</v>
       </c>
       <c r="G1771" t="n">
-        <v>27.2329196929932</v>
+        <v>27.2329216003418</v>
       </c>
       <c r="H1771" t="n">
         <v>389635</v>
@@ -51757,7 +51757,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1772" t="n">
-        <v>25.7430286407471</v>
+        <v>25.7430305480957</v>
       </c>
       <c r="H1772" t="n">
         <v>728494</v>
@@ -51815,7 +51815,7 @@
         <v>26.9099998474121</v>
       </c>
       <c r="G1774" t="n">
-        <v>25.3752727508545</v>
+        <v>25.3752746582031</v>
       </c>
       <c r="H1774" t="n">
         <v>391342</v>
@@ -51931,7 +51931,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1778" t="n">
-        <v>25.3658428192139</v>
+        <v>25.3658447265625</v>
       </c>
       <c r="H1778" t="n">
         <v>367666</v>
@@ -52018,7 +52018,7 @@
         <v>27.8799991607666</v>
       </c>
       <c r="G1781" t="n">
-        <v>26.2899513244629</v>
+        <v>26.2899532318115</v>
       </c>
       <c r="H1781" t="n">
         <v>481113</v>
@@ -52192,7 +52192,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G1787" t="n">
-        <v>25.5544357299805</v>
+        <v>25.5544376373291</v>
       </c>
       <c r="H1787" t="n">
         <v>666195</v>
@@ -52279,7 +52279,7 @@
         <v>26.8199996948242</v>
       </c>
       <c r="G1790" t="n">
-        <v>25.2904071807861</v>
+        <v>25.2904052734375</v>
       </c>
       <c r="H1790" t="n">
         <v>1472568</v>
@@ -52308,7 +52308,7 @@
         <v>26.2900009155273</v>
       </c>
       <c r="G1791" t="n">
-        <v>24.7906341552734</v>
+        <v>24.7906322479248</v>
       </c>
       <c r="H1791" t="n">
         <v>976654</v>
@@ -52366,7 +52366,7 @@
         <v>27.4599990844727</v>
       </c>
       <c r="G1793" t="n">
-        <v>25.8939037322998</v>
+        <v>25.8939056396484</v>
       </c>
       <c r="H1793" t="n">
         <v>605510</v>
@@ -52482,7 +52482,7 @@
         <v>25.7099990844727</v>
       </c>
       <c r="G1797" t="n">
-        <v>24.243709564209</v>
+        <v>24.2437076568604</v>
       </c>
       <c r="H1797" t="n">
         <v>1959838</v>
@@ -52540,7 +52540,7 @@
         <v>25.8899993896484</v>
       </c>
       <c r="G1799" t="n">
-        <v>24.4134464263916</v>
+        <v>24.413444519043</v>
       </c>
       <c r="H1799" t="n">
         <v>440981</v>
@@ -52598,7 +52598,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1801" t="n">
-        <v>24.3285789489746</v>
+        <v>24.328577041626</v>
       </c>
       <c r="H1801" t="n">
         <v>528877</v>
@@ -52627,7 +52627,7 @@
         <v>25.7399997711182</v>
       </c>
       <c r="G1802" t="n">
-        <v>24.2719993591309</v>
+        <v>24.2720012664795</v>
       </c>
       <c r="H1802" t="n">
         <v>436121</v>
@@ -52656,7 +52656,7 @@
         <v>25.5400009155273</v>
       </c>
       <c r="G1803" t="n">
-        <v>24.0834083557129</v>
+        <v>24.0834102630615</v>
       </c>
       <c r="H1803" t="n">
         <v>465119</v>
@@ -52685,7 +52685,7 @@
         <v>25.2700004577637</v>
       </c>
       <c r="G1804" t="n">
-        <v>23.8288078308105</v>
+        <v>23.8288059234619</v>
       </c>
       <c r="H1804" t="n">
         <v>578529</v>
@@ -52743,7 +52743,7 @@
         <v>27.6399993896484</v>
       </c>
       <c r="G1806" t="n">
-        <v>26.0636386871338</v>
+        <v>26.0636405944824</v>
       </c>
       <c r="H1806" t="n">
         <v>1998047</v>
@@ -52801,7 +52801,7 @@
         <v>28.5</v>
       </c>
       <c r="G1808" t="n">
-        <v>26.8745918273926</v>
+        <v>26.8745937347412</v>
       </c>
       <c r="H1808" t="n">
         <v>1102940</v>
@@ -52859,7 +52859,7 @@
         <v>28</v>
       </c>
       <c r="G1810" t="n">
-        <v>26.4031085968018</v>
+        <v>26.4031066894531</v>
       </c>
       <c r="H1810" t="n">
         <v>634206</v>
@@ -52888,7 +52888,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1811" t="n">
-        <v>26.1202182769775</v>
+        <v>26.1202163696289</v>
       </c>
       <c r="H1811" t="n">
         <v>536068</v>
@@ -52917,7 +52917,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1812" t="n">
-        <v>25.0829524993896</v>
+        <v>25.0829544067383</v>
       </c>
       <c r="H1812" t="n">
         <v>874547</v>
@@ -52975,7 +52975,7 @@
         <v>27.3400001525879</v>
       </c>
       <c r="G1814" t="n">
-        <v>25.7807502746582</v>
+        <v>25.7807483673096</v>
       </c>
       <c r="H1814" t="n">
         <v>416691</v>
@@ -53033,7 +53033,7 @@
         <v>28.1599998474121</v>
       </c>
       <c r="G1816" t="n">
-        <v>26.5539817810059</v>
+        <v>26.5539836883545</v>
       </c>
       <c r="H1816" t="n">
         <v>528323</v>
@@ -53062,7 +53062,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1817" t="n">
-        <v>25.837329864502</v>
+        <v>25.8373279571533</v>
       </c>
       <c r="H1817" t="n">
         <v>743290</v>
@@ -53120,7 +53120,7 @@
         <v>27.0499992370605</v>
       </c>
       <c r="G1819" t="n">
-        <v>25.5072898864746</v>
+        <v>25.507287979126</v>
       </c>
       <c r="H1819" t="n">
         <v>400612</v>
@@ -53323,7 +53323,7 @@
         <v>28.2199993133545</v>
       </c>
       <c r="G1826" t="n">
-        <v>26.610559463501</v>
+        <v>26.6105613708496</v>
       </c>
       <c r="H1826" t="n">
         <v>1305140</v>
@@ -53352,7 +53352,7 @@
         <v>30.1200008392334</v>
       </c>
       <c r="G1827" t="n">
-        <v>28.4022006988525</v>
+        <v>28.4022026062012</v>
       </c>
       <c r="H1827" t="n">
         <v>1939145</v>
@@ -53410,7 +53410,7 @@
         <v>29.3600006103516</v>
       </c>
       <c r="G1829" t="n">
-        <v>27.6855449676514</v>
+        <v>27.685546875</v>
       </c>
       <c r="H1829" t="n">
         <v>774702</v>
@@ -53468,7 +53468,7 @@
         <v>30.1200008392334</v>
       </c>
       <c r="G1831" t="n">
-        <v>28.4022006988525</v>
+        <v>28.4022026062012</v>
       </c>
       <c r="H1831" t="n">
         <v>470545</v>
@@ -53526,7 +53526,7 @@
         <v>29.0200004577637</v>
       </c>
       <c r="G1833" t="n">
-        <v>27.3649349212646</v>
+        <v>27.3649368286133</v>
       </c>
       <c r="H1833" t="n">
         <v>651545</v>
@@ -53555,7 +53555,7 @@
         <v>29.9699993133545</v>
       </c>
       <c r="G1834" t="n">
-        <v>28.2607555389404</v>
+        <v>28.2607574462891</v>
       </c>
       <c r="H1834" t="n">
         <v>683934</v>
@@ -53613,7 +53613,7 @@
         <v>29.9699993133545</v>
       </c>
       <c r="G1836" t="n">
-        <v>28.2607555389404</v>
+        <v>28.2607574462891</v>
       </c>
       <c r="H1836" t="n">
         <v>607249</v>
@@ -53642,7 +53642,7 @@
         <v>29.8299999237061</v>
       </c>
       <c r="G1837" t="n">
-        <v>28.1287403106689</v>
+        <v>28.1287422180176</v>
       </c>
       <c r="H1837" t="n">
         <v>811184</v>
@@ -53671,7 +53671,7 @@
         <v>29.8600006103516</v>
       </c>
       <c r="G1838" t="n">
-        <v>28.1570320129395</v>
+        <v>28.1570301055908</v>
       </c>
       <c r="H1838" t="n">
         <v>754932</v>
@@ -53729,7 +53729,7 @@
         <v>30.1299991607666</v>
       </c>
       <c r="G1840" t="n">
-        <v>28.4116287231445</v>
+        <v>28.4116306304932</v>
       </c>
       <c r="H1840" t="n">
         <v>467397</v>
@@ -53874,7 +53874,7 @@
         <v>31.6499996185303</v>
       </c>
       <c r="G1845" t="n">
-        <v>29.8449401855469</v>
+        <v>29.8449420928955</v>
       </c>
       <c r="H1845" t="n">
         <v>665575</v>
@@ -53903,7 +53903,7 @@
         <v>32.0099983215332</v>
       </c>
       <c r="G1846" t="n">
-        <v>30.1844081878662</v>
+        <v>30.1844100952148</v>
       </c>
       <c r="H1846" t="n">
         <v>507679</v>
@@ -53961,7 +53961,7 @@
         <v>31.8299999237061</v>
       </c>
       <c r="G1848" t="n">
-        <v>30.0146751403809</v>
+        <v>30.0146770477295</v>
       </c>
       <c r="H1848" t="n">
         <v>491188</v>
@@ -54106,7 +54106,7 @@
         <v>32.3699989318848</v>
       </c>
       <c r="G1853" t="n">
-        <v>30.5238761901855</v>
+        <v>30.5238780975342</v>
       </c>
       <c r="H1853" t="n">
         <v>593105</v>
@@ -54135,7 +54135,7 @@
         <v>33.1800003051758</v>
       </c>
       <c r="G1854" t="n">
-        <v>31.2876834869385</v>
+        <v>31.2876853942871</v>
       </c>
       <c r="H1854" t="n">
         <v>551571</v>
@@ -54164,7 +54164,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1855" t="n">
-        <v>30.8350582122803</v>
+        <v>30.8350601196289</v>
       </c>
       <c r="H1855" t="n">
         <v>538499</v>
@@ -54280,7 +54280,7 @@
         <v>32.810001373291</v>
       </c>
       <c r="G1859" t="n">
-        <v>30.9387893676758</v>
+        <v>30.9387912750244</v>
       </c>
       <c r="H1859" t="n">
         <v>311612</v>
@@ -54309,7 +54309,7 @@
         <v>33.4199981689453</v>
       </c>
       <c r="G1860" t="n">
-        <v>31.5139942169189</v>
+        <v>31.5139923095703</v>
       </c>
       <c r="H1860" t="n">
         <v>602763</v>
@@ -54367,7 +54367,7 @@
         <v>33.0400009155273</v>
       </c>
       <c r="G1862" t="n">
-        <v>31.1556701660156</v>
+        <v>31.1556720733643</v>
       </c>
       <c r="H1862" t="n">
         <v>351111</v>
@@ -54396,7 +54396,7 @@
         <v>33.3800010681152</v>
       </c>
       <c r="G1863" t="n">
-        <v>31.4762783050537</v>
+        <v>31.4762763977051</v>
       </c>
       <c r="H1863" t="n">
         <v>397676</v>
@@ -54425,7 +54425,7 @@
         <v>33.7900009155273</v>
       </c>
       <c r="G1864" t="n">
-        <v>31.8628978729248</v>
+        <v>31.8628940582275</v>
       </c>
       <c r="H1864" t="n">
         <v>502736</v>
@@ -54454,7 +54454,7 @@
         <v>33.2799987792969</v>
       </c>
       <c r="G1865" t="n">
-        <v>31.3819789886475</v>
+        <v>31.3819770812988</v>
       </c>
       <c r="H1865" t="n">
         <v>653624</v>
@@ -54657,7 +54657,7 @@
         <v>35.3199996948242</v>
       </c>
       <c r="G1872" t="n">
-        <v>33.3056373596191</v>
+        <v>33.3056335449219</v>
       </c>
       <c r="H1872" t="n">
         <v>496197</v>
@@ -54715,7 +54715,7 @@
         <v>36.0099983215332</v>
       </c>
       <c r="G1874" t="n">
-        <v>33.9562797546387</v>
+        <v>33.9562835693359</v>
       </c>
       <c r="H1874" t="n">
         <v>548810</v>
@@ -54744,7 +54744,7 @@
         <v>35.7299995422363</v>
       </c>
       <c r="G1875" t="n">
-        <v>33.6922492980957</v>
+        <v>33.692253112793</v>
       </c>
       <c r="H1875" t="n">
         <v>305110</v>
@@ -54831,7 +54831,7 @@
         <v>33.9099998474121</v>
       </c>
       <c r="G1878" t="n">
-        <v>31.9760475158691</v>
+        <v>31.9760513305664</v>
       </c>
       <c r="H1878" t="n">
         <v>497232</v>
@@ -54860,7 +54860,7 @@
         <v>34.2200012207031</v>
       </c>
       <c r="G1879" t="n">
-        <v>32.2683753967285</v>
+        <v>32.2683715820312</v>
       </c>
       <c r="H1879" t="n">
         <v>375025</v>
@@ -80009,6 +80009,35 @@
         <v>1126108</v>
       </c>
       <c r="I2746" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2747">
+      <c r="A2747" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2747" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2747" t="n">
+        <v>12.8400001525879</v>
+      </c>
+      <c r="D2747" t="n">
+        <v>12.8699998855591</v>
+      </c>
+      <c r="E2747" t="n">
+        <v>12.664999961853</v>
+      </c>
+      <c r="F2747" t="n">
+        <v>12.7849998474121</v>
+      </c>
+      <c r="G2747" t="n">
+        <v>12.7849998474121</v>
+      </c>
+      <c r="H2747" t="n">
+        <v>631343</v>
+      </c>
+      <c r="I2747" t="s">
         <v>9</v>
       </c>
     </row>
